--- a/nao_positivados_06-2026.xlsx
+++ b/nao_positivados_06-2026.xlsx
@@ -36008,7 +36008,7 @@
         <v>6122</v>
       </c>
       <c r="D467" t="s">
-        <v>7468</v>
+        <v>7469</v>
       </c>
       <c r="E467" t="s">
         <v>8030</v>
@@ -36028,7 +36028,7 @@
         <v>6255</v>
       </c>
       <c r="D468" t="s">
-        <v>7469</v>
+        <v>7468</v>
       </c>
       <c r="E468" t="s">
         <v>8030</v>
@@ -93414,7 +93414,7 @@
         <v>6711</v>
       </c>
       <c r="D3112" t="s">
-        <v>7769</v>
+        <v>7426</v>
       </c>
       <c r="E3112" t="s">
         <v>8129</v>
@@ -93437,7 +93437,7 @@
         <v>6019</v>
       </c>
       <c r="D3113" t="s">
-        <v>7624</v>
+        <v>7625</v>
       </c>
       <c r="E3113" t="s">
         <v>8129</v>

--- a/nao_positivados_06-2026.xlsx
+++ b/nao_positivados_06-2026.xlsx
@@ -22414,496 +22414,496 @@
     <t>APERITIVO APEROL 750 ML</t>
   </si>
   <si>
-    <t>VINHO QUINTA DE VENTOZELO TINTO CÃ0</t>
+    <t>VINHO TINTO QUINTA DE VENTOZELO SOUSAO</t>
   </si>
   <si>
     <t>HUMB. CANALE DENARIO MALBEC 750ML</t>
   </si>
   <si>
+    <t>VINHO LA TOGATA BRUNELLO ETQ AZUL 750ML</t>
+  </si>
+  <si>
+    <t>VINHO FREIXO TERROIR TINTO 750ML</t>
+  </si>
+  <si>
+    <t>VINHO BAROLO BUSSIA RISERVA 750ML</t>
+  </si>
+  <si>
     <t>VINHO LA TOGATA ROSSO 750ML</t>
   </si>
   <si>
-    <t>VINHO LA TOGATA BRUNELLO ETQ AZUL 750ML</t>
-  </si>
-  <si>
-    <t>VINHO FREIXO TERROIR TINTO 750ML</t>
+    <t>HUMB. CANALE DENARIO RESERVA CAB. FRANC</t>
+  </si>
+  <si>
+    <t>RED BULL SUGAR FREE 24X250ML</t>
+  </si>
+  <si>
+    <t>RED BULL TROPICAL 24X250ML</t>
+  </si>
+  <si>
+    <t>WHISKY BUCHANANS 12 YEARS 1L</t>
+  </si>
+  <si>
+    <t>GIN BEEFEATER PINK 750ML</t>
+  </si>
+  <si>
+    <t>LICOR BALLENA MORANGO 750ML</t>
+  </si>
+  <si>
+    <t>WHISKY JIM BEAM HONEY 1L</t>
+  </si>
+  <si>
+    <t>RED BULL CEREJA 24X250ML</t>
+  </si>
+  <si>
+    <t>SMIRNOFF ICE 24X275ML LONG</t>
+  </si>
+  <si>
+    <t>GIN ROCKS STRAWBERRY 1LT</t>
+  </si>
+  <si>
+    <t>VODKA SMIRNOFF 600 ML</t>
+  </si>
+  <si>
+    <t>GIN GORDONS PINK 700ML</t>
+  </si>
+  <si>
+    <t>WHISKY J WALKER RED LABEL 1L</t>
+  </si>
+  <si>
+    <t>VINHO DOM BOSCO TINTO SECO 750ML</t>
+  </si>
+  <si>
+    <t>VODCA BAM CIROC RED BERRY 750ML</t>
+  </si>
+  <si>
+    <t>SAKE AZUMA KIRIN SOFT 740ML</t>
+  </si>
+  <si>
+    <t>GIN BEEFEATER BOTANICS 750ML</t>
+  </si>
+  <si>
+    <t>CHANDON PASSION ROSE 750ML</t>
+  </si>
+  <si>
+    <t>WHISKY WHITE HORSE - 1L</t>
+  </si>
+  <si>
+    <t>LICOR BANANINHA CARIOCA 750ML</t>
+  </si>
+  <si>
+    <t>CHANDON PASSION ON ICE 750 ML</t>
+  </si>
+  <si>
+    <t>APERITIVO CAMPARI 998ML</t>
+  </si>
+  <si>
+    <t>RC ATUM PEDACOS EM OLEO 24X140G</t>
+  </si>
+  <si>
+    <t>WHISKY JACK DANIELS APPLE 1L</t>
+  </si>
+  <si>
+    <t>GIN INVICTUS MELANCIA 900ML</t>
+  </si>
+  <si>
+    <t>NECTAR MARACUJA 12X1000ML</t>
+  </si>
+  <si>
+    <t>VINHO TINTO QUINTA DO MORGADO 750ML</t>
+  </si>
+  <si>
+    <t>AGUARDENTE OLD CESAR 88 965 ML</t>
+  </si>
+  <si>
+    <t>VINHO CAVAS DE ORO BLEND TINTO 750ML</t>
+  </si>
+  <si>
+    <t>VINHO TINTO QUINTA DO MORGADO 1LT</t>
+  </si>
+  <si>
+    <t>VINHO GRAVEDAD CAB. SAUV. DEDST</t>
+  </si>
+  <si>
+    <t>CERVEJA AMSTEL ULTRA 473 ML</t>
+  </si>
+  <si>
+    <t>COMARY MELFORT COQUETEL DE MEL 1L</t>
+  </si>
+  <si>
+    <t>LICOR COINTREAU 700 ML</t>
+  </si>
+  <si>
+    <t>CERVEJA AMSTEL PURO MALTE 473 ML</t>
+  </si>
+  <si>
+    <t>VINHO CASA PERINI CHARDONNAY 750ML</t>
+  </si>
+  <si>
+    <t>ESPUM CASA PERINI BRUT 750ML</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN LN 330ML DESC 4X6UN</t>
+  </si>
+  <si>
+    <t>CERVEJA AMSTEL LAGER 0,269LT SHR 12UNPBR</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN - KEG 5 LITROS C/2 DESC</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MORANGO C/21 UN</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT HORTELA C/21 UN</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA 200GR DUO (DP10 X20G)</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G CROCANTE (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G AMENDOIM (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>RANCHEIRO RECHEADO CHOCOLATE 90G</t>
+  </si>
+  <si>
+    <t>ST PIERRE LATA MARGARITA LT 6X270ML</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G COOKIES BRANCO (DP 16</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA BOMBOM 200G BRANCO</t>
+  </si>
+  <si>
+    <t>NG BARRA 80G 40% MEIO AMARGO (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA BOMBOM 200G (10X20G)</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G FLOCOS (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>ST PIERRE BLUEBERRY LT 24X270ML</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MELANCIA C/21 UN</t>
+  </si>
+  <si>
+    <t>MARTINI EXTRA DRY 750 ML</t>
+  </si>
+  <si>
+    <t>WHISKY GENTLEMAN JACK 1L</t>
+  </si>
+  <si>
+    <t>BALA HALLS EXTRA FORTE C/21 UND</t>
+  </si>
+  <si>
+    <t>ST PIERRE ZERO LATA TROPICAL LT 6X310ML</t>
+  </si>
+  <si>
+    <t>RUM BACARDI SUPERIOR 980ML</t>
+  </si>
+  <si>
+    <t>BALA HALLS MORANGO C/21 UND</t>
+  </si>
+  <si>
+    <t>RANCHEIRO ROSQ 500G COCO</t>
+  </si>
+  <si>
+    <t>ST PIERRE ZERO LATA GUARANA  LT 6X310ML</t>
+  </si>
+  <si>
+    <t>RC SARDINHA 125G TOMATE (05 UND)</t>
+  </si>
+  <si>
+    <t>RC ATUM RALADO MOLHO DE TOMATE 24X140G</t>
+  </si>
+  <si>
+    <t>ST PIERRE LATA SUGAR FREE LT 24X270ML</t>
+  </si>
+  <si>
+    <t>WHISKY JACK DANIELS 1L - DEST</t>
+  </si>
+  <si>
+    <t>ST PIERRE LATA PALOMA LT 270MLX6</t>
+  </si>
+  <si>
+    <t>CHANDON BABY RESERVE BRUT 187 ML</t>
+  </si>
+  <si>
+    <t>MACALLAN DOUBLE CASK 12Y 700ML</t>
+  </si>
+  <si>
+    <t>CHAMPAGNE RUINART BLANC DE BLANCS 750ML</t>
+  </si>
+  <si>
+    <t>TEQUILA DON JULIO BLANCO 750ML</t>
+  </si>
+  <si>
+    <t>NAVEIA ORIGINAL 12X1L</t>
+  </si>
+  <si>
+    <t>NAVEIA BARISTA 12X1L</t>
+  </si>
+  <si>
+    <t>NAVEIA CHOCOLATE 12X1L</t>
+  </si>
+  <si>
+    <t>MARTINI ROSATO 750 ML</t>
+  </si>
+  <si>
+    <t>PINATI NUTS COCO 16X4X25G</t>
+  </si>
+  <si>
+    <t>DP BOMBOM DADINHO ESPEC 198G</t>
+  </si>
+  <si>
+    <t>DP BOMBOM LOVERS AO LEITE CREAMY 660G</t>
+  </si>
+  <si>
+    <t>PINATI NUTS BANANA 16X4X30G</t>
+  </si>
+  <si>
+    <t>PINATI SLIM WHEY BEIJINHO 16X35G</t>
+  </si>
+  <si>
+    <t>RUM BACARDI GOLD 700ML</t>
+  </si>
+  <si>
+    <t>PINATI DOUBLE BAR BRIGADEIRO 32X35G</t>
+  </si>
+  <si>
+    <t>MOVING JUICE PROTEIN UVA 12X300ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL SF NECTARINA 4X250ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL SF MAÇA 4X250ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL ZERO</t>
+  </si>
+  <si>
+    <t>MOLHO TABASCO GREEN PEPPER SAUCE 12X60ML</t>
+  </si>
+  <si>
+    <t>MOVING BOOSTER ABACAXI HORTELA 24X310ML</t>
+  </si>
+  <si>
+    <t>GLENMORANGIE TALE OF SPICES 750ML</t>
+  </si>
+  <si>
+    <t>AMARULA C LIQUEUR 750 ML</t>
+  </si>
+  <si>
+    <t>JACK DANIELS BLACKBERRY 1L</t>
+  </si>
+  <si>
+    <t>DP PACOCA GAMADINHO POTE 50X15G</t>
+  </si>
+  <si>
+    <t>RC SARDINHA 125G OLEO (05 UND)</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MENTA C/21 UN</t>
+  </si>
+  <si>
+    <t>NG BARRA 360G 40% MEIO AMARGO (DP 40X9G)</t>
+  </si>
+  <si>
+    <t>NG NEUGEBAUER HITS 200G BOMBOM SORTIDO</t>
+  </si>
+  <si>
+    <t>PINATI SLIM WHEY BRIGADEIRO 16X35G</t>
+  </si>
+  <si>
+    <t>PINATI DB WHEY FRAPE DE COCO 12X50G</t>
+  </si>
+  <si>
+    <t>PACOCA GAMADINHO 100X15G</t>
+  </si>
+  <si>
+    <t>NG DOCE DE LEITE MUMU 350G</t>
+  </si>
+  <si>
+    <t>PINATI SWEET COCADINHA CHOCO 24X14G</t>
+  </si>
+  <si>
+    <t>PF MENTOS STICK 14 B. FRUTAS DP/16</t>
+  </si>
+  <si>
+    <t>VEUVE CLICQUOT BRUT 750 ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL CEREJA</t>
+  </si>
+  <si>
+    <t>RC ATUM SOLIDO NATURAL 24X170G</t>
+  </si>
+  <si>
+    <t>BALA HALLS CEREJA C/21 UND</t>
+  </si>
+  <si>
+    <t>BOM AR AERO 360 ML ALEGRIA</t>
+  </si>
+  <si>
+    <t>WHISKY JAMESON CASKMATES IPA 750ML</t>
+  </si>
+  <si>
+    <t>AZEITE DE OLIVA EV ESSENZA 5L</t>
+  </si>
+  <si>
+    <t>NG BIBS 720G AMENDOLATE (DP 18X40G)</t>
+  </si>
+  <si>
+    <t>BALA HALLS UVA VERDE C/21 UND</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MAX RASPEBERRY 14X16,5G</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MENTA C/ 14 UND</t>
+  </si>
+  <si>
+    <t>PINATI NUTS ORIGINAL 20X30G</t>
+  </si>
+  <si>
+    <t>ST PIERRE ZERO LATA GREEN APPLE 24X310ML</t>
+  </si>
+  <si>
+    <t>PF FRUTTELLA MAST.MOR.NAT DP/16</t>
+  </si>
+  <si>
+    <t>CHICLETE BUBBALOO TUTTI FRUTI C/60 UN</t>
+  </si>
+  <si>
+    <t>NATIKOS BARRA F. BANANA E AÇAI 12X30G</t>
+  </si>
+  <si>
+    <t>CACHACA JOIA DA SERRA TRADICIONAL 1L</t>
+  </si>
+  <si>
+    <t>INSETICIDA SBP 450 ML MULTI</t>
+  </si>
+  <si>
+    <t>INSETICIDA SBP 360 ML ULTRA BARREIRA</t>
+  </si>
+  <si>
+    <t>VINHO GRAVEDAD CARMENERE 750ML</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA BOMBOM 500G</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G BRANCO (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA BOMBOM BRANCO 500G</t>
+  </si>
+  <si>
+    <t>WHISKY BALLANTINE S FINEST 750ML</t>
+  </si>
+  <si>
+    <t>LICOR ESC DRAMBUIE 750 ML</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MAX MENTABERRY 14X16,5G</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G AO LEITE (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>BOM AR AERO 360 ML CHEIRO DE TALCO</t>
+  </si>
+  <si>
+    <t>BOM AR AERO 360 ML LIMAO SICILIANO</t>
+  </si>
+  <si>
+    <t>PINATI NUTS BANANA 20X30G</t>
+  </si>
+  <si>
+    <t>NAPOLITANO STICKS 16X29G</t>
+  </si>
+  <si>
+    <t>RANCHEIRO WAFER CHOCOLATE 78G</t>
+  </si>
+  <si>
+    <t>SMIRNOFF RED PET 1750 ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL SF POMELO 4X250ML</t>
+  </si>
+  <si>
+    <t>AGUA MINERAL MAMBA WATER C/ GAS 12X350ML</t>
+  </si>
+  <si>
+    <t>RED BULL SF NECTARINA 24X250ML</t>
+  </si>
+  <si>
+    <t>ST PIERRE VIDRO PINK LIMONADE LN 275X12</t>
+  </si>
+  <si>
+    <t>WHISKY J WALKER GREEN LABEL - 750ML</t>
+  </si>
+  <si>
+    <t>RED BULL SF MAÇA 24X250ML</t>
+  </si>
+  <si>
+    <t>GIN MARINA 750ML</t>
+  </si>
+  <si>
+    <t>VINHO TTO BERTOLI CHIANTI DOCG 750ML</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN ZERO LONG  24X330ML</t>
+  </si>
+  <si>
+    <t>WHISKY CHIVAS XV GOLD 700ML</t>
+  </si>
+  <si>
+    <t>FRISANTE MACAW TROPICAL MOSC. ROSE 750ML</t>
+  </si>
+  <si>
+    <t>FRISANTE MACAW TROPICAL MOSCATO 750ML</t>
+  </si>
+  <si>
+    <t>ESPUMANTE ARESTI CHARDONNAY 187,5ML</t>
+  </si>
+  <si>
+    <t>WHISKY J WALKER GOLD LABEL RESERVE 750ML</t>
+  </si>
+  <si>
+    <t>RED BULL SF POMELO 24X250ML</t>
+  </si>
+  <si>
+    <t>NOSSO CHOP RED DRAFT VD 6X600ML</t>
+  </si>
+  <si>
+    <t>VINHO ARESTI ESTATE S. CHARDONNAY 187ML</t>
+  </si>
+  <si>
+    <t>VINHO ARESTI ESTATE S. CAB SAUV 187ML</t>
+  </si>
+  <si>
+    <t>VINHO FOODKILLER CARMENERE 750ML</t>
+  </si>
+  <si>
+    <t>VINHO ARESTI ESTATE S. CAB SAUV 750ML</t>
+  </si>
+  <si>
+    <t>WHISKY J WALKER BLUE LABEL 750 ML</t>
+  </si>
+  <si>
+    <t>VILLA ROSA COLHEITA BRANCO 750ML</t>
   </si>
   <si>
     <t>VINHO BCO ARCAIA PINOT GRIGIO 750ML</t>
-  </si>
-  <si>
-    <t>VINHO BAROLO BUSSIA RISERVA 750ML</t>
-  </si>
-  <si>
-    <t>HUMB. CANALE DENARIO RESERVA CAB. FRANC</t>
-  </si>
-  <si>
-    <t>RED BULL SUGAR FREE 24X250ML</t>
-  </si>
-  <si>
-    <t>RED BULL TROPICAL 24X250ML</t>
-  </si>
-  <si>
-    <t>WHISKY BUCHANANS 12 YEARS 1L</t>
-  </si>
-  <si>
-    <t>GIN BEEFEATER PINK 750ML</t>
-  </si>
-  <si>
-    <t>LICOR BALLENA MORANGO 750ML</t>
-  </si>
-  <si>
-    <t>WHISKY JIM BEAM HONEY 1L</t>
-  </si>
-  <si>
-    <t>RED BULL CEREJA 24X250ML</t>
-  </si>
-  <si>
-    <t>SMIRNOFF ICE 24X275ML LONG</t>
-  </si>
-  <si>
-    <t>GIN ROCKS STRAWBERRY 1LT</t>
-  </si>
-  <si>
-    <t>VODKA SMIRNOFF 600 ML</t>
-  </si>
-  <si>
-    <t>GIN GORDONS PINK 700ML</t>
-  </si>
-  <si>
-    <t>WHISKY J WALKER RED LABEL 1L</t>
-  </si>
-  <si>
-    <t>VINHO DOM BOSCO TINTO SECO 750ML</t>
-  </si>
-  <si>
-    <t>VODCA BAM CIROC RED BERRY 750ML</t>
-  </si>
-  <si>
-    <t>SAKE AZUMA KIRIN SOFT 740ML</t>
-  </si>
-  <si>
-    <t>GIN BEEFEATER BOTANICS 750ML</t>
-  </si>
-  <si>
-    <t>CHANDON PASSION ROSE 750ML</t>
-  </si>
-  <si>
-    <t>WHISKY WHITE HORSE - 1L</t>
-  </si>
-  <si>
-    <t>LICOR BANANINHA CARIOCA 750ML</t>
-  </si>
-  <si>
-    <t>CHANDON PASSION ON ICE 750 ML</t>
-  </si>
-  <si>
-    <t>APERITIVO CAMPARI 998ML</t>
-  </si>
-  <si>
-    <t>RC ATUM PEDACOS EM OLEO 24X140G</t>
-  </si>
-  <si>
-    <t>WHISKY JACK DANIELS APPLE 1L</t>
-  </si>
-  <si>
-    <t>GIN INVICTUS MELANCIA 900ML</t>
-  </si>
-  <si>
-    <t>NECTAR MARACUJA 12X1000ML</t>
-  </si>
-  <si>
-    <t>VINHO TINTO QUINTA DO MORGADO 750ML</t>
-  </si>
-  <si>
-    <t>AGUARDENTE OLD CESAR 88 965 ML</t>
-  </si>
-  <si>
-    <t>VINHO CAVAS DE ORO BLEND TINTO 750ML</t>
-  </si>
-  <si>
-    <t>VINHO TINTO QUINTA DO MORGADO 1LT</t>
-  </si>
-  <si>
-    <t>VINHO GRAVEDAD CAB. SAUV. DEDST</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL ULTRA 473 ML</t>
-  </si>
-  <si>
-    <t>COMARY MELFORT COQUETEL DE MEL 1L</t>
-  </si>
-  <si>
-    <t>LICOR COINTREAU 700 ML</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL PURO MALTE 473 ML</t>
-  </si>
-  <si>
-    <t>VINHO CASA PERINI CHARDONNAY 750ML</t>
-  </si>
-  <si>
-    <t>ESPUM CASA PERINI BRUT 750ML</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN LN 330ML DESC 4X6UN</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL LAGER 0,269LT SHR 12UNPBR</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN - KEG 5 LITROS C/2 DESC</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MORANGO C/21 UN</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT HORTELA C/21 UN</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA 200GR DUO (DP10 X20G)</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G CROCANTE (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G AMENDOIM (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>RANCHEIRO RECHEADO CHOCOLATE 90G</t>
-  </si>
-  <si>
-    <t>ST PIERRE LATA MARGARITA LT 6X270ML</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G COOKIES BRANCO (DP 16</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA BOMBOM 200G BRANCO</t>
-  </si>
-  <si>
-    <t>NG BARRA 80G 40% MEIO AMARGO (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA BOMBOM 200G (10X20G)</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G FLOCOS (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>ST PIERRE BLUEBERRY LT 24X270ML</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MELANCIA C/21 UN</t>
-  </si>
-  <si>
-    <t>MARTINI EXTRA DRY 750 ML</t>
-  </si>
-  <si>
-    <t>WHISKY GENTLEMAN JACK 1L</t>
-  </si>
-  <si>
-    <t>BALA HALLS EXTRA FORTE C/21 UND</t>
-  </si>
-  <si>
-    <t>ST PIERRE ZERO LATA TROPICAL LT 6X310ML</t>
-  </si>
-  <si>
-    <t>RUM BACARDI SUPERIOR 980ML</t>
-  </si>
-  <si>
-    <t>BALA HALLS MORANGO C/21 UND</t>
-  </si>
-  <si>
-    <t>RANCHEIRO ROSQ 500G COCO</t>
-  </si>
-  <si>
-    <t>ST PIERRE ZERO LATA GUARANA  LT 6X310ML</t>
-  </si>
-  <si>
-    <t>RC SARDINHA 125G TOMATE (05 UND)</t>
-  </si>
-  <si>
-    <t>RC ATUM RALADO MOLHO DE TOMATE 24X140G</t>
-  </si>
-  <si>
-    <t>ST PIERRE LATA SUGAR FREE LT 24X270ML</t>
-  </si>
-  <si>
-    <t>WHISKY JACK DANIELS 1L - DEST</t>
-  </si>
-  <si>
-    <t>ST PIERRE LATA PALOMA LT 270MLX6</t>
-  </si>
-  <si>
-    <t>CHANDON BABY RESERVE BRUT 187 ML</t>
-  </si>
-  <si>
-    <t>MACALLAN DOUBLE CASK 12Y 700ML</t>
-  </si>
-  <si>
-    <t>CHAMPAGNE RUINART BLANC DE BLANCS 750ML</t>
-  </si>
-  <si>
-    <t>TEQUILA DON JULIO BLANCO 750ML</t>
-  </si>
-  <si>
-    <t>NAVEIA ORIGINAL 12X1L</t>
-  </si>
-  <si>
-    <t>NAVEIA BARISTA 12X1L</t>
-  </si>
-  <si>
-    <t>NAVEIA CHOCOLATE 12X1L</t>
-  </si>
-  <si>
-    <t>MARTINI ROSATO 750 ML</t>
-  </si>
-  <si>
-    <t>PINATI NUTS COCO 16X4X25G</t>
-  </si>
-  <si>
-    <t>DP BOMBOM DADINHO ESPEC 198G</t>
-  </si>
-  <si>
-    <t>DP BOMBOM LOVERS AO LEITE CREAMY 660G</t>
-  </si>
-  <si>
-    <t>PINATI NUTS BANANA 16X4X30G</t>
-  </si>
-  <si>
-    <t>PINATI SLIM WHEY BEIJINHO 16X35G</t>
-  </si>
-  <si>
-    <t>RUM BACARDI GOLD 700ML</t>
-  </si>
-  <si>
-    <t>PINATI DOUBLE BAR BRIGADEIRO 32X35G</t>
-  </si>
-  <si>
-    <t>MOVING JUICE PROTEIN UVA 12X300ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL SF NECTARINA 4X250ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL SF MAÇA 4X250ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL ZERO</t>
-  </si>
-  <si>
-    <t>MOLHO TABASCO GREEN PEPPER SAUCE 12X60ML</t>
-  </si>
-  <si>
-    <t>MOVING BOOSTER ABACAXI HORTELA 24X310ML</t>
-  </si>
-  <si>
-    <t>GLENMORANGIE TALE OF SPICES 750ML</t>
-  </si>
-  <si>
-    <t>AMARULA C LIQUEUR 750 ML</t>
-  </si>
-  <si>
-    <t>JACK DANIELS BLACKBERRY 1L</t>
-  </si>
-  <si>
-    <t>DP PACOCA GAMADINHO POTE 50X15G</t>
-  </si>
-  <si>
-    <t>RC SARDINHA 125G OLEO (05 UND)</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MENTA C/21 UN</t>
-  </si>
-  <si>
-    <t>NG BARRA 360G 40% MEIO AMARGO (DP 40X9G)</t>
-  </si>
-  <si>
-    <t>NG NEUGEBAUER HITS 200G BOMBOM SORTIDO</t>
-  </si>
-  <si>
-    <t>PINATI SLIM WHEY BRIGADEIRO 16X35G</t>
-  </si>
-  <si>
-    <t>PINATI DB WHEY FRAPE DE COCO 12X50G</t>
-  </si>
-  <si>
-    <t>PACOCA GAMADINHO 100X15G</t>
-  </si>
-  <si>
-    <t>NG DOCE DE LEITE MUMU 350G</t>
-  </si>
-  <si>
-    <t>PINATI SWEET COCADINHA CHOCO 24X14G</t>
-  </si>
-  <si>
-    <t>PF MENTOS STICK 14 B. FRUTAS DP/16</t>
-  </si>
-  <si>
-    <t>VEUVE CLICQUOT BRUT 750 ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL CEREJA</t>
-  </si>
-  <si>
-    <t>RC ATUM SOLIDO NATURAL 24X170G</t>
-  </si>
-  <si>
-    <t>BALA HALLS CEREJA C/21 UND</t>
-  </si>
-  <si>
-    <t>BOM AR AERO 360 ML ALEGRIA</t>
-  </si>
-  <si>
-    <t>WHISKY JAMESON CASKMATES IPA 750ML</t>
-  </si>
-  <si>
-    <t>AZEITE DE OLIVA EV ESSENZA 5L</t>
-  </si>
-  <si>
-    <t>NG BIBS 720G AMENDOLATE (DP 18X40G)</t>
-  </si>
-  <si>
-    <t>BALA HALLS UVA VERDE C/21 UND</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MAX RASPEBERRY 14X16,5G</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MENTA C/ 14 UND</t>
-  </si>
-  <si>
-    <t>PINATI NUTS ORIGINAL 20X30G</t>
-  </si>
-  <si>
-    <t>ST PIERRE ZERO LATA GREEN APPLE 24X310ML</t>
-  </si>
-  <si>
-    <t>PF FRUTTELLA MAST.MOR.NAT DP/16</t>
-  </si>
-  <si>
-    <t>CHICLETE BUBBALOO TUTTI FRUTI C/60 UN</t>
-  </si>
-  <si>
-    <t>NATIKOS BARRA F. BANANA E AÇAI 12X30G</t>
-  </si>
-  <si>
-    <t>CACHACA JOIA DA SERRA TRADICIONAL 1L</t>
-  </si>
-  <si>
-    <t>INSETICIDA SBP 450 ML MULTI</t>
-  </si>
-  <si>
-    <t>INSETICIDA SBP 360 ML ULTRA BARREIRA</t>
-  </si>
-  <si>
-    <t>VINHO GRAVEDAD CARMENERE 750ML</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA BOMBOM 500G</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G BRANCO (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA BOMBOM BRANCO 500G</t>
-  </si>
-  <si>
-    <t>WHISKY BALLANTINE S FINEST 750ML</t>
-  </si>
-  <si>
-    <t>LICOR ESC DRAMBUIE 750 ML</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MAX MENTABERRY 14X16,5G</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G AO LEITE (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>BOM AR AERO 360 ML CHEIRO DE TALCO</t>
-  </si>
-  <si>
-    <t>BOM AR AERO 360 ML LIMAO SICILIANO</t>
-  </si>
-  <si>
-    <t>PINATI NUTS BANANA 20X30G</t>
-  </si>
-  <si>
-    <t>NAPOLITANO STICKS 16X29G</t>
-  </si>
-  <si>
-    <t>RANCHEIRO WAFER CHOCOLATE 78G</t>
-  </si>
-  <si>
-    <t>SMIRNOFF RED PET 1750 ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL SF POMELO 4X250ML</t>
-  </si>
-  <si>
-    <t>AGUA MINERAL MAMBA WATER C/ GAS 12X350ML</t>
-  </si>
-  <si>
-    <t>RED BULL SF NECTARINA 24X250ML</t>
-  </si>
-  <si>
-    <t>ST PIERRE VIDRO PINK LIMONADE LN 275X12</t>
-  </si>
-  <si>
-    <t>WHISKY J WALKER GREEN LABEL - 750ML</t>
-  </si>
-  <si>
-    <t>RED BULL SF MAÇA 24X250ML</t>
-  </si>
-  <si>
-    <t>GIN MARINA 750ML</t>
-  </si>
-  <si>
-    <t>VINHO TTO BERTOLI CHIANTI DOCG 750ML</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN ZERO LONG  24X330ML</t>
-  </si>
-  <si>
-    <t>WHISKY CHIVAS XV GOLD 700ML</t>
-  </si>
-  <si>
-    <t>FRISANTE MACAW TROPICAL MOSC. ROSE 750ML</t>
-  </si>
-  <si>
-    <t>FRISANTE MACAW TROPICAL MOSCATO 750ML</t>
-  </si>
-  <si>
-    <t>ESPUMANTE ARESTI CHARDONNAY 187,5ML</t>
-  </si>
-  <si>
-    <t>WHISKY J WALKER GOLD LABEL RESERVE 750ML</t>
-  </si>
-  <si>
-    <t>RED BULL SF POMELO 24X250ML</t>
-  </si>
-  <si>
-    <t>NOSSO CHOP RED DRAFT VD 6X600ML</t>
-  </si>
-  <si>
-    <t>VINHO ARESTI ESTATE S. CHARDONNAY 187ML</t>
-  </si>
-  <si>
-    <t>VINHO ARESTI ESTATE S. CAB SAUV 187ML</t>
-  </si>
-  <si>
-    <t>VINHO FOODKILLER CARMENERE 750ML</t>
-  </si>
-  <si>
-    <t>VINHO ARESTI ESTATE S. CAB SAUV 750ML</t>
-  </si>
-  <si>
-    <t>WHISKY J WALKER BLUE LABEL 750 ML</t>
-  </si>
-  <si>
-    <t>VILLA ROSA COLHEITA BRANCO 750ML</t>
   </si>
   <si>
     <t>VODCA BAM CIROC RED BERRY 750 ML</t>
@@ -35925,7 +35925,7 @@
         <v>6252</v>
       </c>
       <c r="D463" t="s">
-        <v>7469</v>
+        <v>7468</v>
       </c>
       <c r="E463" t="s">
         <v>8030</v>
@@ -35945,7 +35945,7 @@
         <v>6253</v>
       </c>
       <c r="D464" t="s">
-        <v>7470</v>
+        <v>7469</v>
       </c>
       <c r="E464" t="s">
         <v>8030</v>
@@ -35965,7 +35965,7 @@
         <v>6225</v>
       </c>
       <c r="D465" t="s">
-        <v>7471</v>
+        <v>7406</v>
       </c>
       <c r="E465" t="s">
         <v>8030</v>
@@ -35988,7 +35988,7 @@
         <v>6254</v>
       </c>
       <c r="D466" t="s">
-        <v>7472</v>
+        <v>7470</v>
       </c>
       <c r="E466" t="s">
         <v>8030</v>
@@ -36008,7 +36008,7 @@
         <v>6122</v>
       </c>
       <c r="D467" t="s">
-        <v>7469</v>
+        <v>7471</v>
       </c>
       <c r="E467" t="s">
         <v>8030</v>
@@ -36048,7 +36048,7 @@
         <v>6092</v>
       </c>
       <c r="D469" t="s">
-        <v>7468</v>
+        <v>7471</v>
       </c>
       <c r="E469" t="s">
         <v>8030</v>
@@ -36088,7 +36088,7 @@
         <v>6256</v>
       </c>
       <c r="D471" t="s">
-        <v>7473</v>
+        <v>7472</v>
       </c>
       <c r="E471" t="s">
         <v>8030</v>
@@ -36131,7 +36131,7 @@
         <v>6018</v>
       </c>
       <c r="D473" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E473" t="s">
         <v>8031</v>
@@ -36154,7 +36154,7 @@
         <v>6258</v>
       </c>
       <c r="D474" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E474" t="s">
         <v>8031</v>
@@ -36177,7 +36177,7 @@
         <v>6259</v>
       </c>
       <c r="D475" t="s">
-        <v>7476</v>
+        <v>7475</v>
       </c>
       <c r="E475" t="s">
         <v>8031</v>
@@ -36200,7 +36200,7 @@
         <v>6260</v>
       </c>
       <c r="D476" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E476" t="s">
         <v>8032</v>
@@ -36240,7 +36240,7 @@
         <v>6262</v>
       </c>
       <c r="D478" t="s">
-        <v>7476</v>
+        <v>7475</v>
       </c>
       <c r="E478" t="s">
         <v>8032</v>
@@ -36440,7 +36440,7 @@
         <v>6270</v>
       </c>
       <c r="D488" t="s">
-        <v>7478</v>
+        <v>7477</v>
       </c>
       <c r="E488" t="s">
         <v>8032</v>
@@ -36760,7 +36760,7 @@
         <v>6084</v>
       </c>
       <c r="D504" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E504" t="s">
         <v>8032</v>
@@ -37040,7 +37040,7 @@
         <v>6295</v>
       </c>
       <c r="D518" t="s">
-        <v>7480</v>
+        <v>7479</v>
       </c>
       <c r="E518" t="s">
         <v>8033</v>
@@ -37083,7 +37083,7 @@
         <v>6297</v>
       </c>
       <c r="D520" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E520" t="s">
         <v>8034</v>
@@ -37303,7 +37303,7 @@
         <v>6084</v>
       </c>
       <c r="D531" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E531" t="s">
         <v>8034</v>
@@ -37343,7 +37343,7 @@
         <v>6303</v>
       </c>
       <c r="D533" t="s">
-        <v>7482</v>
+        <v>7481</v>
       </c>
       <c r="E533" t="s">
         <v>8034</v>
@@ -37363,7 +37363,7 @@
         <v>6306</v>
       </c>
       <c r="D534" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E534" t="s">
         <v>8034</v>
@@ -37486,7 +37486,7 @@
         <v>6082</v>
       </c>
       <c r="D540" t="s">
-        <v>7482</v>
+        <v>7481</v>
       </c>
       <c r="E540" t="s">
         <v>8036</v>
@@ -37666,7 +37666,7 @@
         <v>6318</v>
       </c>
       <c r="D549" t="s">
-        <v>7484</v>
+        <v>7483</v>
       </c>
       <c r="E549" t="s">
         <v>8036</v>
@@ -37706,7 +37706,7 @@
         <v>6320</v>
       </c>
       <c r="D551" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E551" t="s">
         <v>8036</v>
@@ -37726,7 +37726,7 @@
         <v>6321</v>
       </c>
       <c r="D552" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E552" t="s">
         <v>8036</v>
@@ -37846,7 +37846,7 @@
         <v>6326</v>
       </c>
       <c r="D558" t="s">
-        <v>7486</v>
+        <v>7485</v>
       </c>
       <c r="E558" t="s">
         <v>8036</v>
@@ -37906,7 +37906,7 @@
         <v>6329</v>
       </c>
       <c r="D561" t="s">
-        <v>7487</v>
+        <v>7486</v>
       </c>
       <c r="E561" t="s">
         <v>8036</v>
@@ -37946,7 +37946,7 @@
         <v>6330</v>
       </c>
       <c r="D563" t="s">
-        <v>7488</v>
+        <v>7487</v>
       </c>
       <c r="E563" t="s">
         <v>8036</v>
@@ -37986,7 +37986,7 @@
         <v>6331</v>
       </c>
       <c r="D565" t="s">
-        <v>7489</v>
+        <v>7488</v>
       </c>
       <c r="E565" t="s">
         <v>8036</v>
@@ -38086,7 +38086,7 @@
         <v>6335</v>
       </c>
       <c r="D570" t="s">
-        <v>7490</v>
+        <v>7489</v>
       </c>
       <c r="E570" t="s">
         <v>8037</v>
@@ -38106,7 +38106,7 @@
         <v>6336</v>
       </c>
       <c r="D571" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E571" t="s">
         <v>8037</v>
@@ -38146,7 +38146,7 @@
         <v>6338</v>
       </c>
       <c r="D573" t="s">
-        <v>7491</v>
+        <v>7490</v>
       </c>
       <c r="E573" t="s">
         <v>8037</v>
@@ -38232,7 +38232,7 @@
         <v>6032</v>
       </c>
       <c r="D577" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E577" t="s">
         <v>8039</v>
@@ -38252,7 +38252,7 @@
         <v>6032</v>
       </c>
       <c r="D578" t="s">
-        <v>7492</v>
+        <v>7491</v>
       </c>
       <c r="E578" t="s">
         <v>8039</v>
@@ -38338,7 +38338,7 @@
         <v>6257</v>
       </c>
       <c r="D582" t="s">
-        <v>7493</v>
+        <v>7492</v>
       </c>
       <c r="E582" t="s">
         <v>8039</v>
@@ -38358,7 +38358,7 @@
         <v>6341</v>
       </c>
       <c r="D583" t="s">
-        <v>7490</v>
+        <v>7489</v>
       </c>
       <c r="E583" t="s">
         <v>8039</v>
@@ -38381,7 +38381,7 @@
         <v>6342</v>
       </c>
       <c r="D584" t="s">
-        <v>7494</v>
+        <v>7493</v>
       </c>
       <c r="E584" t="s">
         <v>8039</v>
@@ -38427,7 +38427,7 @@
         <v>6114</v>
       </c>
       <c r="D586" t="s">
-        <v>7495</v>
+        <v>7494</v>
       </c>
       <c r="E586" t="s">
         <v>8039</v>
@@ -38447,7 +38447,7 @@
         <v>5995</v>
       </c>
       <c r="D587" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E587" t="s">
         <v>8039</v>
@@ -38553,7 +38553,7 @@
         <v>6002</v>
       </c>
       <c r="D592" t="s">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="E592" t="s">
         <v>8039</v>
@@ -38576,7 +38576,7 @@
         <v>6345</v>
       </c>
       <c r="D593" t="s">
-        <v>7495</v>
+        <v>7494</v>
       </c>
       <c r="E593" t="s">
         <v>8039</v>
@@ -38685,7 +38685,7 @@
         <v>6220</v>
       </c>
       <c r="D598" t="s">
-        <v>7497</v>
+        <v>7496</v>
       </c>
       <c r="E598" t="s">
         <v>8039</v>
@@ -38837,7 +38837,7 @@
         <v>6348</v>
       </c>
       <c r="D605" t="s">
-        <v>7498</v>
+        <v>7497</v>
       </c>
       <c r="E605" t="s">
         <v>8039</v>
@@ -39092,7 +39092,7 @@
         <v>6001</v>
       </c>
       <c r="D617" t="s">
-        <v>7499</v>
+        <v>7498</v>
       </c>
       <c r="E617" t="s">
         <v>8039</v>
@@ -39112,7 +39112,7 @@
         <v>6347</v>
       </c>
       <c r="D618" t="s">
-        <v>7500</v>
+        <v>7499</v>
       </c>
       <c r="E618" t="s">
         <v>8039</v>
@@ -39181,7 +39181,7 @@
         <v>6001</v>
       </c>
       <c r="D621" t="s">
-        <v>7501</v>
+        <v>7500</v>
       </c>
       <c r="E621" t="s">
         <v>8039</v>
@@ -39468,7 +39468,7 @@
         <v>6352</v>
       </c>
       <c r="D634" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E634" t="s">
         <v>8039</v>
@@ -39488,7 +39488,7 @@
         <v>6001</v>
       </c>
       <c r="D635" t="s">
-        <v>7502</v>
+        <v>7501</v>
       </c>
       <c r="E635" t="s">
         <v>8039</v>
@@ -39508,7 +39508,7 @@
         <v>6001</v>
       </c>
       <c r="D636" t="s">
-        <v>7503</v>
+        <v>7502</v>
       </c>
       <c r="E636" t="s">
         <v>8039</v>
@@ -39591,7 +39591,7 @@
         <v>6355</v>
       </c>
       <c r="D640" t="s">
-        <v>7504</v>
+        <v>7503</v>
       </c>
       <c r="E640" t="s">
         <v>8040</v>
@@ -39631,7 +39631,7 @@
         <v>6357</v>
       </c>
       <c r="D642" t="s">
-        <v>7505</v>
+        <v>7504</v>
       </c>
       <c r="E642" t="s">
         <v>8040</v>
@@ -39674,7 +39674,7 @@
         <v>6359</v>
       </c>
       <c r="D644" t="s">
-        <v>7506</v>
+        <v>7505</v>
       </c>
       <c r="E644" t="s">
         <v>8040</v>
@@ -39826,7 +39826,7 @@
         <v>6363</v>
       </c>
       <c r="D651" t="s">
-        <v>7507</v>
+        <v>7506</v>
       </c>
       <c r="E651" t="s">
         <v>8040</v>
@@ -39952,7 +39952,7 @@
         <v>6356</v>
       </c>
       <c r="D657" t="s">
-        <v>7508</v>
+        <v>7507</v>
       </c>
       <c r="E657" t="s">
         <v>8040</v>
@@ -40113,7 +40113,7 @@
         <v>6369</v>
       </c>
       <c r="D664" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E664" t="s">
         <v>8040</v>
@@ -40245,7 +40245,7 @@
         <v>6375</v>
       </c>
       <c r="D670" t="s">
-        <v>7507</v>
+        <v>7506</v>
       </c>
       <c r="E670" t="s">
         <v>8040</v>
@@ -40265,7 +40265,7 @@
         <v>6376</v>
       </c>
       <c r="D671" t="s">
-        <v>7510</v>
+        <v>7509</v>
       </c>
       <c r="E671" t="s">
         <v>8040</v>
@@ -40285,7 +40285,7 @@
         <v>6377</v>
       </c>
       <c r="D672" t="s">
-        <v>7511</v>
+        <v>7510</v>
       </c>
       <c r="E672" t="s">
         <v>8040</v>
@@ -40305,7 +40305,7 @@
         <v>6117</v>
       </c>
       <c r="D673" t="s">
-        <v>7512</v>
+        <v>7511</v>
       </c>
       <c r="E673" t="s">
         <v>8040</v>
@@ -40348,7 +40348,7 @@
         <v>6379</v>
       </c>
       <c r="D675" t="s">
-        <v>7513</v>
+        <v>7512</v>
       </c>
       <c r="E675" t="s">
         <v>8041</v>
@@ -40368,7 +40368,7 @@
         <v>6380</v>
       </c>
       <c r="D676" t="s">
-        <v>7514</v>
+        <v>7513</v>
       </c>
       <c r="E676" t="s">
         <v>8041</v>
@@ -40388,7 +40388,7 @@
         <v>6381</v>
       </c>
       <c r="D677" t="s">
-        <v>7515</v>
+        <v>7514</v>
       </c>
       <c r="E677" t="s">
         <v>8041</v>
@@ -40448,7 +40448,7 @@
         <v>6383</v>
       </c>
       <c r="D680" t="s">
-        <v>7516</v>
+        <v>7515</v>
       </c>
       <c r="E680" t="s">
         <v>8041</v>
@@ -40468,7 +40468,7 @@
         <v>6384</v>
       </c>
       <c r="D681" t="s">
-        <v>7517</v>
+        <v>7516</v>
       </c>
       <c r="E681" t="s">
         <v>8041</v>
@@ -40686,7 +40686,7 @@
         <v>6391</v>
       </c>
       <c r="D691" t="s">
-        <v>7518</v>
+        <v>7517</v>
       </c>
       <c r="E691" t="s">
         <v>8041</v>
@@ -40732,7 +40732,7 @@
         <v>6393</v>
       </c>
       <c r="D693" t="s">
-        <v>7519</v>
+        <v>7518</v>
       </c>
       <c r="E693" t="s">
         <v>8041</v>
@@ -40752,7 +40752,7 @@
         <v>6394</v>
       </c>
       <c r="D694" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E694" t="s">
         <v>8041</v>
@@ -40792,7 +40792,7 @@
         <v>6396</v>
       </c>
       <c r="D696" t="s">
-        <v>7520</v>
+        <v>7519</v>
       </c>
       <c r="E696" t="s">
         <v>8041</v>
@@ -40812,7 +40812,7 @@
         <v>6397</v>
       </c>
       <c r="D697" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E697" t="s">
         <v>8041</v>
@@ -40832,7 +40832,7 @@
         <v>6398</v>
       </c>
       <c r="D698" t="s">
-        <v>7522</v>
+        <v>7521</v>
       </c>
       <c r="E698" t="s">
         <v>8041</v>
@@ -40872,7 +40872,7 @@
         <v>6386</v>
       </c>
       <c r="D700" t="s">
-        <v>7523</v>
+        <v>7522</v>
       </c>
       <c r="E700" t="s">
         <v>8041</v>
@@ -40895,7 +40895,7 @@
         <v>6399</v>
       </c>
       <c r="D701" t="s">
-        <v>7524</v>
+        <v>7523</v>
       </c>
       <c r="E701" t="s">
         <v>8041</v>
@@ -41056,7 +41056,7 @@
         <v>6405</v>
       </c>
       <c r="D708" t="s">
-        <v>7525</v>
+        <v>7524</v>
       </c>
       <c r="E708" t="s">
         <v>8041</v>
@@ -41125,7 +41125,7 @@
         <v>6408</v>
       </c>
       <c r="D711" t="s">
-        <v>7526</v>
+        <v>7525</v>
       </c>
       <c r="E711" t="s">
         <v>8041</v>
@@ -41145,7 +41145,7 @@
         <v>6409</v>
       </c>
       <c r="D712" t="s">
-        <v>7527</v>
+        <v>7526</v>
       </c>
       <c r="E712" t="s">
         <v>8041</v>
@@ -41165,7 +41165,7 @@
         <v>6410</v>
       </c>
       <c r="D713" t="s">
-        <v>7528</v>
+        <v>7527</v>
       </c>
       <c r="E713" t="s">
         <v>8041</v>
@@ -41185,7 +41185,7 @@
         <v>6411</v>
       </c>
       <c r="D714" t="s">
-        <v>7529</v>
+        <v>7528</v>
       </c>
       <c r="E714" t="s">
         <v>8041</v>
@@ -41205,7 +41205,7 @@
         <v>6392</v>
       </c>
       <c r="D715" t="s">
-        <v>7523</v>
+        <v>7522</v>
       </c>
       <c r="E715" t="s">
         <v>8041</v>
@@ -41228,7 +41228,7 @@
         <v>6412</v>
       </c>
       <c r="D716" t="s">
-        <v>7530</v>
+        <v>7529</v>
       </c>
       <c r="E716" t="s">
         <v>8041</v>
@@ -41271,7 +41271,7 @@
         <v>6414</v>
       </c>
       <c r="D718" t="s">
-        <v>7514</v>
+        <v>7513</v>
       </c>
       <c r="E718" t="s">
         <v>8041</v>
@@ -41452,7 +41452,7 @@
         <v>6421</v>
       </c>
       <c r="D726" t="s">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="E726" t="s">
         <v>8041</v>
@@ -41541,7 +41541,7 @@
         <v>6423</v>
       </c>
       <c r="D730" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E730" t="s">
         <v>8041</v>
@@ -41564,7 +41564,7 @@
         <v>6415</v>
       </c>
       <c r="D731" t="s">
-        <v>7532</v>
+        <v>7531</v>
       </c>
       <c r="E731" t="s">
         <v>8041</v>
@@ -41584,7 +41584,7 @@
         <v>6424</v>
       </c>
       <c r="D732" t="s">
-        <v>7533</v>
+        <v>7532</v>
       </c>
       <c r="E732" t="s">
         <v>8041</v>
@@ -41607,7 +41607,7 @@
         <v>6379</v>
       </c>
       <c r="D733" t="s">
-        <v>7534</v>
+        <v>7533</v>
       </c>
       <c r="E733" t="s">
         <v>8041</v>
@@ -41630,7 +41630,7 @@
         <v>6425</v>
       </c>
       <c r="D734" t="s">
-        <v>7535</v>
+        <v>7534</v>
       </c>
       <c r="E734" t="s">
         <v>8041</v>
@@ -41650,7 +41650,7 @@
         <v>6379</v>
       </c>
       <c r="D735" t="s">
-        <v>7535</v>
+        <v>7534</v>
       </c>
       <c r="E735" t="s">
         <v>8041</v>
@@ -41670,7 +41670,7 @@
         <v>6426</v>
       </c>
       <c r="D736" t="s">
-        <v>7536</v>
+        <v>7535</v>
       </c>
       <c r="E736" t="s">
         <v>8041</v>
@@ -41716,7 +41716,7 @@
         <v>6402</v>
       </c>
       <c r="D738" t="s">
-        <v>7524</v>
+        <v>7523</v>
       </c>
       <c r="E738" t="s">
         <v>8041</v>
@@ -41739,7 +41739,7 @@
         <v>6295</v>
       </c>
       <c r="D739" t="s">
-        <v>7524</v>
+        <v>7523</v>
       </c>
       <c r="E739" t="s">
         <v>8041</v>
@@ -41762,7 +41762,7 @@
         <v>6428</v>
       </c>
       <c r="D740" t="s">
-        <v>7524</v>
+        <v>7523</v>
       </c>
       <c r="E740" t="s">
         <v>8041</v>
@@ -41808,7 +41808,7 @@
         <v>6429</v>
       </c>
       <c r="D742" t="s">
-        <v>7537</v>
+        <v>7536</v>
       </c>
       <c r="E742" t="s">
         <v>8041</v>
@@ -41848,7 +41848,7 @@
         <v>6084</v>
       </c>
       <c r="D744" t="s">
-        <v>7538</v>
+        <v>7537</v>
       </c>
       <c r="E744" t="s">
         <v>8042</v>
@@ -41888,7 +41888,7 @@
         <v>6430</v>
       </c>
       <c r="D746" t="s">
-        <v>7538</v>
+        <v>7537</v>
       </c>
       <c r="E746" t="s">
         <v>8042</v>
@@ -41928,7 +41928,7 @@
         <v>6432</v>
       </c>
       <c r="D748" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E748" t="s">
         <v>8044</v>
@@ -41951,7 +41951,7 @@
         <v>6410</v>
       </c>
       <c r="D749" t="s">
-        <v>7539</v>
+        <v>7538</v>
       </c>
       <c r="E749" t="s">
         <v>8044</v>
@@ -41971,7 +41971,7 @@
         <v>6433</v>
       </c>
       <c r="D750" t="s">
-        <v>7540</v>
+        <v>7539</v>
       </c>
       <c r="E750" t="s">
         <v>8045</v>
@@ -41994,7 +41994,7 @@
         <v>6434</v>
       </c>
       <c r="D751" t="s">
-        <v>7541</v>
+        <v>7540</v>
       </c>
       <c r="E751" t="s">
         <v>8045</v>
@@ -42132,7 +42132,7 @@
         <v>6439</v>
       </c>
       <c r="D757" t="s">
-        <v>7542</v>
+        <v>7541</v>
       </c>
       <c r="E757" t="s">
         <v>8045</v>
@@ -42178,7 +42178,7 @@
         <v>6440</v>
       </c>
       <c r="D759" t="s">
-        <v>7543</v>
+        <v>7542</v>
       </c>
       <c r="E759" t="s">
         <v>8045</v>
@@ -42201,7 +42201,7 @@
         <v>6265</v>
       </c>
       <c r="D760" t="s">
-        <v>7542</v>
+        <v>7541</v>
       </c>
       <c r="E760" t="s">
         <v>8045</v>
@@ -42247,7 +42247,7 @@
         <v>6415</v>
       </c>
       <c r="D762" t="s">
-        <v>7544</v>
+        <v>7543</v>
       </c>
       <c r="E762" t="s">
         <v>8046</v>
@@ -42270,7 +42270,7 @@
         <v>6442</v>
       </c>
       <c r="D763" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E763" t="s">
         <v>8046</v>
@@ -42293,7 +42293,7 @@
         <v>6443</v>
       </c>
       <c r="D764" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E764" t="s">
         <v>8046</v>
@@ -42313,7 +42313,7 @@
         <v>6444</v>
       </c>
       <c r="D765" t="s">
-        <v>7546</v>
+        <v>7545</v>
       </c>
       <c r="E765" t="s">
         <v>8046</v>
@@ -42356,7 +42356,7 @@
         <v>6410</v>
       </c>
       <c r="D767" t="s">
-        <v>7546</v>
+        <v>7545</v>
       </c>
       <c r="E767" t="s">
         <v>8046</v>
@@ -42376,7 +42376,7 @@
         <v>6446</v>
       </c>
       <c r="D768" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E768" t="s">
         <v>8046</v>
@@ -42399,7 +42399,7 @@
         <v>6101</v>
       </c>
       <c r="D769" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E769" t="s">
         <v>8046</v>
@@ -42422,7 +42422,7 @@
         <v>6447</v>
       </c>
       <c r="D770" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E770" t="s">
         <v>8046</v>
@@ -42442,7 +42442,7 @@
         <v>6017</v>
       </c>
       <c r="D771" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E771" t="s">
         <v>8046</v>
@@ -42462,7 +42462,7 @@
         <v>6099</v>
       </c>
       <c r="D772" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E772" t="s">
         <v>8046</v>
@@ -42482,7 +42482,7 @@
         <v>6448</v>
       </c>
       <c r="D773" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E773" t="s">
         <v>8046</v>
@@ -42545,7 +42545,7 @@
         <v>6099</v>
       </c>
       <c r="D776" t="s">
-        <v>7544</v>
+        <v>7543</v>
       </c>
       <c r="E776" t="s">
         <v>8046</v>
@@ -42568,7 +42568,7 @@
         <v>6450</v>
       </c>
       <c r="D777" t="s">
-        <v>7544</v>
+        <v>7543</v>
       </c>
       <c r="E777" t="s">
         <v>8046</v>
@@ -42697,7 +42697,7 @@
         <v>6453</v>
       </c>
       <c r="D783" t="s">
-        <v>7547</v>
+        <v>7546</v>
       </c>
       <c r="E783" t="s">
         <v>8046</v>
@@ -42737,7 +42737,7 @@
         <v>6103</v>
       </c>
       <c r="D785" t="s">
-        <v>7548</v>
+        <v>7547</v>
       </c>
       <c r="E785" t="s">
         <v>8046</v>
@@ -42797,7 +42797,7 @@
         <v>6455</v>
       </c>
       <c r="D788" t="s">
-        <v>7549</v>
+        <v>7548</v>
       </c>
       <c r="E788" t="s">
         <v>8046</v>
@@ -42817,7 +42817,7 @@
         <v>6456</v>
       </c>
       <c r="D789" t="s">
-        <v>7550</v>
+        <v>7549</v>
       </c>
       <c r="E789" t="s">
         <v>8046</v>
@@ -42837,7 +42837,7 @@
         <v>6457</v>
       </c>
       <c r="D790" t="s">
-        <v>7550</v>
+        <v>7549</v>
       </c>
       <c r="E790" t="s">
         <v>8046</v>
@@ -42857,7 +42857,7 @@
         <v>6443</v>
       </c>
       <c r="D791" t="s">
-        <v>7550</v>
+        <v>7549</v>
       </c>
       <c r="E791" t="s">
         <v>8046</v>
@@ -42877,7 +42877,7 @@
         <v>6101</v>
       </c>
       <c r="D792" t="s">
-        <v>7550</v>
+        <v>7549</v>
       </c>
       <c r="E792" t="s">
         <v>8046</v>
@@ -42897,7 +42897,7 @@
         <v>6458</v>
       </c>
       <c r="D793" t="s">
-        <v>7550</v>
+        <v>7549</v>
       </c>
       <c r="E793" t="s">
         <v>8046</v>
@@ -43120,7 +43120,7 @@
         <v>6462</v>
       </c>
       <c r="D804" t="s">
-        <v>7547</v>
+        <v>7546</v>
       </c>
       <c r="E804" t="s">
         <v>8046</v>
@@ -43180,7 +43180,7 @@
         <v>6467</v>
       </c>
       <c r="D807" t="s">
-        <v>7551</v>
+        <v>7550</v>
       </c>
       <c r="E807" t="s">
         <v>8046</v>
@@ -43260,7 +43260,7 @@
         <v>6101</v>
       </c>
       <c r="D811" t="s">
-        <v>7552</v>
+        <v>7551</v>
       </c>
       <c r="E811" t="s">
         <v>8046</v>
@@ -43280,7 +43280,7 @@
         <v>6468</v>
       </c>
       <c r="D812" t="s">
-        <v>7552</v>
+        <v>7551</v>
       </c>
       <c r="E812" t="s">
         <v>8046</v>
@@ -43300,7 +43300,7 @@
         <v>6380</v>
       </c>
       <c r="D813" t="s">
-        <v>7553</v>
+        <v>7552</v>
       </c>
       <c r="E813" t="s">
         <v>8046</v>
@@ -43340,7 +43340,7 @@
         <v>6470</v>
       </c>
       <c r="D815" t="s">
-        <v>7554</v>
+        <v>7553</v>
       </c>
       <c r="E815" t="s">
         <v>8046</v>
@@ -43360,7 +43360,7 @@
         <v>6417</v>
       </c>
       <c r="D816" t="s">
-        <v>7552</v>
+        <v>7551</v>
       </c>
       <c r="E816" t="s">
         <v>8046</v>
@@ -43380,7 +43380,7 @@
         <v>6454</v>
       </c>
       <c r="D817" t="s">
-        <v>7552</v>
+        <v>7551</v>
       </c>
       <c r="E817" t="s">
         <v>8046</v>
@@ -43400,7 +43400,7 @@
         <v>6084</v>
       </c>
       <c r="D818" t="s">
-        <v>7555</v>
+        <v>7554</v>
       </c>
       <c r="E818" t="s">
         <v>8047</v>
@@ -43420,7 +43420,7 @@
         <v>6211</v>
       </c>
       <c r="D819" t="s">
-        <v>7556</v>
+        <v>7555</v>
       </c>
       <c r="E819" t="s">
         <v>8047</v>
@@ -43440,7 +43440,7 @@
         <v>6471</v>
       </c>
       <c r="D820" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E820" t="s">
         <v>8047</v>
@@ -43583,7 +43583,7 @@
         <v>6474</v>
       </c>
       <c r="D827" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E827" t="s">
         <v>8047</v>
@@ -43989,7 +43989,7 @@
         <v>6018</v>
       </c>
       <c r="D847" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E847" t="s">
         <v>8047</v>
@@ -44089,7 +44089,7 @@
         <v>6478</v>
       </c>
       <c r="D852" t="s">
-        <v>7559</v>
+        <v>7558</v>
       </c>
       <c r="E852" t="s">
         <v>8047</v>
@@ -44132,7 +44132,7 @@
         <v>6479</v>
       </c>
       <c r="D854" t="s">
-        <v>7560</v>
+        <v>7559</v>
       </c>
       <c r="E854" t="s">
         <v>8047</v>
@@ -44267,7 +44267,7 @@
         <v>6481</v>
       </c>
       <c r="D860" t="s">
-        <v>7561</v>
+        <v>7560</v>
       </c>
       <c r="E860" t="s">
         <v>8049</v>
@@ -44310,7 +44310,7 @@
         <v>6482</v>
       </c>
       <c r="D862" t="s">
-        <v>7562</v>
+        <v>7561</v>
       </c>
       <c r="E862" t="s">
         <v>8050</v>
@@ -44333,7 +44333,7 @@
         <v>6483</v>
       </c>
       <c r="D863" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E863" t="s">
         <v>8051</v>
@@ -44433,7 +44433,7 @@
         <v>6487</v>
       </c>
       <c r="D868" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E868" t="s">
         <v>8051</v>
@@ -44513,7 +44513,7 @@
         <v>6491</v>
       </c>
       <c r="D872" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E872" t="s">
         <v>8051</v>
@@ -44633,7 +44633,7 @@
         <v>6496</v>
       </c>
       <c r="D878" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E878" t="s">
         <v>8052</v>
@@ -44653,7 +44653,7 @@
         <v>6497</v>
       </c>
       <c r="D879" t="s">
-        <v>7563</v>
+        <v>7562</v>
       </c>
       <c r="E879" t="s">
         <v>8052</v>
@@ -44693,7 +44693,7 @@
         <v>6051</v>
       </c>
       <c r="D881" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E881" t="s">
         <v>8052</v>
@@ -44713,7 +44713,7 @@
         <v>6084</v>
       </c>
       <c r="D882" t="s">
-        <v>7530</v>
+        <v>7529</v>
       </c>
       <c r="E882" t="s">
         <v>8053</v>
@@ -44733,7 +44733,7 @@
         <v>6499</v>
       </c>
       <c r="D883" t="s">
-        <v>7526</v>
+        <v>7525</v>
       </c>
       <c r="E883" t="s">
         <v>8053</v>
@@ -44753,7 +44753,7 @@
         <v>6084</v>
       </c>
       <c r="D884" t="s">
-        <v>7526</v>
+        <v>7525</v>
       </c>
       <c r="E884" t="s">
         <v>8053</v>
@@ -44773,7 +44773,7 @@
         <v>6084</v>
       </c>
       <c r="D885" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E885" t="s">
         <v>8053</v>
@@ -44796,7 +44796,7 @@
         <v>6084</v>
       </c>
       <c r="D886" t="s">
-        <v>7535</v>
+        <v>7534</v>
       </c>
       <c r="E886" t="s">
         <v>8053</v>
@@ -44836,7 +44836,7 @@
         <v>6084</v>
       </c>
       <c r="D888" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E888" t="s">
         <v>8053</v>
@@ -44859,7 +44859,7 @@
         <v>6501</v>
       </c>
       <c r="D889" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E889" t="s">
         <v>8053</v>
@@ -44879,7 +44879,7 @@
         <v>6502</v>
       </c>
       <c r="D890" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E890" t="s">
         <v>8053</v>
@@ -44942,7 +44942,7 @@
         <v>6505</v>
       </c>
       <c r="D893" t="s">
-        <v>7529</v>
+        <v>7528</v>
       </c>
       <c r="E893" t="s">
         <v>8053</v>
@@ -44962,7 +44962,7 @@
         <v>6084</v>
       </c>
       <c r="D894" t="s">
-        <v>7567</v>
+        <v>7566</v>
       </c>
       <c r="E894" t="s">
         <v>8053</v>
@@ -44985,7 +44985,7 @@
         <v>6506</v>
       </c>
       <c r="D895" t="s">
-        <v>7568</v>
+        <v>7567</v>
       </c>
       <c r="E895" t="s">
         <v>8053</v>
@@ -45008,7 +45008,7 @@
         <v>6507</v>
       </c>
       <c r="D896" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E896" t="s">
         <v>8053</v>
@@ -45074,7 +45074,7 @@
         <v>6509</v>
       </c>
       <c r="D899" t="s">
-        <v>7570</v>
+        <v>7569</v>
       </c>
       <c r="E899" t="s">
         <v>8053</v>
@@ -45094,7 +45094,7 @@
         <v>6510</v>
       </c>
       <c r="D900" t="s">
-        <v>7571</v>
+        <v>7570</v>
       </c>
       <c r="E900" t="s">
         <v>8053</v>
@@ -45114,7 +45114,7 @@
         <v>6505</v>
       </c>
       <c r="D901" t="s">
-        <v>7572</v>
+        <v>7571</v>
       </c>
       <c r="E901" t="s">
         <v>8053</v>
@@ -45137,7 +45137,7 @@
         <v>6511</v>
       </c>
       <c r="D902" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E902" t="s">
         <v>8053</v>
@@ -45157,7 +45157,7 @@
         <v>6084</v>
       </c>
       <c r="D903" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E903" t="s">
         <v>8053</v>
@@ -45200,7 +45200,7 @@
         <v>6084</v>
       </c>
       <c r="D905" t="s">
-        <v>7533</v>
+        <v>7532</v>
       </c>
       <c r="E905" t="s">
         <v>8053</v>
@@ -45220,7 +45220,7 @@
         <v>6084</v>
       </c>
       <c r="D906" t="s">
-        <v>7574</v>
+        <v>7573</v>
       </c>
       <c r="E906" t="s">
         <v>8053</v>
@@ -45243,7 +45243,7 @@
         <v>6513</v>
       </c>
       <c r="D907" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E907" t="s">
         <v>8053</v>
@@ -45263,7 +45263,7 @@
         <v>6506</v>
       </c>
       <c r="D908" t="s">
-        <v>7576</v>
+        <v>7575</v>
       </c>
       <c r="E908" t="s">
         <v>8053</v>
@@ -45306,7 +45306,7 @@
         <v>6499</v>
       </c>
       <c r="D910" t="s">
-        <v>7526</v>
+        <v>7525</v>
       </c>
       <c r="E910" t="s">
         <v>8053</v>
@@ -45326,7 +45326,7 @@
         <v>6383</v>
       </c>
       <c r="D911" t="s">
-        <v>7577</v>
+        <v>7576</v>
       </c>
       <c r="E911" t="s">
         <v>8053</v>
@@ -45395,7 +45395,7 @@
         <v>6515</v>
       </c>
       <c r="D914" t="s">
-        <v>7578</v>
+        <v>7577</v>
       </c>
       <c r="E914" t="s">
         <v>8053</v>
@@ -45415,7 +45415,7 @@
         <v>6213</v>
       </c>
       <c r="D915" t="s">
-        <v>7571</v>
+        <v>7570</v>
       </c>
       <c r="E915" t="s">
         <v>8053</v>
@@ -45478,7 +45478,7 @@
         <v>6084</v>
       </c>
       <c r="D918" t="s">
-        <v>7579</v>
+        <v>7578</v>
       </c>
       <c r="E918" t="s">
         <v>8053</v>
@@ -45547,7 +45547,7 @@
         <v>6517</v>
       </c>
       <c r="D921" t="s">
-        <v>7514</v>
+        <v>7513</v>
       </c>
       <c r="E921" t="s">
         <v>8053</v>
@@ -45570,7 +45570,7 @@
         <v>6518</v>
       </c>
       <c r="D922" t="s">
-        <v>7580</v>
+        <v>7579</v>
       </c>
       <c r="E922" t="s">
         <v>8053</v>
@@ -45590,7 +45590,7 @@
         <v>6084</v>
       </c>
       <c r="D923" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E923" t="s">
         <v>8053</v>
@@ -45636,7 +45636,7 @@
         <v>6519</v>
       </c>
       <c r="D925" t="s">
-        <v>7582</v>
+        <v>7581</v>
       </c>
       <c r="E925" t="s">
         <v>8053</v>
@@ -45656,7 +45656,7 @@
         <v>6520</v>
       </c>
       <c r="D926" t="s">
-        <v>7571</v>
+        <v>7570</v>
       </c>
       <c r="E926" t="s">
         <v>8053</v>
@@ -45679,7 +45679,7 @@
         <v>6213</v>
       </c>
       <c r="D927" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E927" t="s">
         <v>8053</v>
@@ -45699,7 +45699,7 @@
         <v>6505</v>
       </c>
       <c r="D928" t="s">
-        <v>7572</v>
+        <v>7571</v>
       </c>
       <c r="E928" t="s">
         <v>8053</v>
@@ -45739,7 +45739,7 @@
         <v>6505</v>
       </c>
       <c r="D930" t="s">
-        <v>7583</v>
+        <v>7582</v>
       </c>
       <c r="E930" t="s">
         <v>8053</v>
@@ -45779,7 +45779,7 @@
         <v>6523</v>
       </c>
       <c r="D932" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E932" t="s">
         <v>8053</v>
@@ -45822,7 +45822,7 @@
         <v>6525</v>
       </c>
       <c r="D934" t="s">
-        <v>7529</v>
+        <v>7528</v>
       </c>
       <c r="E934" t="s">
         <v>8053</v>
@@ -45842,7 +45842,7 @@
         <v>6084</v>
       </c>
       <c r="D935" t="s">
-        <v>7584</v>
+        <v>7583</v>
       </c>
       <c r="E935" t="s">
         <v>8053</v>
@@ -45862,7 +45862,7 @@
         <v>6084</v>
       </c>
       <c r="D936" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E936" t="s">
         <v>8053</v>
@@ -45885,7 +45885,7 @@
         <v>6084</v>
       </c>
       <c r="D937" t="s">
-        <v>7513</v>
+        <v>7512</v>
       </c>
       <c r="E937" t="s">
         <v>8053</v>
@@ -45925,7 +45925,7 @@
         <v>6084</v>
       </c>
       <c r="D939" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E939" t="s">
         <v>8053</v>
@@ -45965,7 +45965,7 @@
         <v>6084</v>
       </c>
       <c r="D941" t="s">
-        <v>7585</v>
+        <v>7584</v>
       </c>
       <c r="E941" t="s">
         <v>8053</v>
@@ -45988,7 +45988,7 @@
         <v>6084</v>
       </c>
       <c r="D942" t="s">
-        <v>7529</v>
+        <v>7528</v>
       </c>
       <c r="E942" t="s">
         <v>8053</v>
@@ -46008,7 +46008,7 @@
         <v>6502</v>
       </c>
       <c r="D943" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E943" t="s">
         <v>8053</v>
@@ -46028,7 +46028,7 @@
         <v>6084</v>
       </c>
       <c r="D944" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E944" t="s">
         <v>8053</v>
@@ -46048,7 +46048,7 @@
         <v>6084</v>
       </c>
       <c r="D945" t="s">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="E945" t="s">
         <v>8053</v>
@@ -46068,7 +46068,7 @@
         <v>6527</v>
       </c>
       <c r="D946" t="s">
-        <v>7587</v>
+        <v>7586</v>
       </c>
       <c r="E946" t="s">
         <v>8053</v>
@@ -46114,7 +46114,7 @@
         <v>6084</v>
       </c>
       <c r="D948" t="s">
-        <v>7588</v>
+        <v>7587</v>
       </c>
       <c r="E948" t="s">
         <v>8053</v>
@@ -46134,7 +46134,7 @@
         <v>6084</v>
       </c>
       <c r="D949" t="s">
-        <v>7516</v>
+        <v>7515</v>
       </c>
       <c r="E949" t="s">
         <v>8053</v>
@@ -46154,7 +46154,7 @@
         <v>6084</v>
       </c>
       <c r="D950" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E950" t="s">
         <v>8053</v>
@@ -46194,7 +46194,7 @@
         <v>6084</v>
       </c>
       <c r="D952" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E952" t="s">
         <v>8053</v>
@@ -46214,7 +46214,7 @@
         <v>6517</v>
       </c>
       <c r="D953" t="s">
-        <v>7590</v>
+        <v>7589</v>
       </c>
       <c r="E953" t="s">
         <v>8053</v>
@@ -46237,7 +46237,7 @@
         <v>6505</v>
       </c>
       <c r="D954" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E954" t="s">
         <v>8053</v>
@@ -46257,7 +46257,7 @@
         <v>6502</v>
       </c>
       <c r="D955" t="s">
-        <v>7591</v>
+        <v>7590</v>
       </c>
       <c r="E955" t="s">
         <v>8053</v>
@@ -46300,7 +46300,7 @@
         <v>6529</v>
       </c>
       <c r="D957" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E957" t="s">
         <v>8053</v>
@@ -46323,7 +46323,7 @@
         <v>6530</v>
       </c>
       <c r="D958" t="s">
-        <v>7593</v>
+        <v>7592</v>
       </c>
       <c r="E958" t="s">
         <v>8053</v>
@@ -46346,7 +46346,7 @@
         <v>6084</v>
       </c>
       <c r="D959" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E959" t="s">
         <v>8053</v>
@@ -46389,7 +46389,7 @@
         <v>6084</v>
       </c>
       <c r="D961" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E961" t="s">
         <v>8053</v>
@@ -46432,7 +46432,7 @@
         <v>6519</v>
       </c>
       <c r="D963" t="s">
-        <v>7523</v>
+        <v>7522</v>
       </c>
       <c r="E963" t="s">
         <v>8053</v>
@@ -46495,7 +46495,7 @@
         <v>6084</v>
       </c>
       <c r="D966" t="s">
-        <v>7513</v>
+        <v>7512</v>
       </c>
       <c r="E966" t="s">
         <v>8053</v>
@@ -46515,7 +46515,7 @@
         <v>6504</v>
       </c>
       <c r="D967" t="s">
-        <v>7514</v>
+        <v>7513</v>
       </c>
       <c r="E967" t="s">
         <v>8053</v>
@@ -46638,7 +46638,7 @@
         <v>6084</v>
       </c>
       <c r="D973" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E973" t="s">
         <v>8053</v>
@@ -46658,7 +46658,7 @@
         <v>6084</v>
       </c>
       <c r="D974" t="s">
-        <v>7515</v>
+        <v>7514</v>
       </c>
       <c r="E974" t="s">
         <v>8053</v>
@@ -46698,7 +46698,7 @@
         <v>6084</v>
       </c>
       <c r="D976" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E976" t="s">
         <v>8053</v>
@@ -46721,7 +46721,7 @@
         <v>6535</v>
       </c>
       <c r="D977" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E977" t="s">
         <v>8053</v>
@@ -46741,7 +46741,7 @@
         <v>6536</v>
       </c>
       <c r="D978" t="s">
-        <v>7596</v>
+        <v>7595</v>
       </c>
       <c r="E978" t="s">
         <v>8053</v>
@@ -46804,7 +46804,7 @@
         <v>6084</v>
       </c>
       <c r="D981" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E981" t="s">
         <v>8053</v>
@@ -46850,7 +46850,7 @@
         <v>6084</v>
       </c>
       <c r="D983" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E983" t="s">
         <v>8053</v>
@@ -46893,7 +46893,7 @@
         <v>6502</v>
       </c>
       <c r="D985" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E985" t="s">
         <v>8053</v>
@@ -46913,7 +46913,7 @@
         <v>6084</v>
       </c>
       <c r="D986" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E986" t="s">
         <v>8053</v>
@@ -46933,7 +46933,7 @@
         <v>6511</v>
       </c>
       <c r="D987" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E987" t="s">
         <v>8053</v>
@@ -46993,7 +46993,7 @@
         <v>6504</v>
       </c>
       <c r="D990" t="s">
-        <v>7529</v>
+        <v>7528</v>
       </c>
       <c r="E990" t="s">
         <v>8053</v>
@@ -47056,7 +47056,7 @@
         <v>6213</v>
       </c>
       <c r="D993" t="s">
-        <v>7598</v>
+        <v>7597</v>
       </c>
       <c r="E993" t="s">
         <v>8053</v>
@@ -47145,7 +47145,7 @@
         <v>6526</v>
       </c>
       <c r="D997" t="s">
-        <v>7599</v>
+        <v>7598</v>
       </c>
       <c r="E997" t="s">
         <v>8053</v>
@@ -47165,7 +47165,7 @@
         <v>6542</v>
       </c>
       <c r="D998" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E998" t="s">
         <v>8053</v>
@@ -47268,7 +47268,7 @@
         <v>6507</v>
       </c>
       <c r="D1003" t="s">
-        <v>7601</v>
+        <v>7600</v>
       </c>
       <c r="E1003" t="s">
         <v>8053</v>
@@ -47291,7 +47291,7 @@
         <v>6084</v>
       </c>
       <c r="D1004" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E1004" t="s">
         <v>8053</v>
@@ -47314,7 +47314,7 @@
         <v>6543</v>
       </c>
       <c r="D1005" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1005" t="s">
         <v>8053</v>
@@ -47337,7 +47337,7 @@
         <v>6544</v>
       </c>
       <c r="D1006" t="s">
-        <v>7603</v>
+        <v>7602</v>
       </c>
       <c r="E1006" t="s">
         <v>8053</v>
@@ -47360,7 +47360,7 @@
         <v>6214</v>
       </c>
       <c r="D1007" t="s">
-        <v>7593</v>
+        <v>7592</v>
       </c>
       <c r="E1007" t="s">
         <v>8053</v>
@@ -47383,7 +47383,7 @@
         <v>6526</v>
       </c>
       <c r="D1008" t="s">
-        <v>7534</v>
+        <v>7533</v>
       </c>
       <c r="E1008" t="s">
         <v>8053</v>
@@ -47406,7 +47406,7 @@
         <v>6533</v>
       </c>
       <c r="D1009" t="s">
-        <v>7523</v>
+        <v>7522</v>
       </c>
       <c r="E1009" t="s">
         <v>8053</v>
@@ -47452,7 +47452,7 @@
         <v>6084</v>
       </c>
       <c r="D1011" t="s">
-        <v>7604</v>
+        <v>7603</v>
       </c>
       <c r="E1011" t="s">
         <v>8053</v>
@@ -47475,7 +47475,7 @@
         <v>6545</v>
       </c>
       <c r="D1012" t="s">
-        <v>7604</v>
+        <v>7603</v>
       </c>
       <c r="E1012" t="s">
         <v>8053</v>
@@ -47498,7 +47498,7 @@
         <v>6066</v>
       </c>
       <c r="D1013" t="s">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="E1013" t="s">
         <v>8053</v>
@@ -47521,7 +47521,7 @@
         <v>6546</v>
       </c>
       <c r="D1014" t="s">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="E1014" t="s">
         <v>8053</v>
@@ -47544,7 +47544,7 @@
         <v>6084</v>
       </c>
       <c r="D1015" t="s">
-        <v>7579</v>
+        <v>7578</v>
       </c>
       <c r="E1015" t="s">
         <v>8053</v>
@@ -47567,7 +47567,7 @@
         <v>6084</v>
       </c>
       <c r="D1016" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E1016" t="s">
         <v>8053</v>
@@ -47590,7 +47590,7 @@
         <v>6202</v>
       </c>
       <c r="D1017" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E1017" t="s">
         <v>8053</v>
@@ -47630,7 +47630,7 @@
         <v>6542</v>
       </c>
       <c r="D1019" t="s">
-        <v>7596</v>
+        <v>7595</v>
       </c>
       <c r="E1019" t="s">
         <v>8053</v>
@@ -47693,7 +47693,7 @@
         <v>6502</v>
       </c>
       <c r="D1022" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E1022" t="s">
         <v>8053</v>
@@ -47733,7 +47733,7 @@
         <v>6084</v>
       </c>
       <c r="D1024" t="s">
-        <v>7513</v>
+        <v>7512</v>
       </c>
       <c r="E1024" t="s">
         <v>8053</v>
@@ -47773,7 +47773,7 @@
         <v>6084</v>
       </c>
       <c r="D1026" t="s">
-        <v>7606</v>
+        <v>7605</v>
       </c>
       <c r="E1026" t="s">
         <v>8053</v>
@@ -47793,7 +47793,7 @@
         <v>6478</v>
       </c>
       <c r="D1027" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E1027" t="s">
         <v>8053</v>
@@ -47813,7 +47813,7 @@
         <v>6001</v>
       </c>
       <c r="D1028" t="s">
-        <v>7607</v>
+        <v>7606</v>
       </c>
       <c r="E1028" t="s">
         <v>8054</v>
@@ -47882,7 +47882,7 @@
         <v>6547</v>
       </c>
       <c r="D1031" t="s">
-        <v>7608</v>
+        <v>7607</v>
       </c>
       <c r="E1031" t="s">
         <v>8055</v>
@@ -47928,7 +47928,7 @@
         <v>6257</v>
       </c>
       <c r="D1033" t="s">
-        <v>7609</v>
+        <v>7608</v>
       </c>
       <c r="E1033" t="s">
         <v>8055</v>
@@ -47971,7 +47971,7 @@
         <v>6548</v>
       </c>
       <c r="D1035" t="s">
-        <v>7610</v>
+        <v>7609</v>
       </c>
       <c r="E1035" t="s">
         <v>8055</v>
@@ -47994,7 +47994,7 @@
         <v>6549</v>
       </c>
       <c r="D1036" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E1036" t="s">
         <v>8055</v>
@@ -48057,7 +48057,7 @@
         <v>6348</v>
       </c>
       <c r="D1039" t="s">
-        <v>7494</v>
+        <v>7493</v>
       </c>
       <c r="E1039" t="s">
         <v>8055</v>
@@ -48143,7 +48143,7 @@
         <v>6464</v>
       </c>
       <c r="D1043" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E1043" t="s">
         <v>8055</v>
@@ -48166,7 +48166,7 @@
         <v>6553</v>
       </c>
       <c r="D1044" t="s">
-        <v>7609</v>
+        <v>7608</v>
       </c>
       <c r="E1044" t="s">
         <v>8055</v>
@@ -48186,7 +48186,7 @@
         <v>6554</v>
       </c>
       <c r="D1045" t="s">
-        <v>7613</v>
+        <v>7612</v>
       </c>
       <c r="E1045" t="s">
         <v>8055</v>
@@ -48209,7 +48209,7 @@
         <v>6553</v>
       </c>
       <c r="D1046" t="s">
-        <v>7607</v>
+        <v>7606</v>
       </c>
       <c r="E1046" t="s">
         <v>8055</v>
@@ -48255,7 +48255,7 @@
         <v>6556</v>
       </c>
       <c r="D1048" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1048" t="s">
         <v>8055</v>
@@ -48370,7 +48370,7 @@
         <v>6559</v>
       </c>
       <c r="D1053" t="s">
-        <v>7609</v>
+        <v>7608</v>
       </c>
       <c r="E1053" t="s">
         <v>8055</v>
@@ -48393,7 +48393,7 @@
         <v>6560</v>
       </c>
       <c r="D1054" t="s">
-        <v>7506</v>
+        <v>7505</v>
       </c>
       <c r="E1054" t="s">
         <v>8055</v>
@@ -48416,7 +48416,7 @@
         <v>6561</v>
       </c>
       <c r="D1055" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E1055" t="s">
         <v>8055</v>
@@ -48439,7 +48439,7 @@
         <v>6478</v>
       </c>
       <c r="D1056" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E1056" t="s">
         <v>8055</v>
@@ -48459,7 +48459,7 @@
         <v>6419</v>
       </c>
       <c r="D1057" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1057" t="s">
         <v>8055</v>
@@ -48528,7 +48528,7 @@
         <v>6214</v>
       </c>
       <c r="D1060" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1060" t="s">
         <v>8055</v>
@@ -48551,7 +48551,7 @@
         <v>6563</v>
       </c>
       <c r="D1061" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1061" t="s">
         <v>8055</v>
@@ -48597,7 +48597,7 @@
         <v>6084</v>
       </c>
       <c r="D1063" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1063" t="s">
         <v>8055</v>
@@ -48666,7 +48666,7 @@
         <v>6478</v>
       </c>
       <c r="D1066" t="s">
-        <v>7618</v>
+        <v>7617</v>
       </c>
       <c r="E1066" t="s">
         <v>8055</v>
@@ -48689,7 +48689,7 @@
         <v>6108</v>
       </c>
       <c r="D1067" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E1067" t="s">
         <v>8055</v>
@@ -48735,7 +48735,7 @@
         <v>6565</v>
       </c>
       <c r="D1069" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E1069" t="s">
         <v>8055</v>
@@ -48758,7 +48758,7 @@
         <v>6566</v>
       </c>
       <c r="D1070" t="s">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="E1070" t="s">
         <v>8055</v>
@@ -48824,7 +48824,7 @@
         <v>6553</v>
       </c>
       <c r="D1073" t="s">
-        <v>7620</v>
+        <v>7619</v>
       </c>
       <c r="E1073" t="s">
         <v>8055</v>
@@ -48847,7 +48847,7 @@
         <v>6568</v>
       </c>
       <c r="D1074" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E1074" t="s">
         <v>8055</v>
@@ -48893,7 +48893,7 @@
         <v>6347</v>
       </c>
       <c r="D1076" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E1076" t="s">
         <v>8055</v>
@@ -48933,7 +48933,7 @@
         <v>6032</v>
       </c>
       <c r="D1078" t="s">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="E1078" t="s">
         <v>8055</v>
@@ -48999,7 +48999,7 @@
         <v>6478</v>
       </c>
       <c r="D1081" t="s">
-        <v>7609</v>
+        <v>7608</v>
       </c>
       <c r="E1081" t="s">
         <v>8055</v>
@@ -49022,7 +49022,7 @@
         <v>6571</v>
       </c>
       <c r="D1082" t="s">
-        <v>7497</v>
+        <v>7496</v>
       </c>
       <c r="E1082" t="s">
         <v>8055</v>
@@ -49042,7 +49042,7 @@
         <v>6572</v>
       </c>
       <c r="D1083" t="s">
-        <v>7620</v>
+        <v>7619</v>
       </c>
       <c r="E1083" t="s">
         <v>8055</v>
@@ -49200,7 +49200,7 @@
         <v>6575</v>
       </c>
       <c r="D1090" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E1090" t="s">
         <v>8055</v>
@@ -49246,7 +49246,7 @@
         <v>6576</v>
       </c>
       <c r="D1092" t="s">
-        <v>7623</v>
+        <v>7622</v>
       </c>
       <c r="E1092" t="s">
         <v>8055</v>
@@ -49312,7 +49312,7 @@
         <v>6578</v>
       </c>
       <c r="D1095" t="s">
-        <v>7623</v>
+        <v>7622</v>
       </c>
       <c r="E1095" t="s">
         <v>8055</v>
@@ -49355,7 +49355,7 @@
         <v>6553</v>
       </c>
       <c r="D1097" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1097" t="s">
         <v>8055</v>
@@ -49398,7 +49398,7 @@
         <v>6568</v>
       </c>
       <c r="D1099" t="s">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="E1099" t="s">
         <v>8055</v>
@@ -49464,7 +49464,7 @@
         <v>6257</v>
       </c>
       <c r="D1102" t="s">
-        <v>7624</v>
+        <v>7623</v>
       </c>
       <c r="E1102" t="s">
         <v>8055</v>
@@ -49487,7 +49487,7 @@
         <v>6580</v>
       </c>
       <c r="D1103" t="s">
-        <v>7625</v>
+        <v>7624</v>
       </c>
       <c r="E1103" t="s">
         <v>8055</v>
@@ -49510,7 +49510,7 @@
         <v>6581</v>
       </c>
       <c r="D1104" t="s">
-        <v>7626</v>
+        <v>7625</v>
       </c>
       <c r="E1104" t="s">
         <v>8055</v>
@@ -49533,7 +49533,7 @@
         <v>6582</v>
       </c>
       <c r="D1105" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1105" t="s">
         <v>8055</v>
@@ -49579,7 +49579,7 @@
         <v>6028</v>
       </c>
       <c r="D1107" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E1107" t="s">
         <v>8055</v>
@@ -49602,7 +49602,7 @@
         <v>6584</v>
       </c>
       <c r="D1108" t="s">
-        <v>7627</v>
+        <v>7626</v>
       </c>
       <c r="E1108" t="s">
         <v>8055</v>
@@ -49694,7 +49694,7 @@
         <v>6586</v>
       </c>
       <c r="D1112" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E1112" t="s">
         <v>8055</v>
@@ -49714,7 +49714,7 @@
         <v>6553</v>
       </c>
       <c r="D1113" t="s">
-        <v>7628</v>
+        <v>7627</v>
       </c>
       <c r="E1113" t="s">
         <v>8055</v>
@@ -49760,7 +49760,7 @@
         <v>6587</v>
       </c>
       <c r="D1115" t="s">
-        <v>7629</v>
+        <v>7628</v>
       </c>
       <c r="E1115" t="s">
         <v>8055</v>
@@ -49783,7 +49783,7 @@
         <v>6215</v>
       </c>
       <c r="D1116" t="s">
-        <v>7506</v>
+        <v>7505</v>
       </c>
       <c r="E1116" t="s">
         <v>8055</v>
@@ -49806,7 +49806,7 @@
         <v>6561</v>
       </c>
       <c r="D1117" t="s">
-        <v>7471</v>
+        <v>7629</v>
       </c>
       <c r="E1117" t="s">
         <v>8055</v>
@@ -49944,7 +49944,7 @@
         <v>6567</v>
       </c>
       <c r="D1123" t="s">
-        <v>7471</v>
+        <v>7629</v>
       </c>
       <c r="E1123" t="s">
         <v>8055</v>
@@ -50059,7 +50059,7 @@
         <v>6568</v>
       </c>
       <c r="D1128" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E1128" t="s">
         <v>8055</v>
@@ -50082,7 +50082,7 @@
         <v>6559</v>
       </c>
       <c r="D1129" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E1129" t="s">
         <v>8055</v>
@@ -50496,7 +50496,7 @@
         <v>6028</v>
       </c>
       <c r="D1147" t="s">
-        <v>7490</v>
+        <v>7489</v>
       </c>
       <c r="E1147" t="s">
         <v>8058</v>
@@ -50795,7 +50795,7 @@
         <v>6257</v>
       </c>
       <c r="D1160" t="s">
-        <v>7494</v>
+        <v>7493</v>
       </c>
       <c r="E1160" t="s">
         <v>8058</v>
@@ -50933,7 +50933,7 @@
         <v>6597</v>
       </c>
       <c r="D1166" t="s">
-        <v>7494</v>
+        <v>7493</v>
       </c>
       <c r="E1166" t="s">
         <v>8058</v>
@@ -51002,7 +51002,7 @@
         <v>6257</v>
       </c>
       <c r="D1169" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1169" t="s">
         <v>8058</v>
@@ -51692,7 +51692,7 @@
         <v>6600</v>
       </c>
       <c r="D1199" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E1199" t="s">
         <v>8058</v>
@@ -51738,7 +51738,7 @@
         <v>6257</v>
       </c>
       <c r="D1201" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E1201" t="s">
         <v>8058</v>
@@ -52198,7 +52198,7 @@
         <v>6028</v>
       </c>
       <c r="D1221" t="s">
-        <v>7494</v>
+        <v>7493</v>
       </c>
       <c r="E1221" t="s">
         <v>8058</v>
@@ -52359,7 +52359,7 @@
         <v>6257</v>
       </c>
       <c r="D1228" t="s">
-        <v>7599</v>
+        <v>7598</v>
       </c>
       <c r="E1228" t="s">
         <v>8058</v>
@@ -52451,7 +52451,7 @@
         <v>6257</v>
       </c>
       <c r="D1232" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1232" t="s">
         <v>8058</v>
@@ -52520,7 +52520,7 @@
         <v>6257</v>
       </c>
       <c r="D1235" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E1235" t="s">
         <v>8058</v>
@@ -52589,7 +52589,7 @@
         <v>6257</v>
       </c>
       <c r="D1238" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1238" t="s">
         <v>8058</v>
@@ -52865,7 +52865,7 @@
         <v>6257</v>
       </c>
       <c r="D1250" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E1250" t="s">
         <v>8058</v>
@@ -53854,7 +53854,7 @@
         <v>6028</v>
       </c>
       <c r="D1293" t="s">
-        <v>7547</v>
+        <v>7546</v>
       </c>
       <c r="E1293" t="s">
         <v>8058</v>
@@ -53992,7 +53992,7 @@
         <v>6017</v>
       </c>
       <c r="D1299" t="s">
-        <v>7500</v>
+        <v>7499</v>
       </c>
       <c r="E1299" t="s">
         <v>8058</v>
@@ -54429,7 +54429,7 @@
         <v>6017</v>
       </c>
       <c r="D1318" t="s">
-        <v>7626</v>
+        <v>7625</v>
       </c>
       <c r="E1318" t="s">
         <v>8058</v>
@@ -54544,7 +54544,7 @@
         <v>6017</v>
       </c>
       <c r="D1323" t="s">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="E1323" t="s">
         <v>8058</v>
@@ -54981,7 +54981,7 @@
         <v>6257</v>
       </c>
       <c r="D1342" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1342" t="s">
         <v>8058</v>
@@ -55211,7 +55211,7 @@
         <v>6257</v>
       </c>
       <c r="D1352" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E1352" t="s">
         <v>8058</v>
@@ -55234,7 +55234,7 @@
         <v>6257</v>
       </c>
       <c r="D1353" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E1353" t="s">
         <v>8058</v>
@@ -55510,7 +55510,7 @@
         <v>6346</v>
       </c>
       <c r="D1365" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E1365" t="s">
         <v>8058</v>
@@ -55533,7 +55533,7 @@
         <v>6257</v>
       </c>
       <c r="D1366" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1366" t="s">
         <v>8058</v>
@@ -56522,7 +56522,7 @@
         <v>6017</v>
       </c>
       <c r="D1409" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1409" t="s">
         <v>8058</v>
@@ -57051,7 +57051,7 @@
         <v>6257</v>
       </c>
       <c r="D1432" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1432" t="s">
         <v>8058</v>
@@ -57097,7 +57097,7 @@
         <v>6257</v>
       </c>
       <c r="D1434" t="s">
-        <v>7488</v>
+        <v>7487</v>
       </c>
       <c r="E1434" t="s">
         <v>8058</v>
@@ -57695,7 +57695,7 @@
         <v>6024</v>
       </c>
       <c r="D1460" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E1460" t="s">
         <v>8058</v>
@@ -58040,7 +58040,7 @@
         <v>6257</v>
       </c>
       <c r="D1475" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E1475" t="s">
         <v>8058</v>
@@ -58293,7 +58293,7 @@
         <v>6257</v>
       </c>
       <c r="D1486" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1486" t="s">
         <v>8058</v>
@@ -58362,7 +58362,7 @@
         <v>6028</v>
       </c>
       <c r="D1489" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E1489" t="s">
         <v>8058</v>
@@ -58868,7 +58868,7 @@
         <v>6257</v>
       </c>
       <c r="D1511" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E1511" t="s">
         <v>8058</v>
@@ -59512,7 +59512,7 @@
         <v>6005</v>
       </c>
       <c r="D1539" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E1539" t="s">
         <v>8059</v>
@@ -59535,7 +59535,7 @@
         <v>6616</v>
       </c>
       <c r="D1540" t="s">
-        <v>7626</v>
+        <v>7625</v>
       </c>
       <c r="E1540" t="s">
         <v>8059</v>
@@ -59558,7 +59558,7 @@
         <v>6115</v>
       </c>
       <c r="D1541" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E1541" t="s">
         <v>8059</v>
@@ -59742,7 +59742,7 @@
         <v>6623</v>
       </c>
       <c r="D1549" t="s">
-        <v>7625</v>
+        <v>7624</v>
       </c>
       <c r="E1549" t="s">
         <v>8059</v>
@@ -59903,7 +59903,7 @@
         <v>6628</v>
       </c>
       <c r="D1556" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E1556" t="s">
         <v>8059</v>
@@ -60202,7 +60202,7 @@
         <v>6257</v>
       </c>
       <c r="D1569" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E1569" t="s">
         <v>8059</v>
@@ -60570,7 +60570,7 @@
         <v>6028</v>
       </c>
       <c r="D1585" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E1585" t="s">
         <v>8059</v>
@@ -60846,7 +60846,7 @@
         <v>6643</v>
       </c>
       <c r="D1597" t="s">
-        <v>7562</v>
+        <v>7561</v>
       </c>
       <c r="E1597" t="s">
         <v>8059</v>
@@ -61076,7 +61076,7 @@
         <v>6648</v>
       </c>
       <c r="D1607" t="s">
-        <v>7625</v>
+        <v>7624</v>
       </c>
       <c r="E1607" t="s">
         <v>8059</v>
@@ -61099,7 +61099,7 @@
         <v>6649</v>
       </c>
       <c r="D1608" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E1608" t="s">
         <v>8059</v>
@@ -61122,7 +61122,7 @@
         <v>6650</v>
       </c>
       <c r="D1609" t="s">
-        <v>7478</v>
+        <v>7477</v>
       </c>
       <c r="E1609" t="s">
         <v>8059</v>
@@ -61168,7 +61168,7 @@
         <v>6652</v>
       </c>
       <c r="D1611" t="s">
-        <v>7490</v>
+        <v>7489</v>
       </c>
       <c r="E1611" t="s">
         <v>8059</v>
@@ -61329,7 +61329,7 @@
         <v>6658</v>
       </c>
       <c r="D1618" t="s">
-        <v>7625</v>
+        <v>7624</v>
       </c>
       <c r="E1618" t="s">
         <v>8059</v>
@@ -61352,7 +61352,7 @@
         <v>6659</v>
       </c>
       <c r="D1619" t="s">
-        <v>7629</v>
+        <v>7628</v>
       </c>
       <c r="E1619" t="s">
         <v>8059</v>
@@ -61513,7 +61513,7 @@
         <v>6034</v>
       </c>
       <c r="D1626" t="s">
-        <v>7626</v>
+        <v>7625</v>
       </c>
       <c r="E1626" t="s">
         <v>8059</v>
@@ -61927,7 +61927,7 @@
         <v>6629</v>
       </c>
       <c r="D1644" t="s">
-        <v>7471</v>
+        <v>7629</v>
       </c>
       <c r="E1644" t="s">
         <v>8059</v>
@@ -62364,7 +62364,7 @@
         <v>6035</v>
       </c>
       <c r="D1663" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E1663" t="s">
         <v>8059</v>
@@ -62387,7 +62387,7 @@
         <v>6113</v>
       </c>
       <c r="D1664" t="s">
-        <v>7471</v>
+        <v>7629</v>
       </c>
       <c r="E1664" t="s">
         <v>8059</v>
@@ -62732,7 +62732,7 @@
         <v>6622</v>
       </c>
       <c r="D1679" t="s">
-        <v>7468</v>
+        <v>7471</v>
       </c>
       <c r="E1679" t="s">
         <v>8059</v>
@@ -62847,7 +62847,7 @@
         <v>6028</v>
       </c>
       <c r="D1684" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1684" t="s">
         <v>8059</v>
@@ -63077,7 +63077,7 @@
         <v>6257</v>
       </c>
       <c r="D1694" t="s">
-        <v>7525</v>
+        <v>7524</v>
       </c>
       <c r="E1694" t="s">
         <v>8059</v>
@@ -63606,7 +63606,7 @@
         <v>6700</v>
       </c>
       <c r="D1717" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E1717" t="s">
         <v>8059</v>
@@ -64204,7 +64204,7 @@
         <v>6127</v>
       </c>
       <c r="D1743" t="s">
-        <v>7470</v>
+        <v>7469</v>
       </c>
       <c r="E1743" t="s">
         <v>8059</v>
@@ -64273,7 +64273,7 @@
         <v>6716</v>
       </c>
       <c r="D1746" t="s">
-        <v>7596</v>
+        <v>7595</v>
       </c>
       <c r="E1746" t="s">
         <v>8061</v>
@@ -64522,7 +64522,7 @@
         <v>6379</v>
       </c>
       <c r="D1758" t="s">
-        <v>7535</v>
+        <v>7534</v>
       </c>
       <c r="E1758" t="s">
         <v>8061</v>
@@ -64628,7 +64628,7 @@
         <v>6722</v>
       </c>
       <c r="D1763" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E1763" t="s">
         <v>8061</v>
@@ -64648,7 +64648,7 @@
         <v>6723</v>
       </c>
       <c r="D1764" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1764" t="s">
         <v>8061</v>
@@ -64668,7 +64668,7 @@
         <v>6450</v>
       </c>
       <c r="D1765" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1765" t="s">
         <v>8061</v>
@@ -64771,7 +64771,7 @@
         <v>6470</v>
       </c>
       <c r="D1770" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E1770" t="s">
         <v>8061</v>
@@ -64814,7 +64814,7 @@
         <v>6470</v>
       </c>
       <c r="D1772" t="s">
-        <v>7513</v>
+        <v>7512</v>
       </c>
       <c r="E1772" t="s">
         <v>8061</v>
@@ -64860,7 +64860,7 @@
         <v>6716</v>
       </c>
       <c r="D1774" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E1774" t="s">
         <v>8061</v>
@@ -64940,7 +64940,7 @@
         <v>6450</v>
       </c>
       <c r="D1778" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E1778" t="s">
         <v>8061</v>
@@ -64960,7 +64960,7 @@
         <v>6723</v>
       </c>
       <c r="D1779" t="s">
-        <v>7522</v>
+        <v>7521</v>
       </c>
       <c r="E1779" t="s">
         <v>8061</v>
@@ -65003,7 +65003,7 @@
         <v>6728</v>
       </c>
       <c r="D1781" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1781" t="s">
         <v>8061</v>
@@ -65023,7 +65023,7 @@
         <v>6720</v>
       </c>
       <c r="D1782" t="s">
-        <v>7518</v>
+        <v>7517</v>
       </c>
       <c r="E1782" t="s">
         <v>8061</v>
@@ -65046,7 +65046,7 @@
         <v>6729</v>
       </c>
       <c r="D1783" t="s">
-        <v>7606</v>
+        <v>7605</v>
       </c>
       <c r="E1783" t="s">
         <v>8061</v>
@@ -65347,7 +65347,7 @@
         <v>6427</v>
       </c>
       <c r="D1797" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E1797" t="s">
         <v>8061</v>
@@ -65416,7 +65416,7 @@
         <v>6716</v>
       </c>
       <c r="D1800" t="s">
-        <v>7572</v>
+        <v>7571</v>
       </c>
       <c r="E1800" t="s">
         <v>8061</v>
@@ -65456,7 +65456,7 @@
         <v>6732</v>
       </c>
       <c r="D1802" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E1802" t="s">
         <v>8061</v>
@@ -65585,7 +65585,7 @@
         <v>6043</v>
       </c>
       <c r="D1808" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E1808" t="s">
         <v>8061</v>
@@ -65605,7 +65605,7 @@
         <v>6726</v>
       </c>
       <c r="D1809" t="s">
-        <v>7519</v>
+        <v>7518</v>
       </c>
       <c r="E1809" t="s">
         <v>8061</v>
@@ -65685,7 +65685,7 @@
         <v>6718</v>
       </c>
       <c r="D1813" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E1813" t="s">
         <v>8061</v>
@@ -65774,7 +65774,7 @@
         <v>6720</v>
       </c>
       <c r="D1817" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E1817" t="s">
         <v>8061</v>
@@ -65820,7 +65820,7 @@
         <v>6716</v>
       </c>
       <c r="D1819" t="s">
-        <v>7517</v>
+        <v>7516</v>
       </c>
       <c r="E1819" t="s">
         <v>8061</v>
@@ -65909,7 +65909,7 @@
         <v>6470</v>
       </c>
       <c r="D1823" t="s">
-        <v>7574</v>
+        <v>7573</v>
       </c>
       <c r="E1823" t="s">
         <v>8061</v>
@@ -65975,7 +65975,7 @@
         <v>6731</v>
       </c>
       <c r="D1826" t="s">
-        <v>7535</v>
+        <v>7534</v>
       </c>
       <c r="E1826" t="s">
         <v>8061</v>
@@ -66098,7 +66098,7 @@
         <v>6716</v>
       </c>
       <c r="D1832" t="s">
-        <v>7526</v>
+        <v>7525</v>
       </c>
       <c r="E1832" t="s">
         <v>8061</v>
@@ -66121,7 +66121,7 @@
         <v>6464</v>
       </c>
       <c r="D1833" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1833" t="s">
         <v>8061</v>
@@ -66227,7 +66227,7 @@
         <v>6410</v>
       </c>
       <c r="D1838" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E1838" t="s">
         <v>8061</v>
@@ -66376,7 +66376,7 @@
         <v>6744</v>
       </c>
       <c r="D1845" t="s">
-        <v>7577</v>
+        <v>7576</v>
       </c>
       <c r="E1845" t="s">
         <v>8061</v>
@@ -66442,7 +66442,7 @@
         <v>6745</v>
       </c>
       <c r="D1848" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E1848" t="s">
         <v>8061</v>
@@ -66789,7 +66789,7 @@
         <v>6004</v>
       </c>
       <c r="D1864" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E1864" t="s">
         <v>8064</v>
@@ -66924,7 +66924,7 @@
         <v>6754</v>
       </c>
       <c r="D1870" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E1870" t="s">
         <v>8066</v>
@@ -67190,7 +67190,7 @@
         <v>6764</v>
       </c>
       <c r="D1883" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E1883" t="s">
         <v>8066</v>
@@ -67533,7 +67533,7 @@
         <v>6772</v>
       </c>
       <c r="D1900" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E1900" t="s">
         <v>8066</v>
@@ -68480,7 +68480,7 @@
         <v>6084</v>
       </c>
       <c r="D1946" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E1946" t="s">
         <v>8066</v>
@@ -68500,7 +68500,7 @@
         <v>6758</v>
       </c>
       <c r="D1947" t="s">
-        <v>7499</v>
+        <v>7498</v>
       </c>
       <c r="E1947" t="s">
         <v>8066</v>
@@ -68706,7 +68706,7 @@
         <v>6768</v>
       </c>
       <c r="D1957" t="s">
-        <v>7577</v>
+        <v>7576</v>
       </c>
       <c r="E1957" t="s">
         <v>8066</v>
@@ -68746,7 +68746,7 @@
         <v>6178</v>
       </c>
       <c r="D1959" t="s">
-        <v>7499</v>
+        <v>7498</v>
       </c>
       <c r="E1959" t="s">
         <v>8066</v>
@@ -68806,7 +68806,7 @@
         <v>6758</v>
       </c>
       <c r="D1962" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E1962" t="s">
         <v>8066</v>
@@ -68869,7 +68869,7 @@
         <v>6793</v>
       </c>
       <c r="D1965" t="s">
-        <v>7500</v>
+        <v>7499</v>
       </c>
       <c r="E1965" t="s">
         <v>8066</v>
@@ -69104,7 +69104,7 @@
         <v>6008</v>
       </c>
       <c r="D1976" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E1976" t="s">
         <v>8067</v>
@@ -69173,7 +69173,7 @@
         <v>6084</v>
       </c>
       <c r="D1979" t="s">
-        <v>7541</v>
+        <v>7540</v>
       </c>
       <c r="E1979" t="s">
         <v>8068</v>
@@ -69216,7 +69216,7 @@
         <v>6680</v>
       </c>
       <c r="D1981" t="s">
-        <v>7516</v>
+        <v>7515</v>
       </c>
       <c r="E1981" t="s">
         <v>8069</v>
@@ -69302,7 +69302,7 @@
         <v>6467</v>
       </c>
       <c r="D1985" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1985" t="s">
         <v>8069</v>
@@ -69322,7 +69322,7 @@
         <v>6648</v>
       </c>
       <c r="D1986" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1986" t="s">
         <v>8069</v>
@@ -69451,7 +69451,7 @@
         <v>6805</v>
       </c>
       <c r="D1992" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E1992" t="s">
         <v>8069</v>
@@ -69474,7 +69474,7 @@
         <v>6778</v>
       </c>
       <c r="D1993" t="s">
-        <v>7523</v>
+        <v>7522</v>
       </c>
       <c r="E1993" t="s">
         <v>8069</v>
@@ -69683,7 +69683,7 @@
         <v>6808</v>
       </c>
       <c r="D2003" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E2003" t="s">
         <v>8069</v>
@@ -69703,7 +69703,7 @@
         <v>6809</v>
       </c>
       <c r="D2004" t="s">
-        <v>7518</v>
+        <v>7517</v>
       </c>
       <c r="E2004" t="s">
         <v>8069</v>
@@ -69769,7 +69769,7 @@
         <v>6467</v>
       </c>
       <c r="D2007" t="s">
-        <v>7518</v>
+        <v>7517</v>
       </c>
       <c r="E2007" t="s">
         <v>8069</v>
@@ -69792,7 +69792,7 @@
         <v>6762</v>
       </c>
       <c r="D2008" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2008" t="s">
         <v>8069</v>
@@ -69884,7 +69884,7 @@
         <v>6812</v>
       </c>
       <c r="D2012" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E2012" t="s">
         <v>8069</v>
@@ -69970,7 +69970,7 @@
         <v>6464</v>
       </c>
       <c r="D2016" t="s">
-        <v>7562</v>
+        <v>7561</v>
       </c>
       <c r="E2016" t="s">
         <v>8070</v>
@@ -70131,7 +70131,7 @@
         <v>6815</v>
       </c>
       <c r="D2023" t="s">
-        <v>7563</v>
+        <v>7562</v>
       </c>
       <c r="E2023" t="s">
         <v>8073</v>
@@ -70154,7 +70154,7 @@
         <v>6633</v>
       </c>
       <c r="D2024" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E2024" t="s">
         <v>8073</v>
@@ -70243,7 +70243,7 @@
         <v>6816</v>
       </c>
       <c r="D2028" t="s">
-        <v>7624</v>
+        <v>7623</v>
       </c>
       <c r="E2028" t="s">
         <v>8075</v>
@@ -70404,7 +70404,7 @@
         <v>6110</v>
       </c>
       <c r="D2035" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E2035" t="s">
         <v>8076</v>
@@ -71249,7 +71249,7 @@
         <v>6837</v>
       </c>
       <c r="D2075" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2075" t="s">
         <v>8077</v>
@@ -71748,7 +71748,7 @@
         <v>6847</v>
       </c>
       <c r="D2098" t="s">
-        <v>7528</v>
+        <v>7527</v>
       </c>
       <c r="E2098" t="s">
         <v>8078</v>
@@ -71891,7 +71891,7 @@
         <v>6852</v>
       </c>
       <c r="D2105" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2105" t="s">
         <v>8078</v>
@@ -71971,7 +71971,7 @@
         <v>6855</v>
       </c>
       <c r="D2109" t="s">
-        <v>7500</v>
+        <v>7499</v>
       </c>
       <c r="E2109" t="s">
         <v>8079</v>
@@ -71991,7 +71991,7 @@
         <v>6856</v>
       </c>
       <c r="D2110" t="s">
-        <v>7486</v>
+        <v>7485</v>
       </c>
       <c r="E2110" t="s">
         <v>8079</v>
@@ -72123,7 +72123,7 @@
         <v>6862</v>
       </c>
       <c r="D2116" t="s">
-        <v>7476</v>
+        <v>7475</v>
       </c>
       <c r="E2116" t="s">
         <v>8082</v>
@@ -72581,7 +72581,7 @@
         <v>6613</v>
       </c>
       <c r="D2138" t="s">
-        <v>7625</v>
+        <v>7624</v>
       </c>
       <c r="E2138" t="s">
         <v>8084</v>
@@ -73230,7 +73230,7 @@
         <v>6901</v>
       </c>
       <c r="D2170" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2170" t="s">
         <v>8087</v>
@@ -73250,7 +73250,7 @@
         <v>6902</v>
       </c>
       <c r="D2171" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2171" t="s">
         <v>8087</v>
@@ -73270,7 +73270,7 @@
         <v>6903</v>
       </c>
       <c r="D2172" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2172" t="s">
         <v>8087</v>
@@ -73290,7 +73290,7 @@
         <v>6904</v>
       </c>
       <c r="D2173" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2173" t="s">
         <v>8087</v>
@@ -73310,7 +73310,7 @@
         <v>6905</v>
       </c>
       <c r="D2174" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2174" t="s">
         <v>8087</v>
@@ -73330,7 +73330,7 @@
         <v>6493</v>
       </c>
       <c r="D2175" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2175" t="s">
         <v>8087</v>
@@ -73510,7 +73510,7 @@
         <v>6912</v>
       </c>
       <c r="D2184" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2184" t="s">
         <v>8088</v>
@@ -73754,7 +73754,7 @@
         <v>6918</v>
       </c>
       <c r="D2195" t="s">
-        <v>7601</v>
+        <v>7600</v>
       </c>
       <c r="E2195" t="s">
         <v>8088</v>
@@ -73774,7 +73774,7 @@
         <v>6911</v>
       </c>
       <c r="D2196" t="s">
-        <v>7524</v>
+        <v>7523</v>
       </c>
       <c r="E2196" t="s">
         <v>8088</v>
@@ -73797,7 +73797,7 @@
         <v>6919</v>
       </c>
       <c r="D2197" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E2197" t="s">
         <v>8088</v>
@@ -73817,7 +73817,7 @@
         <v>6920</v>
       </c>
       <c r="D2198" t="s">
-        <v>7572</v>
+        <v>7571</v>
       </c>
       <c r="E2198" t="s">
         <v>8088</v>
@@ -73837,7 +73837,7 @@
         <v>6921</v>
       </c>
       <c r="D2199" t="s">
-        <v>7524</v>
+        <v>7523</v>
       </c>
       <c r="E2199" t="s">
         <v>8088</v>
@@ -73860,7 +73860,7 @@
         <v>6412</v>
       </c>
       <c r="D2200" t="s">
-        <v>7533</v>
+        <v>7532</v>
       </c>
       <c r="E2200" t="s">
         <v>8088</v>
@@ -73995,7 +73995,7 @@
         <v>6925</v>
       </c>
       <c r="D2206" t="s">
-        <v>7533</v>
+        <v>7532</v>
       </c>
       <c r="E2206" t="s">
         <v>8088</v>
@@ -74038,7 +74038,7 @@
         <v>6912</v>
       </c>
       <c r="D2208" t="s">
-        <v>7572</v>
+        <v>7571</v>
       </c>
       <c r="E2208" t="s">
         <v>8088</v>
@@ -74213,7 +74213,7 @@
         <v>6931</v>
       </c>
       <c r="D2216" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E2216" t="s">
         <v>8088</v>
@@ -74253,7 +74253,7 @@
         <v>6933</v>
       </c>
       <c r="D2218" t="s">
-        <v>7518</v>
+        <v>7517</v>
       </c>
       <c r="E2218" t="s">
         <v>8088</v>
@@ -74276,7 +74276,7 @@
         <v>6934</v>
       </c>
       <c r="D2219" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E2219" t="s">
         <v>8088</v>
@@ -74385,7 +74385,7 @@
         <v>6917</v>
       </c>
       <c r="D2224" t="s">
-        <v>7522</v>
+        <v>7521</v>
       </c>
       <c r="E2224" t="s">
         <v>8088</v>
@@ -74405,7 +74405,7 @@
         <v>6923</v>
       </c>
       <c r="D2225" t="s">
-        <v>7579</v>
+        <v>7578</v>
       </c>
       <c r="E2225" t="s">
         <v>8088</v>
@@ -74451,7 +74451,7 @@
         <v>6919</v>
       </c>
       <c r="D2227" t="s">
-        <v>7522</v>
+        <v>7521</v>
       </c>
       <c r="E2227" t="s">
         <v>8088</v>
@@ -74563,7 +74563,7 @@
         <v>6938</v>
       </c>
       <c r="D2232" t="s">
-        <v>7606</v>
+        <v>7605</v>
       </c>
       <c r="E2232" t="s">
         <v>8088</v>
@@ -74586,7 +74586,7 @@
         <v>6939</v>
       </c>
       <c r="D2233" t="s">
-        <v>7606</v>
+        <v>7605</v>
       </c>
       <c r="E2233" t="s">
         <v>8088</v>
@@ -74626,7 +74626,7 @@
         <v>6762</v>
       </c>
       <c r="D2235" t="s">
-        <v>7601</v>
+        <v>7600</v>
       </c>
       <c r="E2235" t="s">
         <v>8088</v>
@@ -75199,7 +75199,7 @@
         <v>6223</v>
       </c>
       <c r="D2262" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E2262" t="s">
         <v>8092</v>
@@ -75222,7 +75222,7 @@
         <v>6109</v>
       </c>
       <c r="D2263" t="s">
-        <v>7497</v>
+        <v>7496</v>
       </c>
       <c r="E2263" t="s">
         <v>8092</v>
@@ -75314,7 +75314,7 @@
         <v>6017</v>
       </c>
       <c r="D2267" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E2267" t="s">
         <v>8092</v>
@@ -75337,7 +75337,7 @@
         <v>6955</v>
       </c>
       <c r="D2268" t="s">
-        <v>7491</v>
+        <v>7490</v>
       </c>
       <c r="E2268" t="s">
         <v>8093</v>
@@ -75377,7 +75377,7 @@
         <v>6956</v>
       </c>
       <c r="D2270" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2270" t="s">
         <v>8093</v>
@@ -75397,7 +75397,7 @@
         <v>6014</v>
       </c>
       <c r="D2271" t="s">
-        <v>7495</v>
+        <v>7494</v>
       </c>
       <c r="E2271" t="s">
         <v>8093</v>
@@ -76193,7 +76193,7 @@
         <v>6974</v>
       </c>
       <c r="D2306" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E2306" t="s">
         <v>8093</v>
@@ -76216,7 +76216,7 @@
         <v>6975</v>
       </c>
       <c r="D2307" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E2307" t="s">
         <v>8093</v>
@@ -76460,7 +76460,7 @@
         <v>6257</v>
       </c>
       <c r="D2318" t="s">
-        <v>7562</v>
+        <v>7561</v>
       </c>
       <c r="E2318" t="s">
         <v>8095</v>
@@ -76589,7 +76589,7 @@
         <v>6017</v>
       </c>
       <c r="D2324" t="s">
-        <v>7471</v>
+        <v>7629</v>
       </c>
       <c r="E2324" t="s">
         <v>8095</v>
@@ -76853,7 +76853,7 @@
         <v>6032</v>
       </c>
       <c r="D2336" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E2336" t="s">
         <v>8095</v>
@@ -76953,7 +76953,7 @@
         <v>6028</v>
       </c>
       <c r="D2341" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E2341" t="s">
         <v>8095</v>
@@ -76976,7 +76976,7 @@
         <v>6120</v>
       </c>
       <c r="D2342" t="s">
-        <v>7624</v>
+        <v>7623</v>
       </c>
       <c r="E2342" t="s">
         <v>8095</v>
@@ -77378,7 +77378,7 @@
         <v>6084</v>
       </c>
       <c r="D2360" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E2360" t="s">
         <v>8095</v>
@@ -77401,7 +77401,7 @@
         <v>6028</v>
       </c>
       <c r="D2361" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E2361" t="s">
         <v>8095</v>
@@ -77424,7 +77424,7 @@
         <v>6214</v>
       </c>
       <c r="D2362" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E2362" t="s">
         <v>8095</v>
@@ -77619,7 +77619,7 @@
         <v>6842</v>
       </c>
       <c r="D2371" t="s">
-        <v>7562</v>
+        <v>7561</v>
       </c>
       <c r="E2371" t="s">
         <v>8095</v>
@@ -77906,7 +77906,7 @@
         <v>6579</v>
       </c>
       <c r="D2384" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E2384" t="s">
         <v>8095</v>
@@ -77969,7 +77969,7 @@
         <v>6114</v>
       </c>
       <c r="D2387" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E2387" t="s">
         <v>8095</v>
@@ -78468,7 +78468,7 @@
         <v>6108</v>
       </c>
       <c r="D2410" t="s">
-        <v>7562</v>
+        <v>7561</v>
       </c>
       <c r="E2410" t="s">
         <v>8095</v>
@@ -78580,7 +78580,7 @@
         <v>6114</v>
       </c>
       <c r="D2415" t="s">
-        <v>7629</v>
+        <v>7628</v>
       </c>
       <c r="E2415" t="s">
         <v>8095</v>
@@ -79048,7 +79048,7 @@
         <v>6115</v>
       </c>
       <c r="D2436" t="s">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="E2436" t="s">
         <v>8095</v>
@@ -79091,7 +79091,7 @@
         <v>6998</v>
       </c>
       <c r="D2438" t="s">
-        <v>7478</v>
+        <v>7477</v>
       </c>
       <c r="E2438" t="s">
         <v>8097</v>
@@ -79111,7 +79111,7 @@
         <v>6999</v>
       </c>
       <c r="D2439" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E2439" t="s">
         <v>8097</v>
@@ -79211,7 +79211,7 @@
         <v>7003</v>
       </c>
       <c r="D2444" t="s">
-        <v>7538</v>
+        <v>7537</v>
       </c>
       <c r="E2444" t="s">
         <v>8097</v>
@@ -79311,7 +79311,7 @@
         <v>7008</v>
       </c>
       <c r="D2449" t="s">
-        <v>7500</v>
+        <v>7499</v>
       </c>
       <c r="E2449" t="s">
         <v>8097</v>
@@ -79374,7 +79374,7 @@
         <v>6357</v>
       </c>
       <c r="D2452" t="s">
-        <v>7501</v>
+        <v>7500</v>
       </c>
       <c r="E2452" t="s">
         <v>8098</v>
@@ -79457,7 +79457,7 @@
         <v>6356</v>
       </c>
       <c r="D2456" t="s">
-        <v>7505</v>
+        <v>7504</v>
       </c>
       <c r="E2456" t="s">
         <v>8098</v>
@@ -79557,7 +79557,7 @@
         <v>7016</v>
       </c>
       <c r="D2461" t="s">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="E2461" t="s">
         <v>8098</v>
@@ -79683,7 +79683,7 @@
         <v>7021</v>
       </c>
       <c r="D2467" t="s">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="E2467" t="s">
         <v>8098</v>
@@ -79746,7 +79746,7 @@
         <v>6358</v>
       </c>
       <c r="D2470" t="s">
-        <v>7509</v>
+        <v>7508</v>
       </c>
       <c r="E2470" t="s">
         <v>8098</v>
@@ -80188,7 +80188,7 @@
         <v>6223</v>
       </c>
       <c r="D2490" t="s">
-        <v>7499</v>
+        <v>7498</v>
       </c>
       <c r="E2490" t="s">
         <v>8102</v>
@@ -80326,7 +80326,7 @@
         <v>6223</v>
       </c>
       <c r="D2496" t="s">
-        <v>7556</v>
+        <v>7555</v>
       </c>
       <c r="E2496" t="s">
         <v>8102</v>
@@ -81378,7 +81378,7 @@
         <v>7031</v>
       </c>
       <c r="D2545" t="s">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="E2545" t="s">
         <v>8104</v>
@@ -81398,7 +81398,7 @@
         <v>7032</v>
       </c>
       <c r="D2546" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2546" t="s">
         <v>8104</v>
@@ -81721,7 +81721,7 @@
         <v>7045</v>
       </c>
       <c r="D2562" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2562" t="s">
         <v>8104</v>
@@ -81841,7 +81841,7 @@
         <v>7048</v>
       </c>
       <c r="D2568" t="s">
-        <v>7538</v>
+        <v>7537</v>
       </c>
       <c r="E2568" t="s">
         <v>8105</v>
@@ -81901,7 +81901,7 @@
         <v>7049</v>
       </c>
       <c r="D2571" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E2571" t="s">
         <v>8105</v>
@@ -82181,7 +82181,7 @@
         <v>6084</v>
       </c>
       <c r="D2585" t="s">
-        <v>7500</v>
+        <v>7499</v>
       </c>
       <c r="E2585" t="s">
         <v>8106</v>
@@ -82261,7 +82261,7 @@
         <v>7055</v>
       </c>
       <c r="D2589" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2589" t="s">
         <v>8106</v>
@@ -82361,7 +82361,7 @@
         <v>7059</v>
       </c>
       <c r="D2594" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2594" t="s">
         <v>8106</v>
@@ -82680,7 +82680,7 @@
         <v>7062</v>
       </c>
       <c r="D2608" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2608" t="s">
         <v>8108</v>
@@ -83067,7 +83067,7 @@
         <v>6043</v>
       </c>
       <c r="D2626" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2626" t="s">
         <v>8111</v>
@@ -83110,7 +83110,7 @@
         <v>6636</v>
       </c>
       <c r="D2628" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E2628" t="s">
         <v>8111</v>
@@ -83428,7 +83428,7 @@
         <v>6548</v>
       </c>
       <c r="D2643" t="s">
-        <v>7556</v>
+        <v>7555</v>
       </c>
       <c r="E2643" t="s">
         <v>8111</v>
@@ -83635,7 +83635,7 @@
         <v>7074</v>
       </c>
       <c r="D2652" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2652" t="s">
         <v>8111</v>
@@ -83658,7 +83658,7 @@
         <v>6043</v>
       </c>
       <c r="D2653" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2653" t="s">
         <v>8111</v>
@@ -83704,7 +83704,7 @@
         <v>6583</v>
       </c>
       <c r="D2655" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2655" t="s">
         <v>8111</v>
@@ -83819,7 +83819,7 @@
         <v>7075</v>
       </c>
       <c r="D2660" t="s">
-        <v>7484</v>
+        <v>7483</v>
       </c>
       <c r="E2660" t="s">
         <v>8111</v>
@@ -83842,7 +83842,7 @@
         <v>6084</v>
       </c>
       <c r="D2661" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2661" t="s">
         <v>8111</v>
@@ -83980,7 +83980,7 @@
         <v>6964</v>
       </c>
       <c r="D2667" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E2667" t="s">
         <v>8111</v>
@@ -84023,7 +84023,7 @@
         <v>6084</v>
       </c>
       <c r="D2669" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E2669" t="s">
         <v>8111</v>
@@ -84192,7 +84192,7 @@
         <v>6575</v>
       </c>
       <c r="D2677" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E2677" t="s">
         <v>8111</v>
@@ -84413,7 +84413,7 @@
         <v>7082</v>
       </c>
       <c r="D2687" t="s">
-        <v>7610</v>
+        <v>7609</v>
       </c>
       <c r="E2687" t="s">
         <v>8111</v>
@@ -84525,7 +84525,7 @@
         <v>7081</v>
       </c>
       <c r="D2692" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2692" t="s">
         <v>8111</v>
@@ -84614,7 +84614,7 @@
         <v>6084</v>
       </c>
       <c r="D2696" t="s">
-        <v>7493</v>
+        <v>7492</v>
       </c>
       <c r="E2696" t="s">
         <v>8111</v>
@@ -84683,7 +84683,7 @@
         <v>6479</v>
       </c>
       <c r="D2699" t="s">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="E2699" t="s">
         <v>8111</v>
@@ -84706,7 +84706,7 @@
         <v>6562</v>
       </c>
       <c r="D2700" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E2700" t="s">
         <v>8111</v>
@@ -84769,7 +84769,7 @@
         <v>7087</v>
       </c>
       <c r="D2703" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2703" t="s">
         <v>8111</v>
@@ -84884,7 +84884,7 @@
         <v>7062</v>
       </c>
       <c r="D2708" t="s">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="E2708" t="s">
         <v>8111</v>
@@ -85068,7 +85068,7 @@
         <v>7089</v>
       </c>
       <c r="D2716" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2716" t="s">
         <v>8111</v>
@@ -85157,7 +85157,7 @@
         <v>7090</v>
       </c>
       <c r="D2720" t="s">
-        <v>7607</v>
+        <v>7606</v>
       </c>
       <c r="E2720" t="s">
         <v>8111</v>
@@ -85180,7 +85180,7 @@
         <v>7072</v>
       </c>
       <c r="D2721" t="s">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="E2721" t="s">
         <v>8111</v>
@@ -85223,7 +85223,7 @@
         <v>7077</v>
       </c>
       <c r="D2723" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2723" t="s">
         <v>8111</v>
@@ -85355,7 +85355,7 @@
         <v>7092</v>
       </c>
       <c r="D2729" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2729" t="s">
         <v>8111</v>
@@ -85401,7 +85401,7 @@
         <v>7093</v>
       </c>
       <c r="D2731" t="s">
-        <v>7604</v>
+        <v>7603</v>
       </c>
       <c r="E2731" t="s">
         <v>8113</v>
@@ -85481,7 +85481,7 @@
         <v>6747</v>
       </c>
       <c r="D2735" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2735" t="s">
         <v>8113</v>
@@ -85501,7 +85501,7 @@
         <v>6747</v>
       </c>
       <c r="D2736" t="s">
-        <v>7533</v>
+        <v>7532</v>
       </c>
       <c r="E2736" t="s">
         <v>8113</v>
@@ -85607,7 +85607,7 @@
         <v>6747</v>
       </c>
       <c r="D2741" t="s">
-        <v>7491</v>
+        <v>7490</v>
       </c>
       <c r="E2741" t="s">
         <v>8113</v>
@@ -85647,7 +85647,7 @@
         <v>7098</v>
       </c>
       <c r="D2743" t="s">
-        <v>7539</v>
+        <v>7538</v>
       </c>
       <c r="E2743" t="s">
         <v>8113</v>
@@ -85667,7 +85667,7 @@
         <v>6084</v>
       </c>
       <c r="D2744" t="s">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="E2744" t="s">
         <v>8113</v>
@@ -85747,7 +85747,7 @@
         <v>7096</v>
       </c>
       <c r="D2748" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E2748" t="s">
         <v>8113</v>
@@ -85990,7 +85990,7 @@
         <v>6747</v>
       </c>
       <c r="D2760" t="s">
-        <v>7522</v>
+        <v>7521</v>
       </c>
       <c r="E2760" t="s">
         <v>8113</v>
@@ -86013,7 +86013,7 @@
         <v>6084</v>
       </c>
       <c r="D2761" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E2761" t="s">
         <v>8113</v>
@@ -86033,7 +86033,7 @@
         <v>6084</v>
       </c>
       <c r="D2762" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E2762" t="s">
         <v>8113</v>
@@ -86073,7 +86073,7 @@
         <v>6084</v>
       </c>
       <c r="D2764" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2764" t="s">
         <v>8113</v>
@@ -86116,7 +86116,7 @@
         <v>7096</v>
       </c>
       <c r="D2766" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E2766" t="s">
         <v>8113</v>
@@ -86136,7 +86136,7 @@
         <v>7105</v>
       </c>
       <c r="D2767" t="s">
-        <v>7596</v>
+        <v>7595</v>
       </c>
       <c r="E2767" t="s">
         <v>8113</v>
@@ -86268,7 +86268,7 @@
         <v>7108</v>
       </c>
       <c r="D2773" t="s">
-        <v>7539</v>
+        <v>7538</v>
       </c>
       <c r="E2773" t="s">
         <v>8113</v>
@@ -86417,7 +86417,7 @@
         <v>6909</v>
       </c>
       <c r="D2780" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2780" t="s">
         <v>8113</v>
@@ -86503,7 +86503,7 @@
         <v>7113</v>
       </c>
       <c r="D2784" t="s">
-        <v>7478</v>
+        <v>7477</v>
       </c>
       <c r="E2784" t="s">
         <v>8114</v>
@@ -86526,7 +86526,7 @@
         <v>7114</v>
       </c>
       <c r="D2785" t="s">
-        <v>7478</v>
+        <v>7477</v>
       </c>
       <c r="E2785" t="s">
         <v>8114</v>
@@ -86792,7 +86792,7 @@
         <v>7124</v>
       </c>
       <c r="D2798" t="s">
-        <v>7486</v>
+        <v>7485</v>
       </c>
       <c r="E2798" t="s">
         <v>8115</v>
@@ -87161,7 +87161,7 @@
         <v>7135</v>
       </c>
       <c r="D2816" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E2816" t="s">
         <v>8116</v>
@@ -87181,7 +87181,7 @@
         <v>7138</v>
       </c>
       <c r="D2817" t="s">
-        <v>7604</v>
+        <v>7603</v>
       </c>
       <c r="E2817" t="s">
         <v>8116</v>
@@ -87201,7 +87201,7 @@
         <v>6084</v>
       </c>
       <c r="D2818" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E2818" t="s">
         <v>8116</v>
@@ -87244,7 +87244,7 @@
         <v>7136</v>
       </c>
       <c r="D2820" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2820" t="s">
         <v>8116</v>
@@ -87284,7 +87284,7 @@
         <v>7139</v>
       </c>
       <c r="D2822" t="s">
-        <v>7553</v>
+        <v>7552</v>
       </c>
       <c r="E2822" t="s">
         <v>8116</v>
@@ -87324,7 +87324,7 @@
         <v>7141</v>
       </c>
       <c r="D2824" t="s">
-        <v>7533</v>
+        <v>7532</v>
       </c>
       <c r="E2824" t="s">
         <v>8116</v>
@@ -87347,7 +87347,7 @@
         <v>7142</v>
       </c>
       <c r="D2825" t="s">
-        <v>7518</v>
+        <v>7517</v>
       </c>
       <c r="E2825" t="s">
         <v>8116</v>
@@ -87370,7 +87370,7 @@
         <v>7142</v>
       </c>
       <c r="D2826" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2826" t="s">
         <v>8116</v>
@@ -87430,7 +87430,7 @@
         <v>6020</v>
       </c>
       <c r="D2829" t="s">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="E2829" t="s">
         <v>8116</v>
@@ -87513,7 +87513,7 @@
         <v>6084</v>
       </c>
       <c r="D2833" t="s">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="E2833" t="s">
         <v>8116</v>
@@ -87602,7 +87602,7 @@
         <v>7144</v>
       </c>
       <c r="D2837" t="s">
-        <v>7493</v>
+        <v>7492</v>
       </c>
       <c r="E2837" t="s">
         <v>8116</v>
@@ -87645,7 +87645,7 @@
         <v>7132</v>
       </c>
       <c r="D2839" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2839" t="s">
         <v>8116</v>
@@ -87823,7 +87823,7 @@
         <v>6020</v>
       </c>
       <c r="D2847" t="s">
-        <v>7598</v>
+        <v>7597</v>
       </c>
       <c r="E2847" t="s">
         <v>8116</v>
@@ -87866,7 +87866,7 @@
         <v>7148</v>
       </c>
       <c r="D2849" t="s">
-        <v>7527</v>
+        <v>7526</v>
       </c>
       <c r="E2849" t="s">
         <v>8116</v>
@@ -87889,7 +87889,7 @@
         <v>7151</v>
       </c>
       <c r="D2850" t="s">
-        <v>7482</v>
+        <v>7481</v>
       </c>
       <c r="E2850" t="s">
         <v>8117</v>
@@ -87989,7 +87989,7 @@
         <v>7155</v>
       </c>
       <c r="D2855" t="s">
-        <v>7482</v>
+        <v>7481</v>
       </c>
       <c r="E2855" t="s">
         <v>8117</v>
@@ -88129,7 +88129,7 @@
         <v>7160</v>
       </c>
       <c r="D2862" t="s">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="E2862" t="s">
         <v>8117</v>
@@ -88209,7 +88209,7 @@
         <v>7162</v>
       </c>
       <c r="D2866" t="s">
-        <v>7482</v>
+        <v>7481</v>
       </c>
       <c r="E2866" t="s">
         <v>8117</v>
@@ -88229,7 +88229,7 @@
         <v>7163</v>
       </c>
       <c r="D2867" t="s">
-        <v>7482</v>
+        <v>7481</v>
       </c>
       <c r="E2867" t="s">
         <v>8117</v>
@@ -88812,7 +88812,7 @@
         <v>7187</v>
       </c>
       <c r="D2896" t="s">
-        <v>7538</v>
+        <v>7537</v>
       </c>
       <c r="E2896" t="s">
         <v>8119</v>
@@ -89152,7 +89152,7 @@
         <v>6084</v>
       </c>
       <c r="D2913" t="s">
-        <v>7538</v>
+        <v>7537</v>
       </c>
       <c r="E2913" t="s">
         <v>8119</v>
@@ -89252,7 +89252,7 @@
         <v>6084</v>
       </c>
       <c r="D2918" t="s">
-        <v>7613</v>
+        <v>7612</v>
       </c>
       <c r="E2918" t="s">
         <v>8120</v>
@@ -89275,7 +89275,7 @@
         <v>6084</v>
       </c>
       <c r="D2919" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E2919" t="s">
         <v>8120</v>
@@ -89384,7 +89384,7 @@
         <v>7203</v>
       </c>
       <c r="D2924" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E2924" t="s">
         <v>8120</v>
@@ -89447,7 +89447,7 @@
         <v>6084</v>
       </c>
       <c r="D2927" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E2927" t="s">
         <v>8120</v>
@@ -89570,7 +89570,7 @@
         <v>7205</v>
       </c>
       <c r="D2933" t="s">
-        <v>7521</v>
+        <v>7520</v>
       </c>
       <c r="E2933" t="s">
         <v>8120</v>
@@ -89656,7 +89656,7 @@
         <v>7206</v>
       </c>
       <c r="D2937" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E2937" t="s">
         <v>8120</v>
@@ -89765,7 +89765,7 @@
         <v>7209</v>
       </c>
       <c r="D2942" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2942" t="s">
         <v>8120</v>
@@ -90104,7 +90104,7 @@
         <v>7217</v>
       </c>
       <c r="D2957" t="s">
-        <v>7477</v>
+        <v>7476</v>
       </c>
       <c r="E2957" t="s">
         <v>8122</v>
@@ -90267,7 +90267,7 @@
         <v>7223</v>
       </c>
       <c r="D2965" t="s">
-        <v>7478</v>
+        <v>7477</v>
       </c>
       <c r="E2965" t="s">
         <v>8122</v>
@@ -90467,7 +90467,7 @@
         <v>6191</v>
       </c>
       <c r="D2975" t="s">
-        <v>7494</v>
+        <v>7493</v>
       </c>
       <c r="E2975" t="s">
         <v>8122</v>
@@ -90665,7 +90665,7 @@
         <v>6257</v>
       </c>
       <c r="D2984" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E2984" t="s">
         <v>8124</v>
@@ -90751,7 +90751,7 @@
         <v>6447</v>
       </c>
       <c r="D2988" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E2988" t="s">
         <v>8126</v>
@@ -90837,7 +90837,7 @@
         <v>6101</v>
       </c>
       <c r="D2992" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E2992" t="s">
         <v>8126</v>
@@ -90860,7 +90860,7 @@
         <v>6404</v>
       </c>
       <c r="D2993" t="s">
-        <v>7525</v>
+        <v>7524</v>
       </c>
       <c r="E2993" t="s">
         <v>8126</v>
@@ -90903,7 +90903,7 @@
         <v>6421</v>
       </c>
       <c r="D2995" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E2995" t="s">
         <v>8126</v>
@@ -90943,7 +90943,7 @@
         <v>6447</v>
       </c>
       <c r="D2997" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E2997" t="s">
         <v>8126</v>
@@ -90986,7 +90986,7 @@
         <v>7236</v>
       </c>
       <c r="D2999" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E2999" t="s">
         <v>8126</v>
@@ -91072,7 +91072,7 @@
         <v>6442</v>
       </c>
       <c r="D3003" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E3003" t="s">
         <v>8126</v>
@@ -91092,7 +91092,7 @@
         <v>6447</v>
       </c>
       <c r="D3004" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E3004" t="s">
         <v>8126</v>
@@ -91161,7 +91161,7 @@
         <v>6101</v>
       </c>
       <c r="D3007" t="s">
-        <v>7545</v>
+        <v>7544</v>
       </c>
       <c r="E3007" t="s">
         <v>8126</v>
@@ -91281,7 +91281,7 @@
         <v>6421</v>
       </c>
       <c r="D3013" t="s">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="E3013" t="s">
         <v>8126</v>
@@ -91347,7 +91347,7 @@
         <v>6101</v>
       </c>
       <c r="D3016" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E3016" t="s">
         <v>8126</v>
@@ -91370,7 +91370,7 @@
         <v>6447</v>
       </c>
       <c r="D3017" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E3017" t="s">
         <v>8126</v>
@@ -91573,7 +91573,7 @@
         <v>7239</v>
       </c>
       <c r="D3027" t="s">
-        <v>7610</v>
+        <v>7609</v>
       </c>
       <c r="E3027" t="s">
         <v>8126</v>
@@ -91662,7 +91662,7 @@
         <v>7244</v>
       </c>
       <c r="D3031" t="s">
-        <v>7578</v>
+        <v>7577</v>
       </c>
       <c r="E3031" t="s">
         <v>8126</v>
@@ -91705,7 +91705,7 @@
         <v>6389</v>
       </c>
       <c r="D3033" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E3033" t="s">
         <v>8126</v>
@@ -91791,7 +91791,7 @@
         <v>7239</v>
       </c>
       <c r="D3037" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E3037" t="s">
         <v>8126</v>
@@ -91937,7 +91937,7 @@
         <v>6101</v>
       </c>
       <c r="D3044" t="s">
-        <v>7544</v>
+        <v>7543</v>
       </c>
       <c r="E3044" t="s">
         <v>8126</v>
@@ -91997,7 +91997,7 @@
         <v>6911</v>
       </c>
       <c r="D3047" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E3047" t="s">
         <v>8126</v>
@@ -92040,7 +92040,7 @@
         <v>6922</v>
       </c>
       <c r="D3049" t="s">
-        <v>7596</v>
+        <v>7595</v>
       </c>
       <c r="E3049" t="s">
         <v>8126</v>
@@ -92063,7 +92063,7 @@
         <v>7239</v>
       </c>
       <c r="D3050" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E3050" t="s">
         <v>8126</v>
@@ -92123,7 +92123,7 @@
         <v>6421</v>
       </c>
       <c r="D3053" t="s">
-        <v>7480</v>
+        <v>7479</v>
       </c>
       <c r="E3053" t="s">
         <v>8126</v>
@@ -92192,7 +92192,7 @@
         <v>6421</v>
       </c>
       <c r="D3056" t="s">
-        <v>7537</v>
+        <v>7536</v>
       </c>
       <c r="E3056" t="s">
         <v>8126</v>
@@ -92215,7 +92215,7 @@
         <v>7247</v>
       </c>
       <c r="D3057" t="s">
-        <v>7520</v>
+        <v>7519</v>
       </c>
       <c r="E3057" t="s">
         <v>8126</v>
@@ -92238,7 +92238,7 @@
         <v>6922</v>
       </c>
       <c r="D3058" t="s">
-        <v>7524</v>
+        <v>7523</v>
       </c>
       <c r="E3058" t="s">
         <v>8126</v>
@@ -92327,7 +92327,7 @@
         <v>7242</v>
       </c>
       <c r="D3062" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E3062" t="s">
         <v>8126</v>
@@ -92370,7 +92370,7 @@
         <v>6099</v>
       </c>
       <c r="D3064" t="s">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="E3064" t="s">
         <v>8126</v>
@@ -92393,7 +92393,7 @@
         <v>6447</v>
       </c>
       <c r="D3065" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E3065" t="s">
         <v>8126</v>
@@ -92456,7 +92456,7 @@
         <v>6908</v>
       </c>
       <c r="D3068" t="s">
-        <v>7608</v>
+        <v>7607</v>
       </c>
       <c r="E3068" t="s">
         <v>8126</v>
@@ -92479,7 +92479,7 @@
         <v>6389</v>
       </c>
       <c r="D3069" t="s">
-        <v>7576</v>
+        <v>7575</v>
       </c>
       <c r="E3069" t="s">
         <v>8126</v>
@@ -92525,7 +92525,7 @@
         <v>6447</v>
       </c>
       <c r="D3071" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E3071" t="s">
         <v>8126</v>
@@ -92571,7 +92571,7 @@
         <v>7140</v>
       </c>
       <c r="D3073" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E3073" t="s">
         <v>8126</v>
@@ -92789,7 +92789,7 @@
         <v>6447</v>
       </c>
       <c r="D3083" t="s">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="E3083" t="s">
         <v>8126</v>
@@ -92955,7 +92955,7 @@
         <v>7235</v>
       </c>
       <c r="D3091" t="s">
-        <v>7526</v>
+        <v>7525</v>
       </c>
       <c r="E3091" t="s">
         <v>8126</v>
@@ -92975,7 +92975,7 @@
         <v>7251</v>
       </c>
       <c r="D3092" t="s">
-        <v>7517</v>
+        <v>7516</v>
       </c>
       <c r="E3092" t="s">
         <v>8126</v>
@@ -93144,7 +93144,7 @@
         <v>7246</v>
       </c>
       <c r="D3100" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E3100" t="s">
         <v>8126</v>
@@ -93276,7 +93276,7 @@
         <v>7248</v>
       </c>
       <c r="D3106" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E3106" t="s">
         <v>8126</v>
@@ -93345,7 +93345,7 @@
         <v>7259</v>
       </c>
       <c r="D3109" t="s">
-        <v>7497</v>
+        <v>7496</v>
       </c>
       <c r="E3109" t="s">
         <v>8128</v>
@@ -93414,7 +93414,7 @@
         <v>6711</v>
       </c>
       <c r="D3112" t="s">
-        <v>7426</v>
+        <v>7769</v>
       </c>
       <c r="E3112" t="s">
         <v>8129</v>
@@ -93437,7 +93437,7 @@
         <v>6019</v>
       </c>
       <c r="D3113" t="s">
-        <v>7625</v>
+        <v>7623</v>
       </c>
       <c r="E3113" t="s">
         <v>8129</v>
@@ -93526,7 +93526,7 @@
         <v>6256</v>
       </c>
       <c r="D3117" t="s">
-        <v>7541</v>
+        <v>7540</v>
       </c>
       <c r="E3117" t="s">
         <v>8129</v>
@@ -93848,7 +93848,7 @@
         <v>7267</v>
       </c>
       <c r="D3131" t="s">
-        <v>7543</v>
+        <v>7542</v>
       </c>
       <c r="E3131" t="s">
         <v>8130</v>
@@ -93957,7 +93957,7 @@
         <v>7271</v>
       </c>
       <c r="D3136" t="s">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="E3136" t="s">
         <v>8131</v>
@@ -94037,7 +94037,7 @@
         <v>7274</v>
       </c>
       <c r="D3140" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E3140" t="s">
         <v>8131</v>
@@ -94410,7 +94410,7 @@
         <v>7283</v>
       </c>
       <c r="D3157" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E3157" t="s">
         <v>8133</v>
@@ -94542,7 +94542,7 @@
         <v>7287</v>
       </c>
       <c r="D3163" t="s">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="E3163" t="s">
         <v>8133</v>
@@ -94648,7 +94648,7 @@
         <v>6043</v>
       </c>
       <c r="D3168" t="s">
-        <v>7475</v>
+        <v>7474</v>
       </c>
       <c r="E3168" t="s">
         <v>8133</v>

--- a/nao_positivados_06-2026.xlsx
+++ b/nao_positivados_06-2026.xlsx
@@ -22414,12 +22414,15 @@
     <t>APERITIVO APEROL 750 ML</t>
   </si>
   <si>
-    <t>VINHO TINTO QUINTA DE VENTOZELO SOUSAO</t>
+    <t>VINHO QUINTA DE VENTOZELO TINTO CÃ0</t>
   </si>
   <si>
     <t>HUMB. CANALE DENARIO MALBEC 750ML</t>
   </si>
   <si>
+    <t>VINHO LA TOGATA ROSSO 750ML</t>
+  </si>
+  <si>
     <t>VINHO LA TOGATA BRUNELLO ETQ AZUL 750ML</t>
   </si>
   <si>
@@ -22427,9 +22430,6 @@
   </si>
   <si>
     <t>VINHO BAROLO BUSSIA RISERVA 750ML</t>
-  </si>
-  <si>
-    <t>VINHO LA TOGATA ROSSO 750ML</t>
   </si>
   <si>
     <t>HUMB. CANALE DENARIO RESERVA CAB. FRANC</t>
@@ -35925,7 +35925,7 @@
         <v>6252</v>
       </c>
       <c r="D463" t="s">
-        <v>7468</v>
+        <v>7469</v>
       </c>
       <c r="E463" t="s">
         <v>8030</v>
@@ -35945,7 +35945,7 @@
         <v>6253</v>
       </c>
       <c r="D464" t="s">
-        <v>7469</v>
+        <v>7470</v>
       </c>
       <c r="E464" t="s">
         <v>8030</v>
@@ -35988,7 +35988,7 @@
         <v>6254</v>
       </c>
       <c r="D466" t="s">
-        <v>7470</v>
+        <v>7471</v>
       </c>
       <c r="E466" t="s">
         <v>8030</v>
@@ -36008,7 +36008,7 @@
         <v>6122</v>
       </c>
       <c r="D467" t="s">
-        <v>7471</v>
+        <v>7468</v>
       </c>
       <c r="E467" t="s">
         <v>8030</v>
@@ -36028,7 +36028,7 @@
         <v>6255</v>
       </c>
       <c r="D468" t="s">
-        <v>7468</v>
+        <v>7469</v>
       </c>
       <c r="E468" t="s">
         <v>8030</v>
@@ -36048,7 +36048,7 @@
         <v>6092</v>
       </c>
       <c r="D469" t="s">
-        <v>7471</v>
+        <v>7468</v>
       </c>
       <c r="E469" t="s">
         <v>8030</v>
@@ -36068,7 +36068,7 @@
         <v>6066</v>
       </c>
       <c r="D470" t="s">
-        <v>7468</v>
+        <v>7469</v>
       </c>
       <c r="E470" t="s">
         <v>8030</v>
@@ -62732,7 +62732,7 @@
         <v>6622</v>
       </c>
       <c r="D1679" t="s">
-        <v>7471</v>
+        <v>7468</v>
       </c>
       <c r="E1679" t="s">
         <v>8059</v>
@@ -64204,7 +64204,7 @@
         <v>6127</v>
       </c>
       <c r="D1743" t="s">
-        <v>7469</v>
+        <v>7470</v>
       </c>
       <c r="E1743" t="s">
         <v>8059</v>
@@ -93414,7 +93414,7 @@
         <v>6711</v>
       </c>
       <c r="D3112" t="s">
-        <v>7769</v>
+        <v>7426</v>
       </c>
       <c r="E3112" t="s">
         <v>8129</v>
@@ -93437,7 +93437,7 @@
         <v>6019</v>
       </c>
       <c r="D3113" t="s">
-        <v>7623</v>
+        <v>7624</v>
       </c>
       <c r="E3113" t="s">
         <v>8129</v>

--- a/nao_positivados_06-2026.xlsx
+++ b/nao_positivados_06-2026.xlsx
@@ -22678,517 +22678,517 @@
     <t>CHAMP. VEUVE CLICQUOT BRUT 750 ML</t>
   </si>
   <si>
-    <t>VINHO TINTO QUINTA DE VENTOZELO SOUSAO</t>
+    <t>VINHO QUINTA DE VENTOZELO TINTA AMARELA</t>
   </si>
   <si>
     <t>VINHO MARQUES DE TEJARES FINCA DE LA FAM</t>
   </si>
   <si>
+    <t>VINHO LA TOGATA BRUNELLO ETQ AZUL 750ML</t>
+  </si>
+  <si>
+    <t>VINHO FREIXO TERROIR BRANCO 750ML</t>
+  </si>
+  <si>
+    <t>VINHO BAROLO BUSSIA RISERVA 750ML</t>
+  </si>
+  <si>
     <t>VINHO LA TOGATA ROSSO 750ML</t>
   </si>
   <si>
-    <t>VINHO LA TOGATA BRUNELLO ETQ AZUL 750ML</t>
-  </si>
-  <si>
-    <t>VINHO FREIXO TERROIR BRANCO 750ML</t>
+    <t>HUMB. CANALE DENARIO RESERVA CAB. FRANC</t>
+  </si>
+  <si>
+    <t>NECTAR ABACAXI 12X1000ML</t>
+  </si>
+  <si>
+    <t>WHISKY BUCHANANS 12 YEARS 1L</t>
+  </si>
+  <si>
+    <t>RUM MONTILLA CARTA BRANCA 1L</t>
+  </si>
+  <si>
+    <t>WHISKY JIM BEAM HONEY 1L</t>
+  </si>
+  <si>
+    <t>WHISKY JACK DANIELS APPLE 1L - DEST</t>
+  </si>
+  <si>
+    <t>WHISKY PASSPORT HONEY 670ML</t>
+  </si>
+  <si>
+    <t>MARTINI ROSATO 750 ML</t>
+  </si>
+  <si>
+    <t>AGUARDENTE OLD CESAR 88 965 ML</t>
+  </si>
+  <si>
+    <t>VODKA CIROC 750 ML</t>
+  </si>
+  <si>
+    <t>GIN BEEFEATER BLACKBERRY 700ML</t>
+  </si>
+  <si>
+    <t>LICOR STOCK COCONUT 720 ML</t>
+  </si>
+  <si>
+    <t>SMIRNOFF ICE 24X275ML LONG</t>
+  </si>
+  <si>
+    <t>WHISKY CHANCELER 1L</t>
+  </si>
+  <si>
+    <t>VODKA ORLOFF 1L</t>
+  </si>
+  <si>
+    <t>ESPUMANTE CHANDON BRUT ROSE 750ML</t>
+  </si>
+  <si>
+    <t>RUM BACARDI CARTA BLANCA 980ML</t>
+  </si>
+  <si>
+    <t>VODCA BAM CIROC RED BERRY 750ML</t>
+  </si>
+  <si>
+    <t>GIN BEEFEATER BOTANICS 750ML</t>
+  </si>
+  <si>
+    <t>LICOR FIREBALL 750ML</t>
+  </si>
+  <si>
+    <t>CHANDON PASSION ROSE 750ML</t>
+  </si>
+  <si>
+    <t>WHISKY MAKERS MARK 750ML</t>
+  </si>
+  <si>
+    <t>GIN BEEFEATER PINK 750ML</t>
+  </si>
+  <si>
+    <t>WHISKY WHITE HORSE - 1L</t>
+  </si>
+  <si>
+    <t>CHANDON PASSION ON ICE 750 ML</t>
+  </si>
+  <si>
+    <t>RC ATUM PEDACOS EM OLEO 24X140G</t>
+  </si>
+  <si>
+    <t>VINHO FREIXO TERROIR TINTO 750ML</t>
+  </si>
+  <si>
+    <t>SABOR DO SABOR GIN + COMBO MELANCIA</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 473ML (LATAO) - 12 UNID</t>
+  </si>
+  <si>
+    <t>NECTAR MANGA 12X1000ML</t>
+  </si>
+  <si>
+    <t>ST PIERRE ZERO LATA GREEN APPLE 24X310ML</t>
+  </si>
+  <si>
+    <t>LICOR CAN FIREBALL CX C/ 6X50ML</t>
+  </si>
+  <si>
+    <t>STEINHAGER LOEWE 960ML</t>
+  </si>
+  <si>
+    <t>RUM BACARDI SUPERIOR 980ML</t>
+  </si>
+  <si>
+    <t>MARTINI ROSSO 750 ML</t>
+  </si>
+  <si>
+    <t>ESPUMANTE ARESTI ROSE 187,5ML</t>
+  </si>
+  <si>
+    <t>GIN GORDONS 750 ML</t>
+  </si>
+  <si>
+    <t>SMIRNOFF RED PET 1750 ML</t>
+  </si>
+  <si>
+    <t>AZEITE DE OLIVA EV ESSENZA COZINHAR 5L</t>
+  </si>
+  <si>
+    <t>GIN BOMBAY SAPPHIRE 750ML</t>
+  </si>
+  <si>
+    <t>CERVEJA AMSTEL ULTRA 473 ML</t>
+  </si>
+  <si>
+    <t>COMARY MELFORT COQUETEL DE MEL 1L</t>
+  </si>
+  <si>
+    <t>ICE 51 LIMAO LONG NECK 24X275ML</t>
+  </si>
+  <si>
+    <t>CACHACA YPIOCA 150YO 700ML</t>
+  </si>
+  <si>
+    <t>CERVEJA AMSTEL PURO MALTE 473 ML</t>
+  </si>
+  <si>
+    <t>VINHO CASA PERINI CHARDONNAY 750ML</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN LN 330ML DESC 4X6UN</t>
+  </si>
+  <si>
+    <t>CERVEJA AMSTEL LAGER 0,269LT SHR 12UNPBR</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN - KEG 5 LITROS C/2 DESC</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MORANGO C/21 UN</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT HORTELA C/21 UN</t>
+  </si>
+  <si>
+    <t>NG BARRA 80G 40% MEIO AMARGO (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL SF AMORA</t>
+  </si>
+  <si>
+    <t>PINATI NUTS BANANA 16X4X30G</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G CROCANTE (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL MELANCIA</t>
+  </si>
+  <si>
+    <t>GIN MARINA 750ML</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G AMENDOIM (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>RANCHEIRO RECHEADO BAUNILHA 90G</t>
+  </si>
+  <si>
+    <t>ST PIERRE LATA MARGARITA LT 6X270ML</t>
+  </si>
+  <si>
+    <t>RC SARDINHA 125G OLEO (05 UND)</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA BOMBOM 200G BRANCO</t>
+  </si>
+  <si>
+    <t>ST PIERRE LATA SUGAR FREE LT 24X270ML</t>
+  </si>
+  <si>
+    <t>WHISKY GENTLEMAN JACK 1L</t>
+  </si>
+  <si>
+    <t>BALA HALLS EXTRA FORTE C/21 UND</t>
+  </si>
+  <si>
+    <t>ST PIERRE ZERO LATA TROPICAL LT 6X310ML</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT FRESH INTENSE C/21 UN</t>
+  </si>
+  <si>
+    <t>RC SARDINHA 125G TOMATE (05 UND)</t>
+  </si>
+  <si>
+    <t>ST PIERRE ZERO LATA GUARANA  LT 6X310ML</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G P&amp;B (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G AO LEITE (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>ST PIERRE LATA AGUA TONICA TRAD 24X270ML</t>
+  </si>
+  <si>
+    <t>CACHAÇA JOIA DA SERRA TRADICIONAL 1L</t>
+  </si>
+  <si>
+    <t>GIN GORDONS PINK 700ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL MORANGO PESSEGO</t>
+  </si>
+  <si>
+    <t>VINHO LATITUD 33 MALBEC 750 ML</t>
+  </si>
+  <si>
+    <t>MACALLAN DOUBLE CASK 12Y 700ML</t>
+  </si>
+  <si>
+    <t>HUMB. CANALE DENARIO RESERVA PINOT NOIR</t>
+  </si>
+  <si>
+    <t>TEQUILA DON JULIO BLANCO 750ML</t>
+  </si>
+  <si>
+    <t>CHAMPAGNE RUINART BLANC DE BLANCS 750ML</t>
+  </si>
+  <si>
+    <t>NAVEIA ORIGINAL 12X1L</t>
+  </si>
+  <si>
+    <t>NAVEIA BARISTA 12X1L</t>
+  </si>
+  <si>
+    <t>VODKA GREY GOOSE LE CITRON 750ML</t>
+  </si>
+  <si>
+    <t>RC SARDINHA EM OLEO 125G</t>
+  </si>
+  <si>
+    <t>PINATI NUTS COCO 16X4X25G</t>
+  </si>
+  <si>
+    <t>DP DADINHO TRAD SACHE 90G</t>
+  </si>
+  <si>
+    <t>PINATI SLIM WHEY BEIJINHO 16X35G</t>
+  </si>
+  <si>
+    <t>PINATI NUTS ZERO COCO 16X4X25G</t>
+  </si>
+  <si>
+    <t>RUM BACARDI SUPERIOR 700ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL SF POMELO 4X250ML</t>
+  </si>
+  <si>
+    <t>4 PACK RED BULL SF NECTARINA 4X250ML</t>
+  </si>
+  <si>
+    <t>LICOR BALLENA MORANGO 750 ML</t>
+  </si>
+  <si>
+    <t>ESPUMANTE ALUD BRANCO 750ML</t>
+  </si>
+  <si>
+    <t>WHISKY JACK DANIELS SINATRA 1L</t>
+  </si>
+  <si>
+    <t>VINHO BRANCO JURUPINGA DINALLE 975 ML</t>
+  </si>
+  <si>
+    <t>GIN ROCKS 1LT</t>
+  </si>
+  <si>
+    <t>WHISKY J WALKER GOLD LABEL RESERVE 750ML</t>
+  </si>
+  <si>
+    <t>APERITIVO CAMPARI 998ML</t>
+  </si>
+  <si>
+    <t>VODKA SMIRNOFF 600 ML</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MELANCIA C/21 UN</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT FRESH HERBAL C/21 UN</t>
+  </si>
+  <si>
+    <t>DP PACOCA GAMADINHO POTE 50X15G</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MENTA C/21 UN</t>
+  </si>
+  <si>
+    <t>CHICLETE BUBBALOO HORTELA C/60 UN</t>
+  </si>
+  <si>
+    <t>NG BARRA 360G 40% MEIO AMARGO (DP 40X9G)</t>
+  </si>
+  <si>
+    <t>NG NEUGEBAUER HITS 200G BOMBOM SORTIDO</t>
+  </si>
+  <si>
+    <t>PINATI SLIM WHEY BRIGADEIRO 16X35G</t>
+  </si>
+  <si>
+    <t>PINATI DB WHEY FRAPE DE COCO 12X50G</t>
+  </si>
+  <si>
+    <t>PACOCA GAMADINHO 100X15G</t>
+  </si>
+  <si>
+    <t>VINHO ARESTI ESTATE S.  ROSE 187ML</t>
+  </si>
+  <si>
+    <t>PINATI SWEET COCADINHA CHOCO 24X14G</t>
+  </si>
+  <si>
+    <t>BALA HALLS MORANGO C/21 UND</t>
+  </si>
+  <si>
+    <t>PF MENTOS STICK 14 B. FRUTAS DP/16</t>
+  </si>
+  <si>
+    <t>VEUVE CLICQUOT BRUT 750 ML</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT TUTTI FRUTI C/ 14 UND</t>
+  </si>
+  <si>
+    <t>BOM AR AERO 360 ML ALEGRIA</t>
+  </si>
+  <si>
+    <t>WHISKY JAMESON CASKMATES IPA 750ML</t>
+  </si>
+  <si>
+    <t>AZEITE DE OLIVA EV ESSENZA 5L</t>
+  </si>
+  <si>
+    <t>NG BIBS 720G AMENDOLATE (DP 18X40G)</t>
+  </si>
+  <si>
+    <t>RC ATUM RALADO MOLHO DE TOMATE 170G</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT SENSE BLUEB C/21 UN</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MAX RASPEBERRY 14X16,5G</t>
+  </si>
+  <si>
+    <t>JACK DANIELS HONEY 1 L</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MENTA C/ 14 UND</t>
+  </si>
+  <si>
+    <t>BALA HALLS CEREJA C/21 UND</t>
+  </si>
+  <si>
+    <t>PF MENTOS STICK 14 B. RAINBOW DP/16</t>
+  </si>
+  <si>
+    <t>NG BARRA NEUGE 80G BRANCO (DP 16X80G)</t>
+  </si>
+  <si>
+    <t>CHICLETE BUBBALOO TUTTI FRUTI C/60 UN</t>
+  </si>
+  <si>
+    <t>BOM AR AERO 360 ML PEONIA</t>
+  </si>
+  <si>
+    <t>INSETICIDA SBP 360 ML ULTRA BARREIRA</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT GRF MENTA 6X54G</t>
+  </si>
+  <si>
+    <t>PINATI SIMPLE WHEY PISTACHE 16X35G</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA BOMBOM BRANCO 500G</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA 200GR DUO (DP10 X20G)</t>
+  </si>
+  <si>
+    <t>WHISKY BALLANTINE S FINEST 750ML</t>
+  </si>
+  <si>
+    <t>LICOR SAINT GERMAIN 750 ML</t>
+  </si>
+  <si>
+    <t>CHICLETE TRIDENT MAX MENTABERRY 14X16,5G</t>
+  </si>
+  <si>
+    <t>NG AMOR CARIOCA BOMBOM 200G (10X20G)</t>
+  </si>
+  <si>
+    <t>BOM AR AERO 360 ML CHEIRO DE TALCO</t>
+  </si>
+  <si>
+    <t>NAPOLITANO STICKS 16X29G</t>
+  </si>
+  <si>
+    <t>RC ATUM PEDACOS EM OLEO 170G</t>
+  </si>
+  <si>
+    <t>PINATI NUTS BANANA 20X30G</t>
+  </si>
+  <si>
+    <t>DP DADINHO BITZ AO LEITE 105G</t>
+  </si>
+  <si>
+    <t>RANCHEIRO WAFER LIMAO 78G</t>
+  </si>
+  <si>
+    <t>LICOR STOCK PESSEGO 720 ML</t>
+  </si>
+  <si>
+    <t>XAROPE MONIN MACA VERDE (APPLE) 700 ML</t>
+  </si>
+  <si>
+    <t>VINHO LATITUD 33 MALBEC  750 ML</t>
+  </si>
+  <si>
+    <t>RED BULL SF NECTARINA 24X250ML</t>
+  </si>
+  <si>
+    <t>AMARULA C LIQUEUR 750 ML + 1 COPO</t>
+  </si>
+  <si>
+    <t>WHISKY J WALKER GREEN LABEL - 750ML</t>
+  </si>
+  <si>
+    <t>AGUA MINERAL MAMBA WATER C/ GAS 12X350ML</t>
+  </si>
+  <si>
+    <t>RED BULL SF BLUEBERRY BAUNILHA  24X250ML</t>
+  </si>
+  <si>
+    <t>XAROPE CHERRY MARIE BRIZARD 700ML</t>
+  </si>
+  <si>
+    <t>AGUA MINERAL MINALBA S/GAS LATA 12X310ML</t>
+  </si>
+  <si>
+    <t>LICOR COINTREAU 700 ML</t>
+  </si>
+  <si>
+    <t>VINHO TTO BERTOLI CHIANTI DOCG 750ML</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN ZERO LONG  24X330ML</t>
+  </si>
+  <si>
+    <t>FRISANTE MACAW TROPICAL MOSC. ROSE 750ML</t>
+  </si>
+  <si>
+    <t>FRISANTE MACAW TROPICAL MOSCATO 750ML</t>
+  </si>
+  <si>
+    <t>ESPUMANTE ARESTI CHARDONNAY 187,5ML</t>
+  </si>
+  <si>
+    <t>GIN INVICTUS MELANCIA 900ML</t>
+  </si>
+  <si>
+    <t>WHISKY CHIVAS XV GOLD 700ML</t>
+  </si>
+  <si>
+    <t>TEQUILA EL JIMADOR REPOSADO 750 ML</t>
+  </si>
+  <si>
+    <t>NOSSO CHOP RED DRAFT VD 6X600ML</t>
   </si>
   <si>
     <t>VINHO BCO ARCAIA PINOT GRIGIO 750ML</t>
-  </si>
-  <si>
-    <t>VINHO BAROLO BUSSIA RISERVA 750ML</t>
-  </si>
-  <si>
-    <t>SPINOGLIO TIERRA ALTA VARIETALES TANNAT</t>
-  </si>
-  <si>
-    <t>NECTAR ABACAXI 12X1000ML</t>
-  </si>
-  <si>
-    <t>WHISKY BUCHANANS 12 YEARS 1L</t>
-  </si>
-  <si>
-    <t>RUM MONTILLA CARTA BRANCA 1L</t>
-  </si>
-  <si>
-    <t>WHISKY JIM BEAM HONEY 1L</t>
-  </si>
-  <si>
-    <t>WHISKY JACK DANIELS APPLE 1L - DEST</t>
-  </si>
-  <si>
-    <t>WHISKY PASSPORT HONEY 670ML</t>
-  </si>
-  <si>
-    <t>MARTINI ROSATO 750 ML</t>
-  </si>
-  <si>
-    <t>AGUARDENTE OLD CESAR 88 965 ML</t>
-  </si>
-  <si>
-    <t>VODKA CIROC 750 ML</t>
-  </si>
-  <si>
-    <t>GIN BEEFEATER BLACKBERRY 700ML</t>
-  </si>
-  <si>
-    <t>LICOR STOCK COCONUT 720 ML</t>
-  </si>
-  <si>
-    <t>SMIRNOFF ICE 24X275ML LONG</t>
-  </si>
-  <si>
-    <t>WHISKY CHANCELER 1L</t>
-  </si>
-  <si>
-    <t>VODKA ORLOFF 1L</t>
-  </si>
-  <si>
-    <t>ESPUMANTE CHANDON BRUT ROSE 750ML</t>
-  </si>
-  <si>
-    <t>RUM BACARDI CARTA BLANCA 980ML</t>
-  </si>
-  <si>
-    <t>VODCA BAM CIROC RED BERRY 750ML</t>
-  </si>
-  <si>
-    <t>GIN BEEFEATER BOTANICS 750ML</t>
-  </si>
-  <si>
-    <t>LICOR FIREBALL 750ML</t>
-  </si>
-  <si>
-    <t>CHANDON PASSION ROSE 750ML</t>
-  </si>
-  <si>
-    <t>WHISKY MAKERS MARK 750ML</t>
-  </si>
-  <si>
-    <t>GIN BEEFEATER PINK 750ML</t>
-  </si>
-  <si>
-    <t>WHISKY WHITE HORSE - 1L</t>
-  </si>
-  <si>
-    <t>CHANDON PASSION ON ICE 750 ML</t>
-  </si>
-  <si>
-    <t>RC ATUM PEDACOS EM OLEO 24X140G</t>
-  </si>
-  <si>
-    <t>VINHO FREIXO TERROIR TINTO 750ML</t>
-  </si>
-  <si>
-    <t>SABOR DO SABOR GIN + COMBO MELANCIA</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN 473ML (LATAO) - 12 UNID</t>
-  </si>
-  <si>
-    <t>NECTAR MANGA 12X1000ML</t>
-  </si>
-  <si>
-    <t>ST PIERRE ZERO LATA GREEN APPLE 24X310ML</t>
-  </si>
-  <si>
-    <t>LICOR CAN FIREBALL CX C/ 6X50ML</t>
-  </si>
-  <si>
-    <t>STEINHAGER LOEWE 960ML</t>
-  </si>
-  <si>
-    <t>RUM BACARDI SUPERIOR 980ML</t>
-  </si>
-  <si>
-    <t>MARTINI ROSSO 750 ML</t>
-  </si>
-  <si>
-    <t>ESPUMANTE ARESTI ROSE 187,5ML</t>
-  </si>
-  <si>
-    <t>GIN GORDONS 750 ML</t>
-  </si>
-  <si>
-    <t>SMIRNOFF RED PET 1750 ML</t>
-  </si>
-  <si>
-    <t>AZEITE DE OLIVA EV ESSENZA COZINHAR 5L</t>
-  </si>
-  <si>
-    <t>GIN BOMBAY SAPPHIRE 750ML</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL ULTRA 473 ML</t>
-  </si>
-  <si>
-    <t>COMARY MELFORT COQUETEL DE MEL 1L</t>
-  </si>
-  <si>
-    <t>ICE 51 LIMAO LONG NECK 24X275ML</t>
-  </si>
-  <si>
-    <t>CACHACA YPIOCA 150YO 700ML</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL PURO MALTE 473 ML</t>
-  </si>
-  <si>
-    <t>VINHO CASA PERINI CHARDONNAY 750ML</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN LN 330ML DESC 4X6UN</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL LAGER 0,269LT SHR 12UNPBR</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN - KEG 5 LITROS C/2 DESC</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MORANGO C/21 UN</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT HORTELA C/21 UN</t>
-  </si>
-  <si>
-    <t>NG BARRA 80G 40% MEIO AMARGO (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL SF AMORA</t>
-  </si>
-  <si>
-    <t>PINATI NUTS BANANA 16X4X30G</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G CROCANTE (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL MELANCIA</t>
-  </si>
-  <si>
-    <t>GIN MARINA 750ML</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G AMENDOIM (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>RANCHEIRO RECHEADO BAUNILHA 90G</t>
-  </si>
-  <si>
-    <t>ST PIERRE LATA MARGARITA LT 6X270ML</t>
-  </si>
-  <si>
-    <t>RC SARDINHA 125G OLEO (05 UND)</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA BOMBOM 200G BRANCO</t>
-  </si>
-  <si>
-    <t>ST PIERRE LATA SUGAR FREE LT 24X270ML</t>
-  </si>
-  <si>
-    <t>WHISKY GENTLEMAN JACK 1L</t>
-  </si>
-  <si>
-    <t>BALA HALLS EXTRA FORTE C/21 UND</t>
-  </si>
-  <si>
-    <t>ST PIERRE ZERO LATA TROPICAL LT 6X310ML</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT FRESH INTENSE C/21 UN</t>
-  </si>
-  <si>
-    <t>RC SARDINHA 125G TOMATE (05 UND)</t>
-  </si>
-  <si>
-    <t>ST PIERRE ZERO LATA GUARANA  LT 6X310ML</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G P&amp;B (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G AO LEITE (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>ST PIERRE LATA AGUA TONICA TRAD 24X270ML</t>
-  </si>
-  <si>
-    <t>CACHAÇA JOIA DA SERRA TRADICIONAL 1L</t>
-  </si>
-  <si>
-    <t>GIN GORDONS PINK 700ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL MORANGO PESSEGO</t>
-  </si>
-  <si>
-    <t>VINHO LATITUD 33 MALBEC 750 ML</t>
-  </si>
-  <si>
-    <t>MACALLAN DOUBLE CASK 12Y 700ML</t>
-  </si>
-  <si>
-    <t>HUMB. CANALE DENARIO RESERVA PINOT NOIR</t>
-  </si>
-  <si>
-    <t>TEQUILA DON JULIO BLANCO 750ML</t>
-  </si>
-  <si>
-    <t>CHAMPAGNE RUINART BLANC DE BLANCS 750ML</t>
-  </si>
-  <si>
-    <t>NAVEIA ORIGINAL 12X1L</t>
-  </si>
-  <si>
-    <t>NAVEIA BARISTA 12X1L</t>
-  </si>
-  <si>
-    <t>VODKA GREY GOOSE LE CITRON 750ML</t>
-  </si>
-  <si>
-    <t>RC SARDINHA EM OLEO 125G</t>
-  </si>
-  <si>
-    <t>PINATI NUTS COCO 16X4X25G</t>
-  </si>
-  <si>
-    <t>DP DADINHO TRAD SACHE 90G</t>
-  </si>
-  <si>
-    <t>PINATI SLIM WHEY BEIJINHO 16X35G</t>
-  </si>
-  <si>
-    <t>PINATI NUTS ZERO COCO 16X4X25G</t>
-  </si>
-  <si>
-    <t>RUM BACARDI SUPERIOR 700ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL SF POMELO 4X250ML</t>
-  </si>
-  <si>
-    <t>4 PACK RED BULL SF NECTARINA 4X250ML</t>
-  </si>
-  <si>
-    <t>LICOR BALLENA MORANGO 750 ML</t>
-  </si>
-  <si>
-    <t>ESPUMANTE ALUD BRANCO 750ML</t>
-  </si>
-  <si>
-    <t>WHISKY JACK DANIELS SINATRA 1L</t>
-  </si>
-  <si>
-    <t>VINHO BRANCO JURUPINGA DINALLE 975 ML</t>
-  </si>
-  <si>
-    <t>GIN ROCKS 1LT</t>
-  </si>
-  <si>
-    <t>WHISKY J WALKER GOLD LABEL RESERVE 750ML</t>
-  </si>
-  <si>
-    <t>APERITIVO CAMPARI 998ML</t>
-  </si>
-  <si>
-    <t>VODKA SMIRNOFF 600 ML</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MELANCIA C/21 UN</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT FRESH HERBAL C/21 UN</t>
-  </si>
-  <si>
-    <t>DP PACOCA GAMADINHO POTE 50X15G</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MENTA C/21 UN</t>
-  </si>
-  <si>
-    <t>CHICLETE BUBBALOO HORTELA C/60 UN</t>
-  </si>
-  <si>
-    <t>NG BARRA 360G 40% MEIO AMARGO (DP 40X9G)</t>
-  </si>
-  <si>
-    <t>NG NEUGEBAUER HITS 200G BOMBOM SORTIDO</t>
-  </si>
-  <si>
-    <t>PINATI SLIM WHEY BRIGADEIRO 16X35G</t>
-  </si>
-  <si>
-    <t>PINATI DB WHEY FRAPE DE COCO 12X50G</t>
-  </si>
-  <si>
-    <t>PACOCA GAMADINHO 100X15G</t>
-  </si>
-  <si>
-    <t>VINHO ARESTI ESTATE S.  ROSE 187ML</t>
-  </si>
-  <si>
-    <t>PINATI SWEET COCADINHA CHOCO 24X14G</t>
-  </si>
-  <si>
-    <t>BALA HALLS MORANGO C/21 UND</t>
-  </si>
-  <si>
-    <t>PF MENTOS STICK 14 B. FRUTAS DP/16</t>
-  </si>
-  <si>
-    <t>VEUVE CLICQUOT BRUT 750 ML</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT TUTTI FRUTI C/ 14 UND</t>
-  </si>
-  <si>
-    <t>BOM AR AERO 360 ML ALEGRIA</t>
-  </si>
-  <si>
-    <t>WHISKY JAMESON CASKMATES IPA 750ML</t>
-  </si>
-  <si>
-    <t>AZEITE DE OLIVA EV ESSENZA 5L</t>
-  </si>
-  <si>
-    <t>NG BIBS 720G AMENDOLATE (DP 18X40G)</t>
-  </si>
-  <si>
-    <t>RC ATUM RALADO MOLHO DE TOMATE 170G</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT SENSE BLUEB C/21 UN</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MAX RASPEBERRY 14X16,5G</t>
-  </si>
-  <si>
-    <t>JACK DANIELS HONEY 1 L</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MENTA C/ 14 UND</t>
-  </si>
-  <si>
-    <t>BALA HALLS CEREJA C/21 UND</t>
-  </si>
-  <si>
-    <t>PF MENTOS STICK 14 B. RAINBOW DP/16</t>
-  </si>
-  <si>
-    <t>NG BARRA NEUGE 80G BRANCO (DP 16X80G)</t>
-  </si>
-  <si>
-    <t>CHICLETE BUBBALOO TUTTI FRUTI C/60 UN</t>
-  </si>
-  <si>
-    <t>BOM AR AERO 360 ML PEONIA</t>
-  </si>
-  <si>
-    <t>INSETICIDA SBP 360 ML ULTRA BARREIRA</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT GRF MENTA 6X54G</t>
-  </si>
-  <si>
-    <t>PINATI SIMPLE WHEY PISTACHE 16X35G</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA BOMBOM BRANCO 500G</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA 200GR DUO (DP10 X20G)</t>
-  </si>
-  <si>
-    <t>WHISKY BALLANTINE S FINEST 750ML</t>
-  </si>
-  <si>
-    <t>LICOR SAINT GERMAIN 750 ML</t>
-  </si>
-  <si>
-    <t>CHICLETE TRIDENT MAX MENTABERRY 14X16,5G</t>
-  </si>
-  <si>
-    <t>NG AMOR CARIOCA BOMBOM 200G (10X20G)</t>
-  </si>
-  <si>
-    <t>BOM AR AERO 360 ML CHEIRO DE TALCO</t>
-  </si>
-  <si>
-    <t>NAPOLITANO STICKS 16X29G</t>
-  </si>
-  <si>
-    <t>RC ATUM PEDACOS EM OLEO 170G</t>
-  </si>
-  <si>
-    <t>PINATI NUTS BANANA 20X30G</t>
-  </si>
-  <si>
-    <t>DP DADINHO BITZ AO LEITE 105G</t>
-  </si>
-  <si>
-    <t>RANCHEIRO WAFER LIMAO 78G</t>
-  </si>
-  <si>
-    <t>LICOR STOCK PESSEGO 720 ML</t>
-  </si>
-  <si>
-    <t>XAROPE MONIN MACA VERDE (APPLE) 700 ML</t>
-  </si>
-  <si>
-    <t>VINHO LATITUD 33 MALBEC  750 ML</t>
-  </si>
-  <si>
-    <t>RED BULL SF NECTARINA 24X250ML</t>
-  </si>
-  <si>
-    <t>AMARULA C LIQUEUR 750 ML + 1 COPO</t>
-  </si>
-  <si>
-    <t>WHISKY J WALKER GREEN LABEL - 750ML</t>
-  </si>
-  <si>
-    <t>AGUA MINERAL MAMBA WATER C/ GAS 12X350ML</t>
-  </si>
-  <si>
-    <t>RED BULL SF BLUEBERRY BAUNILHA  24X250ML</t>
-  </si>
-  <si>
-    <t>XAROPE CHERRY MARIE BRIZARD 700ML</t>
-  </si>
-  <si>
-    <t>AGUA MINERAL MINALBA S/GAS LATA 12X310ML</t>
-  </si>
-  <si>
-    <t>LICOR COINTREAU 700 ML</t>
-  </si>
-  <si>
-    <t>VINHO TTO BERTOLI CHIANTI DOCG 750ML</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN ZERO LONG  24X330ML</t>
-  </si>
-  <si>
-    <t>FRISANTE MACAW TROPICAL MOSC. ROSE 750ML</t>
-  </si>
-  <si>
-    <t>FRISANTE MACAW TROPICAL MOSCATO 750ML</t>
-  </si>
-  <si>
-    <t>ESPUMANTE ARESTI CHARDONNAY 187,5ML</t>
-  </si>
-  <si>
-    <t>GIN INVICTUS MELANCIA 900ML</t>
-  </si>
-  <si>
-    <t>WHISKY CHIVAS XV GOLD 700ML</t>
-  </si>
-  <si>
-    <t>TEQUILA EL JIMADOR REPOSADO 750 ML</t>
-  </si>
-  <si>
-    <t>NOSSO CHOP RED DRAFT VD 6X600ML</t>
   </si>
   <si>
     <t>VINHO FOODKILLER CARMENERE 750ML</t>
@@ -36120,7 +36120,7 @@
         <v>6315</v>
       </c>
       <c r="D457" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E457" t="s">
         <v>8125</v>
@@ -36140,7 +36140,7 @@
         <v>6316</v>
       </c>
       <c r="D458" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E458" t="s">
         <v>8125</v>
@@ -36160,7 +36160,7 @@
         <v>6290</v>
       </c>
       <c r="D459" t="s">
-        <v>7559</v>
+        <v>7491</v>
       </c>
       <c r="E459" t="s">
         <v>8125</v>
@@ -36183,7 +36183,7 @@
         <v>6317</v>
       </c>
       <c r="D460" t="s">
-        <v>7560</v>
+        <v>7558</v>
       </c>
       <c r="E460" t="s">
         <v>8125</v>
@@ -36203,7 +36203,7 @@
         <v>6187</v>
       </c>
       <c r="D461" t="s">
-        <v>7556</v>
+        <v>7559</v>
       </c>
       <c r="E461" t="s">
         <v>8125</v>
@@ -36223,7 +36223,7 @@
         <v>6318</v>
       </c>
       <c r="D462" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E462" t="s">
         <v>8125</v>
@@ -36243,7 +36243,7 @@
         <v>6132</v>
       </c>
       <c r="D463" t="s">
-        <v>7557</v>
+        <v>7556</v>
       </c>
       <c r="E463" t="s">
         <v>8125</v>
@@ -36263,7 +36263,7 @@
         <v>6319</v>
       </c>
       <c r="D464" t="s">
-        <v>7561</v>
+        <v>7560</v>
       </c>
       <c r="E464" t="s">
         <v>8125</v>
@@ -36283,7 +36283,7 @@
         <v>6320</v>
       </c>
       <c r="D465" t="s">
-        <v>7562</v>
+        <v>7561</v>
       </c>
       <c r="E465" t="s">
         <v>8126</v>
@@ -36352,7 +36352,7 @@
         <v>6322</v>
       </c>
       <c r="D468" t="s">
-        <v>7563</v>
+        <v>7562</v>
       </c>
       <c r="E468" t="s">
         <v>8126</v>
@@ -36375,7 +36375,7 @@
         <v>6323</v>
       </c>
       <c r="D469" t="s">
-        <v>7563</v>
+        <v>7562</v>
       </c>
       <c r="E469" t="s">
         <v>8127</v>
@@ -36395,7 +36395,7 @@
         <v>6324</v>
       </c>
       <c r="D470" t="s">
-        <v>7563</v>
+        <v>7562</v>
       </c>
       <c r="E470" t="s">
         <v>8127</v>
@@ -36495,7 +36495,7 @@
         <v>6329</v>
       </c>
       <c r="D475" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E475" t="s">
         <v>8127</v>
@@ -36635,7 +36635,7 @@
         <v>6334</v>
       </c>
       <c r="D482" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E482" t="s">
         <v>8127</v>
@@ -36655,7 +36655,7 @@
         <v>6335</v>
       </c>
       <c r="D483" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E483" t="s">
         <v>8127</v>
@@ -36715,7 +36715,7 @@
         <v>6338</v>
       </c>
       <c r="D486" t="s">
-        <v>7567</v>
+        <v>7566</v>
       </c>
       <c r="E486" t="s">
         <v>8127</v>
@@ -36775,7 +36775,7 @@
         <v>6332</v>
       </c>
       <c r="D489" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E489" t="s">
         <v>8127</v>
@@ -36935,7 +36935,7 @@
         <v>6348</v>
       </c>
       <c r="D497" t="s">
-        <v>7568</v>
+        <v>7567</v>
       </c>
       <c r="E497" t="s">
         <v>8127</v>
@@ -37055,7 +37055,7 @@
         <v>6150</v>
       </c>
       <c r="D503" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E503" t="s">
         <v>8127</v>
@@ -37115,7 +37115,7 @@
         <v>6354</v>
       </c>
       <c r="D506" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E506" t="s">
         <v>8127</v>
@@ -37295,7 +37295,7 @@
         <v>6361</v>
       </c>
       <c r="D515" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E515" t="s">
         <v>8127</v>
@@ -37315,7 +37315,7 @@
         <v>6362</v>
       </c>
       <c r="D516" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E516" t="s">
         <v>8127</v>
@@ -37438,7 +37438,7 @@
         <v>6367</v>
       </c>
       <c r="D522" t="s">
-        <v>7570</v>
+        <v>7569</v>
       </c>
       <c r="E522" t="s">
         <v>8129</v>
@@ -37458,7 +37458,7 @@
         <v>6368</v>
       </c>
       <c r="D523" t="s">
-        <v>7571</v>
+        <v>7570</v>
       </c>
       <c r="E523" t="s">
         <v>8130</v>
@@ -37538,7 +37538,7 @@
         <v>6371</v>
       </c>
       <c r="D527" t="s">
-        <v>7572</v>
+        <v>7571</v>
       </c>
       <c r="E527" t="s">
         <v>8130</v>
@@ -37618,7 +37618,7 @@
         <v>6375</v>
       </c>
       <c r="D531" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E531" t="s">
         <v>8130</v>
@@ -37638,7 +37638,7 @@
         <v>6376</v>
       </c>
       <c r="D532" t="s">
-        <v>7574</v>
+        <v>7573</v>
       </c>
       <c r="E532" t="s">
         <v>8130</v>
@@ -37698,7 +37698,7 @@
         <v>6150</v>
       </c>
       <c r="D535" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E535" t="s">
         <v>8130</v>
@@ -37778,7 +37778,7 @@
         <v>6378</v>
       </c>
       <c r="D539" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E539" t="s">
         <v>8130</v>
@@ -38061,7 +38061,7 @@
         <v>6387</v>
       </c>
       <c r="D553" t="s">
-        <v>7576</v>
+        <v>7575</v>
       </c>
       <c r="E553" t="s">
         <v>8132</v>
@@ -38081,7 +38081,7 @@
         <v>6388</v>
       </c>
       <c r="D554" t="s">
-        <v>7576</v>
+        <v>7575</v>
       </c>
       <c r="E554" t="s">
         <v>8132</v>
@@ -38141,7 +38141,7 @@
         <v>6391</v>
       </c>
       <c r="D557" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E557" t="s">
         <v>8132</v>
@@ -38181,7 +38181,7 @@
         <v>6393</v>
       </c>
       <c r="D559" t="s">
-        <v>7577</v>
+        <v>7576</v>
       </c>
       <c r="E559" t="s">
         <v>8132</v>
@@ -38401,7 +38401,7 @@
         <v>6403</v>
       </c>
       <c r="D570" t="s">
-        <v>7578</v>
+        <v>7577</v>
       </c>
       <c r="E570" t="s">
         <v>8132</v>
@@ -38441,7 +38441,7 @@
         <v>6405</v>
       </c>
       <c r="D572" t="s">
-        <v>7563</v>
+        <v>7562</v>
       </c>
       <c r="E572" t="s">
         <v>8132</v>
@@ -38481,7 +38481,7 @@
         <v>6406</v>
       </c>
       <c r="D574" t="s">
-        <v>7579</v>
+        <v>7578</v>
       </c>
       <c r="E574" t="s">
         <v>8132</v>
@@ -38521,7 +38521,7 @@
         <v>6407</v>
       </c>
       <c r="D576" t="s">
-        <v>7580</v>
+        <v>7579</v>
       </c>
       <c r="E576" t="s">
         <v>8133</v>
@@ -38581,7 +38581,7 @@
         <v>6410</v>
       </c>
       <c r="D579" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E579" t="s">
         <v>8133</v>
@@ -38601,7 +38601,7 @@
         <v>6411</v>
       </c>
       <c r="D580" t="s">
-        <v>7582</v>
+        <v>7581</v>
       </c>
       <c r="E580" t="s">
         <v>8133</v>
@@ -38621,7 +38621,7 @@
         <v>6412</v>
       </c>
       <c r="D581" t="s">
-        <v>7583</v>
+        <v>7582</v>
       </c>
       <c r="E581" t="s">
         <v>8133</v>
@@ -38641,7 +38641,7 @@
         <v>6413</v>
       </c>
       <c r="D582" t="s">
-        <v>7584</v>
+        <v>7583</v>
       </c>
       <c r="E582" t="s">
         <v>8133</v>
@@ -38833,7 +38833,7 @@
         <v>6320</v>
       </c>
       <c r="D591" t="s">
-        <v>7585</v>
+        <v>7584</v>
       </c>
       <c r="E591" t="s">
         <v>8135</v>
@@ -38853,7 +38853,7 @@
         <v>6416</v>
       </c>
       <c r="D592" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E592" t="s">
         <v>8135</v>
@@ -38922,7 +38922,7 @@
         <v>6179</v>
       </c>
       <c r="D595" t="s">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="E595" t="s">
         <v>8135</v>
@@ -39071,7 +39071,7 @@
         <v>6420</v>
       </c>
       <c r="D602" t="s">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="E602" t="s">
         <v>8135</v>
@@ -39091,7 +39091,7 @@
         <v>6067</v>
       </c>
       <c r="D603" t="s">
-        <v>7587</v>
+        <v>7586</v>
       </c>
       <c r="E603" t="s">
         <v>8135</v>
@@ -39180,7 +39180,7 @@
         <v>6285</v>
       </c>
       <c r="D607" t="s">
-        <v>7588</v>
+        <v>7587</v>
       </c>
       <c r="E607" t="s">
         <v>8135</v>
@@ -39223,7 +39223,7 @@
         <v>6098</v>
       </c>
       <c r="D609" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E609" t="s">
         <v>8135</v>
@@ -39266,7 +39266,7 @@
         <v>6422</v>
       </c>
       <c r="D611" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E611" t="s">
         <v>8135</v>
@@ -39332,7 +39332,7 @@
         <v>6423</v>
       </c>
       <c r="D614" t="s">
-        <v>7590</v>
+        <v>7589</v>
       </c>
       <c r="E614" t="s">
         <v>8135</v>
@@ -39352,7 +39352,7 @@
         <v>6424</v>
       </c>
       <c r="D615" t="s">
-        <v>7590</v>
+        <v>7589</v>
       </c>
       <c r="E615" t="s">
         <v>8135</v>
@@ -39481,7 +39481,7 @@
         <v>6062</v>
       </c>
       <c r="D621" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E621" t="s">
         <v>8135</v>
@@ -39524,7 +39524,7 @@
         <v>6067</v>
       </c>
       <c r="D623" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E623" t="s">
         <v>8135</v>
@@ -39564,7 +39564,7 @@
         <v>6320</v>
       </c>
       <c r="D625" t="s">
-        <v>7591</v>
+        <v>7590</v>
       </c>
       <c r="E625" t="s">
         <v>8135</v>
@@ -39607,7 +39607,7 @@
         <v>6422</v>
       </c>
       <c r="D627" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E627" t="s">
         <v>8135</v>
@@ -39630,7 +39630,7 @@
         <v>6320</v>
       </c>
       <c r="D628" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E628" t="s">
         <v>8135</v>
@@ -39676,7 +39676,7 @@
         <v>6067</v>
       </c>
       <c r="D630" t="s">
-        <v>7593</v>
+        <v>7592</v>
       </c>
       <c r="E630" t="s">
         <v>8135</v>
@@ -39722,7 +39722,7 @@
         <v>6172</v>
       </c>
       <c r="D632" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E632" t="s">
         <v>8135</v>
@@ -39742,7 +39742,7 @@
         <v>6098</v>
       </c>
       <c r="D633" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E633" t="s">
         <v>8135</v>
@@ -39805,7 +39805,7 @@
         <v>6422</v>
       </c>
       <c r="D636" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E636" t="s">
         <v>8135</v>
@@ -39828,7 +39828,7 @@
         <v>6320</v>
       </c>
       <c r="D637" t="s">
-        <v>7596</v>
+        <v>7595</v>
       </c>
       <c r="E637" t="s">
         <v>8135</v>
@@ -39983,7 +39983,7 @@
         <v>6067</v>
       </c>
       <c r="D644" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E644" t="s">
         <v>8135</v>
@@ -40003,7 +40003,7 @@
         <v>6067</v>
       </c>
       <c r="D645" t="s">
-        <v>7598</v>
+        <v>7597</v>
       </c>
       <c r="E645" t="s">
         <v>8135</v>
@@ -40023,7 +40023,7 @@
         <v>6108</v>
       </c>
       <c r="D646" t="s">
-        <v>7599</v>
+        <v>7598</v>
       </c>
       <c r="E646" t="s">
         <v>8135</v>
@@ -40066,7 +40066,7 @@
         <v>6429</v>
       </c>
       <c r="D648" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E648" t="s">
         <v>8136</v>
@@ -40086,7 +40086,7 @@
         <v>6430</v>
       </c>
       <c r="D649" t="s">
-        <v>7601</v>
+        <v>7600</v>
       </c>
       <c r="E649" t="s">
         <v>8136</v>
@@ -40126,7 +40126,7 @@
         <v>6432</v>
       </c>
       <c r="D651" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E651" t="s">
         <v>8136</v>
@@ -40146,7 +40146,7 @@
         <v>6433</v>
       </c>
       <c r="D652" t="s">
-        <v>7603</v>
+        <v>7602</v>
       </c>
       <c r="E652" t="s">
         <v>8136</v>
@@ -40169,7 +40169,7 @@
         <v>6434</v>
       </c>
       <c r="D653" t="s">
-        <v>7604</v>
+        <v>7603</v>
       </c>
       <c r="E653" t="s">
         <v>8136</v>
@@ -40301,7 +40301,7 @@
         <v>6437</v>
       </c>
       <c r="D659" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E659" t="s">
         <v>8136</v>
@@ -40321,7 +40321,7 @@
         <v>6438</v>
       </c>
       <c r="D660" t="s">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="E660" t="s">
         <v>8136</v>
@@ -40341,7 +40341,7 @@
         <v>6439</v>
       </c>
       <c r="D661" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E661" t="s">
         <v>8136</v>
@@ -40361,7 +40361,7 @@
         <v>6440</v>
       </c>
       <c r="D662" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E662" t="s">
         <v>8136</v>
@@ -40381,7 +40381,7 @@
         <v>6439</v>
       </c>
       <c r="D663" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E663" t="s">
         <v>8136</v>
@@ -40424,7 +40424,7 @@
         <v>6428</v>
       </c>
       <c r="D665" t="s">
-        <v>7606</v>
+        <v>7605</v>
       </c>
       <c r="E665" t="s">
         <v>8136</v>
@@ -40447,7 +40447,7 @@
         <v>6431</v>
       </c>
       <c r="D666" t="s">
-        <v>7606</v>
+        <v>7605</v>
       </c>
       <c r="E666" t="s">
         <v>8136</v>
@@ -40740,7 +40740,7 @@
         <v>6450</v>
       </c>
       <c r="D679" t="s">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="E679" t="s">
         <v>8136</v>
@@ -40760,7 +40760,7 @@
         <v>6451</v>
       </c>
       <c r="D680" t="s">
-        <v>7607</v>
+        <v>7606</v>
       </c>
       <c r="E680" t="s">
         <v>8136</v>
@@ -40780,7 +40780,7 @@
         <v>6452</v>
       </c>
       <c r="D681" t="s">
-        <v>7608</v>
+        <v>7607</v>
       </c>
       <c r="E681" t="s">
         <v>8136</v>
@@ -40800,7 +40800,7 @@
         <v>6182</v>
       </c>
       <c r="D682" t="s">
-        <v>7609</v>
+        <v>7608</v>
       </c>
       <c r="E682" t="s">
         <v>8136</v>
@@ -40843,7 +40843,7 @@
         <v>6454</v>
       </c>
       <c r="D684" t="s">
-        <v>7610</v>
+        <v>7609</v>
       </c>
       <c r="E684" t="s">
         <v>8137</v>
@@ -40863,7 +40863,7 @@
         <v>6455</v>
       </c>
       <c r="D685" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E685" t="s">
         <v>8137</v>
@@ -40883,7 +40883,7 @@
         <v>6456</v>
       </c>
       <c r="D686" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E686" t="s">
         <v>8137</v>
@@ -40903,7 +40903,7 @@
         <v>6457</v>
       </c>
       <c r="D687" t="s">
-        <v>7613</v>
+        <v>7612</v>
       </c>
       <c r="E687" t="s">
         <v>8137</v>
@@ -40923,7 +40923,7 @@
         <v>6456</v>
       </c>
       <c r="D688" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E688" t="s">
         <v>8137</v>
@@ -40943,7 +40943,7 @@
         <v>6458</v>
       </c>
       <c r="D689" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E689" t="s">
         <v>8137</v>
@@ -40963,7 +40963,7 @@
         <v>6459</v>
       </c>
       <c r="D690" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E690" t="s">
         <v>8137</v>
@@ -40983,7 +40983,7 @@
         <v>6456</v>
       </c>
       <c r="D691" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E691" t="s">
         <v>8137</v>
@@ -41026,7 +41026,7 @@
         <v>6461</v>
       </c>
       <c r="D693" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E693" t="s">
         <v>8137</v>
@@ -41118,7 +41118,7 @@
         <v>6463</v>
       </c>
       <c r="D697" t="s">
-        <v>7618</v>
+        <v>7617</v>
       </c>
       <c r="E697" t="s">
         <v>8137</v>
@@ -41181,7 +41181,7 @@
         <v>6466</v>
       </c>
       <c r="D700" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E700" t="s">
         <v>8137</v>
@@ -41204,7 +41204,7 @@
         <v>6467</v>
       </c>
       <c r="D701" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E701" t="s">
         <v>8137</v>
@@ -41227,7 +41227,7 @@
         <v>6468</v>
       </c>
       <c r="D702" t="s">
-        <v>7620</v>
+        <v>7619</v>
       </c>
       <c r="E702" t="s">
         <v>8137</v>
@@ -41287,7 +41287,7 @@
         <v>6471</v>
       </c>
       <c r="D705" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E705" t="s">
         <v>8137</v>
@@ -41307,7 +41307,7 @@
         <v>6472</v>
       </c>
       <c r="D706" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E706" t="s">
         <v>8137</v>
@@ -41327,7 +41327,7 @@
         <v>6473</v>
       </c>
       <c r="D707" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E707" t="s">
         <v>8137</v>
@@ -41347,7 +41347,7 @@
         <v>6461</v>
       </c>
       <c r="D708" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E708" t="s">
         <v>8137</v>
@@ -41393,7 +41393,7 @@
         <v>6475</v>
       </c>
       <c r="D710" t="s">
-        <v>7623</v>
+        <v>7622</v>
       </c>
       <c r="E710" t="s">
         <v>8137</v>
@@ -41439,7 +41439,7 @@
         <v>6477</v>
       </c>
       <c r="D712" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E712" t="s">
         <v>8137</v>
@@ -41479,7 +41479,7 @@
         <v>6479</v>
       </c>
       <c r="D714" t="s">
-        <v>7624</v>
+        <v>7623</v>
       </c>
       <c r="E714" t="s">
         <v>8137</v>
@@ -41499,7 +41499,7 @@
         <v>6480</v>
       </c>
       <c r="D715" t="s">
-        <v>7625</v>
+        <v>7624</v>
       </c>
       <c r="E715" t="s">
         <v>8137</v>
@@ -41519,7 +41519,7 @@
         <v>6467</v>
       </c>
       <c r="D716" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E716" t="s">
         <v>8137</v>
@@ -41542,7 +41542,7 @@
         <v>6481</v>
       </c>
       <c r="D717" t="s">
-        <v>7626</v>
+        <v>7625</v>
       </c>
       <c r="E717" t="s">
         <v>8137</v>
@@ -41562,7 +41562,7 @@
         <v>6482</v>
       </c>
       <c r="D718" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E718" t="s">
         <v>8137</v>
@@ -41585,7 +41585,7 @@
         <v>6483</v>
       </c>
       <c r="D719" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E719" t="s">
         <v>8137</v>
@@ -41766,7 +41766,7 @@
         <v>6490</v>
       </c>
       <c r="D727" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E727" t="s">
         <v>8137</v>
@@ -41855,7 +41855,7 @@
         <v>6484</v>
       </c>
       <c r="D731" t="s">
-        <v>7627</v>
+        <v>7626</v>
       </c>
       <c r="E731" t="s">
         <v>8137</v>
@@ -41875,7 +41875,7 @@
         <v>6494</v>
       </c>
       <c r="D732" t="s">
-        <v>7628</v>
+        <v>7627</v>
       </c>
       <c r="E732" t="s">
         <v>8137</v>
@@ -41898,7 +41898,7 @@
         <v>6454</v>
       </c>
       <c r="D733" t="s">
-        <v>7629</v>
+        <v>7628</v>
       </c>
       <c r="E733" t="s">
         <v>8137</v>
@@ -41921,7 +41921,7 @@
         <v>6495</v>
       </c>
       <c r="D734" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E734" t="s">
         <v>8137</v>
@@ -41941,7 +41941,7 @@
         <v>6454</v>
       </c>
       <c r="D735" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E735" t="s">
         <v>8137</v>
@@ -42007,7 +42007,7 @@
         <v>6366</v>
       </c>
       <c r="D738" t="s">
-        <v>7630</v>
+        <v>7629</v>
       </c>
       <c r="E738" t="s">
         <v>8137</v>
@@ -42030,7 +42030,7 @@
         <v>6498</v>
       </c>
       <c r="D739" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E739" t="s">
         <v>8137</v>
@@ -42053,7 +42053,7 @@
         <v>6499</v>
       </c>
       <c r="D740" t="s">
-        <v>7631</v>
+        <v>7630</v>
       </c>
       <c r="E740" t="s">
         <v>8137</v>
@@ -42099,7 +42099,7 @@
         <v>6500</v>
       </c>
       <c r="D742" t="s">
-        <v>7632</v>
+        <v>7631</v>
       </c>
       <c r="E742" t="s">
         <v>8137</v>
@@ -42239,7 +42239,7 @@
         <v>6503</v>
       </c>
       <c r="D749" t="s">
-        <v>7633</v>
+        <v>7632</v>
       </c>
       <c r="E749" t="s">
         <v>8139</v>
@@ -42259,7 +42259,7 @@
         <v>6504</v>
       </c>
       <c r="D750" t="s">
-        <v>7634</v>
+        <v>7633</v>
       </c>
       <c r="E750" t="s">
         <v>8139</v>
@@ -42319,7 +42319,7 @@
         <v>6507</v>
       </c>
       <c r="D753" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E753" t="s">
         <v>8139</v>
@@ -42402,7 +42402,7 @@
         <v>6479</v>
       </c>
       <c r="D757" t="s">
-        <v>7635</v>
+        <v>7634</v>
       </c>
       <c r="E757" t="s">
         <v>8141</v>
@@ -42422,7 +42422,7 @@
         <v>6511</v>
       </c>
       <c r="D758" t="s">
-        <v>7636</v>
+        <v>7635</v>
       </c>
       <c r="E758" t="s">
         <v>8142</v>
@@ -42445,7 +42445,7 @@
         <v>6512</v>
       </c>
       <c r="D759" t="s">
-        <v>7637</v>
+        <v>7636</v>
       </c>
       <c r="E759" t="s">
         <v>8142</v>
@@ -42583,7 +42583,7 @@
         <v>6320</v>
       </c>
       <c r="D765" t="s">
-        <v>7638</v>
+        <v>7637</v>
       </c>
       <c r="E765" t="s">
         <v>8142</v>
@@ -42606,7 +42606,7 @@
         <v>6516</v>
       </c>
       <c r="D766" t="s">
-        <v>7639</v>
+        <v>7638</v>
       </c>
       <c r="E766" t="s">
         <v>8142</v>
@@ -42629,7 +42629,7 @@
         <v>6328</v>
       </c>
       <c r="D767" t="s">
-        <v>7640</v>
+        <v>7639</v>
       </c>
       <c r="E767" t="s">
         <v>8142</v>
@@ -42718,7 +42718,7 @@
         <v>6484</v>
       </c>
       <c r="D771" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E771" t="s">
         <v>8143</v>
@@ -42741,7 +42741,7 @@
         <v>6520</v>
       </c>
       <c r="D772" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E772" t="s">
         <v>8143</v>
@@ -42787,7 +42787,7 @@
         <v>6522</v>
       </c>
       <c r="D774" t="s">
-        <v>7642</v>
+        <v>7641</v>
       </c>
       <c r="E774" t="s">
         <v>8143</v>
@@ -42827,7 +42827,7 @@
         <v>6524</v>
       </c>
       <c r="D776" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E776" t="s">
         <v>8143</v>
@@ -42850,7 +42850,7 @@
         <v>6166</v>
       </c>
       <c r="D777" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E777" t="s">
         <v>8143</v>
@@ -42873,7 +42873,7 @@
         <v>6525</v>
       </c>
       <c r="D778" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E778" t="s">
         <v>8143</v>
@@ -42893,7 +42893,7 @@
         <v>6479</v>
       </c>
       <c r="D779" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E779" t="s">
         <v>8143</v>
@@ -42913,7 +42913,7 @@
         <v>6525</v>
       </c>
       <c r="D780" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E780" t="s">
         <v>8143</v>
@@ -42956,7 +42956,7 @@
         <v>6526</v>
       </c>
       <c r="D782" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E782" t="s">
         <v>8143</v>
@@ -42976,7 +42976,7 @@
         <v>6085</v>
       </c>
       <c r="D783" t="s">
-        <v>7642</v>
+        <v>7641</v>
       </c>
       <c r="E783" t="s">
         <v>8143</v>
@@ -42996,7 +42996,7 @@
         <v>6164</v>
       </c>
       <c r="D784" t="s">
-        <v>7642</v>
+        <v>7641</v>
       </c>
       <c r="E784" t="s">
         <v>8143</v>
@@ -43016,7 +43016,7 @@
         <v>6527</v>
       </c>
       <c r="D785" t="s">
-        <v>7642</v>
+        <v>7641</v>
       </c>
       <c r="E785" t="s">
         <v>8143</v>
@@ -43059,7 +43059,7 @@
         <v>6529</v>
       </c>
       <c r="D787" t="s">
-        <v>7643</v>
+        <v>7642</v>
       </c>
       <c r="E787" t="s">
         <v>8143</v>
@@ -43105,7 +43105,7 @@
         <v>6530</v>
       </c>
       <c r="D789" t="s">
-        <v>7644</v>
+        <v>7643</v>
       </c>
       <c r="E789" t="s">
         <v>8143</v>
@@ -43145,7 +43145,7 @@
         <v>6150</v>
       </c>
       <c r="D791" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E791" t="s">
         <v>8143</v>
@@ -43185,7 +43185,7 @@
         <v>6533</v>
       </c>
       <c r="D793" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E793" t="s">
         <v>8143</v>
@@ -43245,7 +43245,7 @@
         <v>6168</v>
       </c>
       <c r="D796" t="s">
-        <v>7645</v>
+        <v>7644</v>
       </c>
       <c r="E796" t="s">
         <v>8143</v>
@@ -43265,7 +43265,7 @@
         <v>6534</v>
       </c>
       <c r="D797" t="s">
-        <v>7646</v>
+        <v>7645</v>
       </c>
       <c r="E797" t="s">
         <v>8143</v>
@@ -43285,7 +43285,7 @@
         <v>6535</v>
       </c>
       <c r="D798" t="s">
-        <v>7646</v>
+        <v>7645</v>
       </c>
       <c r="E798" t="s">
         <v>8143</v>
@@ -43305,7 +43305,7 @@
         <v>6523</v>
       </c>
       <c r="D799" t="s">
-        <v>7646</v>
+        <v>7645</v>
       </c>
       <c r="E799" t="s">
         <v>8143</v>
@@ -43325,7 +43325,7 @@
         <v>6166</v>
       </c>
       <c r="D800" t="s">
-        <v>7646</v>
+        <v>7645</v>
       </c>
       <c r="E800" t="s">
         <v>8143</v>
@@ -43345,7 +43345,7 @@
         <v>6536</v>
       </c>
       <c r="D801" t="s">
-        <v>7646</v>
+        <v>7645</v>
       </c>
       <c r="E801" t="s">
         <v>8143</v>
@@ -43365,7 +43365,7 @@
         <v>6537</v>
       </c>
       <c r="D802" t="s">
-        <v>7646</v>
+        <v>7645</v>
       </c>
       <c r="E802" t="s">
         <v>8143</v>
@@ -43548,7 +43548,7 @@
         <v>6525</v>
       </c>
       <c r="D811" t="s">
-        <v>7568</v>
+        <v>7567</v>
       </c>
       <c r="E811" t="s">
         <v>8143</v>
@@ -43588,7 +43588,7 @@
         <v>6543</v>
       </c>
       <c r="D813" t="s">
-        <v>7645</v>
+        <v>7644</v>
       </c>
       <c r="E813" t="s">
         <v>8143</v>
@@ -43608,7 +43608,7 @@
         <v>6544</v>
       </c>
       <c r="D814" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E814" t="s">
         <v>8143</v>
@@ -43628,7 +43628,7 @@
         <v>6541</v>
       </c>
       <c r="D815" t="s">
-        <v>7568</v>
+        <v>7567</v>
       </c>
       <c r="E815" t="s">
         <v>8143</v>
@@ -43648,7 +43648,7 @@
         <v>6545</v>
       </c>
       <c r="D816" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E816" t="s">
         <v>8143</v>
@@ -43668,7 +43668,7 @@
         <v>6546</v>
       </c>
       <c r="D817" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E817" t="s">
         <v>8143</v>
@@ -43688,7 +43688,7 @@
         <v>6547</v>
       </c>
       <c r="D818" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E818" t="s">
         <v>8143</v>
@@ -43708,7 +43708,7 @@
         <v>6479</v>
       </c>
       <c r="D819" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E819" t="s">
         <v>8143</v>
@@ -43748,7 +43748,7 @@
         <v>6166</v>
       </c>
       <c r="D821" t="s">
-        <v>7647</v>
+        <v>7646</v>
       </c>
       <c r="E821" t="s">
         <v>8143</v>
@@ -43768,7 +43768,7 @@
         <v>6548</v>
       </c>
       <c r="D822" t="s">
-        <v>7648</v>
+        <v>7647</v>
       </c>
       <c r="E822" t="s">
         <v>8143</v>
@@ -43788,7 +43788,7 @@
         <v>6455</v>
       </c>
       <c r="D823" t="s">
-        <v>7649</v>
+        <v>7648</v>
       </c>
       <c r="E823" t="s">
         <v>8143</v>
@@ -43808,7 +43808,7 @@
         <v>6549</v>
       </c>
       <c r="D824" t="s">
-        <v>7648</v>
+        <v>7647</v>
       </c>
       <c r="E824" t="s">
         <v>8143</v>
@@ -43828,7 +43828,7 @@
         <v>6550</v>
       </c>
       <c r="D825" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E825" t="s">
         <v>8143</v>
@@ -43848,7 +43848,7 @@
         <v>6486</v>
       </c>
       <c r="D826" t="s">
-        <v>7647</v>
+        <v>7646</v>
       </c>
       <c r="E826" t="s">
         <v>8143</v>
@@ -43868,7 +43868,7 @@
         <v>6533</v>
       </c>
       <c r="D827" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E827" t="s">
         <v>8143</v>
@@ -43951,7 +43951,7 @@
         <v>6551</v>
       </c>
       <c r="D831" t="s">
-        <v>7650</v>
+        <v>7649</v>
       </c>
       <c r="E831" t="s">
         <v>8144</v>
@@ -43994,7 +43994,7 @@
         <v>6553</v>
       </c>
       <c r="D833" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E833" t="s">
         <v>8144</v>
@@ -44034,7 +44034,7 @@
         <v>6253</v>
       </c>
       <c r="D835" t="s">
-        <v>7651</v>
+        <v>7650</v>
       </c>
       <c r="E835" t="s">
         <v>8144</v>
@@ -44663,7 +44663,7 @@
         <v>6094</v>
       </c>
       <c r="D866" t="s">
-        <v>7652</v>
+        <v>7651</v>
       </c>
       <c r="E866" t="s">
         <v>8145</v>
@@ -44709,7 +44709,7 @@
         <v>6560</v>
       </c>
       <c r="D868" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E868" t="s">
         <v>8145</v>
@@ -44732,7 +44732,7 @@
         <v>6094</v>
       </c>
       <c r="D869" t="s">
-        <v>7652</v>
+        <v>7651</v>
       </c>
       <c r="E869" t="s">
         <v>8145</v>
@@ -44798,7 +44798,7 @@
         <v>6562</v>
       </c>
       <c r="D872" t="s">
-        <v>7654</v>
+        <v>7653</v>
       </c>
       <c r="E872" t="s">
         <v>8146</v>
@@ -44884,7 +44884,7 @@
         <v>6564</v>
       </c>
       <c r="D876" t="s">
-        <v>7655</v>
+        <v>7654</v>
       </c>
       <c r="E876" t="s">
         <v>8148</v>
@@ -44984,7 +44984,7 @@
         <v>6568</v>
       </c>
       <c r="D881" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E881" t="s">
         <v>8148</v>
@@ -45004,7 +45004,7 @@
         <v>6569</v>
       </c>
       <c r="D882" t="s">
-        <v>7656</v>
+        <v>7655</v>
       </c>
       <c r="E882" t="s">
         <v>8148</v>
@@ -45164,7 +45164,7 @@
         <v>6576</v>
       </c>
       <c r="D890" t="s">
-        <v>7657</v>
+        <v>7656</v>
       </c>
       <c r="E890" t="s">
         <v>8149</v>
@@ -45204,7 +45204,7 @@
         <v>6578</v>
       </c>
       <c r="D892" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E892" t="s">
         <v>8149</v>
@@ -45284,7 +45284,7 @@
         <v>6117</v>
       </c>
       <c r="D896" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E896" t="s">
         <v>8149</v>
@@ -45304,7 +45304,7 @@
         <v>6150</v>
       </c>
       <c r="D897" t="s">
-        <v>7626</v>
+        <v>7625</v>
       </c>
       <c r="E897" t="s">
         <v>8150</v>
@@ -45324,7 +45324,7 @@
         <v>6582</v>
       </c>
       <c r="D898" t="s">
-        <v>7660</v>
+        <v>7659</v>
       </c>
       <c r="E898" t="s">
         <v>8150</v>
@@ -45344,7 +45344,7 @@
         <v>6150</v>
       </c>
       <c r="D899" t="s">
-        <v>7661</v>
+        <v>7660</v>
       </c>
       <c r="E899" t="s">
         <v>8150</v>
@@ -45364,7 +45364,7 @@
         <v>6150</v>
       </c>
       <c r="D900" t="s">
-        <v>7662</v>
+        <v>7661</v>
       </c>
       <c r="E900" t="s">
         <v>8150</v>
@@ -45387,7 +45387,7 @@
         <v>6150</v>
       </c>
       <c r="D901" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E901" t="s">
         <v>8150</v>
@@ -45427,7 +45427,7 @@
         <v>6150</v>
       </c>
       <c r="D903" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E903" t="s">
         <v>8150</v>
@@ -45450,7 +45450,7 @@
         <v>6584</v>
       </c>
       <c r="D904" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E904" t="s">
         <v>8150</v>
@@ -45470,7 +45470,7 @@
         <v>6585</v>
       </c>
       <c r="D905" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E905" t="s">
         <v>8150</v>
@@ -45533,7 +45533,7 @@
         <v>6588</v>
       </c>
       <c r="D908" t="s">
-        <v>7664</v>
+        <v>7663</v>
       </c>
       <c r="E908" t="s">
         <v>8150</v>
@@ -45553,7 +45553,7 @@
         <v>6150</v>
       </c>
       <c r="D909" t="s">
-        <v>7665</v>
+        <v>7664</v>
       </c>
       <c r="E909" t="s">
         <v>8150</v>
@@ -45576,7 +45576,7 @@
         <v>6589</v>
       </c>
       <c r="D910" t="s">
-        <v>7666</v>
+        <v>7665</v>
       </c>
       <c r="E910" t="s">
         <v>8150</v>
@@ -45599,7 +45599,7 @@
         <v>6590</v>
       </c>
       <c r="D911" t="s">
-        <v>7667</v>
+        <v>7666</v>
       </c>
       <c r="E911" t="s">
         <v>8150</v>
@@ -45665,7 +45665,7 @@
         <v>6592</v>
       </c>
       <c r="D914" t="s">
-        <v>7668</v>
+        <v>7667</v>
       </c>
       <c r="E914" t="s">
         <v>8150</v>
@@ -45685,7 +45685,7 @@
         <v>6593</v>
       </c>
       <c r="D915" t="s">
-        <v>7669</v>
+        <v>7668</v>
       </c>
       <c r="E915" t="s">
         <v>8150</v>
@@ -45705,7 +45705,7 @@
         <v>6588</v>
       </c>
       <c r="D916" t="s">
-        <v>7670</v>
+        <v>7669</v>
       </c>
       <c r="E916" t="s">
         <v>8150</v>
@@ -45728,7 +45728,7 @@
         <v>6594</v>
       </c>
       <c r="D917" t="s">
-        <v>7671</v>
+        <v>7670</v>
       </c>
       <c r="E917" t="s">
         <v>8150</v>
@@ -45748,7 +45748,7 @@
         <v>6150</v>
       </c>
       <c r="D918" t="s">
-        <v>7672</v>
+        <v>7671</v>
       </c>
       <c r="E918" t="s">
         <v>8150</v>
@@ -45791,7 +45791,7 @@
         <v>6150</v>
       </c>
       <c r="D920" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E920" t="s">
         <v>8150</v>
@@ -45811,7 +45811,7 @@
         <v>6150</v>
       </c>
       <c r="D921" t="s">
-        <v>7673</v>
+        <v>7672</v>
       </c>
       <c r="E921" t="s">
         <v>8150</v>
@@ -45834,7 +45834,7 @@
         <v>6596</v>
       </c>
       <c r="D922" t="s">
-        <v>7674</v>
+        <v>7673</v>
       </c>
       <c r="E922" t="s">
         <v>8150</v>
@@ -45854,7 +45854,7 @@
         <v>6589</v>
       </c>
       <c r="D923" t="s">
-        <v>7651</v>
+        <v>7650</v>
       </c>
       <c r="E923" t="s">
         <v>8150</v>
@@ -45897,7 +45897,7 @@
         <v>6582</v>
       </c>
       <c r="D925" t="s">
-        <v>7675</v>
+        <v>7674</v>
       </c>
       <c r="E925" t="s">
         <v>8150</v>
@@ -45917,7 +45917,7 @@
         <v>6458</v>
       </c>
       <c r="D926" t="s">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="E926" t="s">
         <v>8150</v>
@@ -45986,7 +45986,7 @@
         <v>6598</v>
       </c>
       <c r="D929" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E929" t="s">
         <v>8150</v>
@@ -46006,7 +46006,7 @@
         <v>6278</v>
       </c>
       <c r="D930" t="s">
-        <v>7669</v>
+        <v>7668</v>
       </c>
       <c r="E930" t="s">
         <v>8150</v>
@@ -46069,7 +46069,7 @@
         <v>6150</v>
       </c>
       <c r="D933" t="s">
-        <v>7676</v>
+        <v>7675</v>
       </c>
       <c r="E933" t="s">
         <v>8150</v>
@@ -46115,7 +46115,7 @@
         <v>6599</v>
       </c>
       <c r="D935" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E935" t="s">
         <v>8150</v>
@@ -46138,7 +46138,7 @@
         <v>6600</v>
       </c>
       <c r="D936" t="s">
-        <v>7677</v>
+        <v>7676</v>
       </c>
       <c r="E936" t="s">
         <v>8150</v>
@@ -46158,7 +46158,7 @@
         <v>6150</v>
       </c>
       <c r="D937" t="s">
-        <v>7678</v>
+        <v>7677</v>
       </c>
       <c r="E937" t="s">
         <v>8150</v>
@@ -46204,7 +46204,7 @@
         <v>6601</v>
       </c>
       <c r="D939" t="s">
-        <v>7679</v>
+        <v>7678</v>
       </c>
       <c r="E939" t="s">
         <v>8150</v>
@@ -46224,7 +46224,7 @@
         <v>6602</v>
       </c>
       <c r="D940" t="s">
-        <v>7669</v>
+        <v>7668</v>
       </c>
       <c r="E940" t="s">
         <v>8150</v>
@@ -46247,7 +46247,7 @@
         <v>6278</v>
       </c>
       <c r="D941" t="s">
-        <v>7631</v>
+        <v>7630</v>
       </c>
       <c r="E941" t="s">
         <v>8150</v>
@@ -46267,7 +46267,7 @@
         <v>6588</v>
       </c>
       <c r="D942" t="s">
-        <v>7680</v>
+        <v>7679</v>
       </c>
       <c r="E942" t="s">
         <v>8150</v>
@@ -46307,7 +46307,7 @@
         <v>6588</v>
       </c>
       <c r="D944" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E944" t="s">
         <v>8150</v>
@@ -46347,7 +46347,7 @@
         <v>6605</v>
       </c>
       <c r="D946" t="s">
-        <v>7681</v>
+        <v>7680</v>
       </c>
       <c r="E946" t="s">
         <v>8150</v>
@@ -46390,7 +46390,7 @@
         <v>6607</v>
       </c>
       <c r="D948" t="s">
-        <v>7625</v>
+        <v>7624</v>
       </c>
       <c r="E948" t="s">
         <v>8150</v>
@@ -46410,7 +46410,7 @@
         <v>6150</v>
       </c>
       <c r="D949" t="s">
-        <v>7682</v>
+        <v>7681</v>
       </c>
       <c r="E949" t="s">
         <v>8150</v>
@@ -46430,7 +46430,7 @@
         <v>6150</v>
       </c>
       <c r="D950" t="s">
-        <v>7660</v>
+        <v>7659</v>
       </c>
       <c r="E950" t="s">
         <v>8150</v>
@@ -46453,7 +46453,7 @@
         <v>6150</v>
       </c>
       <c r="D951" t="s">
-        <v>7660</v>
+        <v>7659</v>
       </c>
       <c r="E951" t="s">
         <v>8150</v>
@@ -46473,7 +46473,7 @@
         <v>6608</v>
       </c>
       <c r="D952" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E952" t="s">
         <v>8150</v>
@@ -46493,7 +46493,7 @@
         <v>6150</v>
       </c>
       <c r="D953" t="s">
-        <v>7662</v>
+        <v>7661</v>
       </c>
       <c r="E953" t="s">
         <v>8150</v>
@@ -46556,7 +46556,7 @@
         <v>6150</v>
       </c>
       <c r="D956" t="s">
-        <v>7684</v>
+        <v>7683</v>
       </c>
       <c r="E956" t="s">
         <v>8150</v>
@@ -46576,7 +46576,7 @@
         <v>6585</v>
       </c>
       <c r="D957" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E957" t="s">
         <v>8150</v>
@@ -46596,7 +46596,7 @@
         <v>6150</v>
       </c>
       <c r="D958" t="s">
-        <v>7685</v>
+        <v>7684</v>
       </c>
       <c r="E958" t="s">
         <v>8150</v>
@@ -46636,7 +46636,7 @@
         <v>6609</v>
       </c>
       <c r="D960" t="s">
-        <v>7591</v>
+        <v>7590</v>
       </c>
       <c r="E960" t="s">
         <v>8150</v>
@@ -46682,7 +46682,7 @@
         <v>6150</v>
       </c>
       <c r="D962" t="s">
-        <v>7686</v>
+        <v>7685</v>
       </c>
       <c r="E962" t="s">
         <v>8150</v>
@@ -46702,7 +46702,7 @@
         <v>6150</v>
       </c>
       <c r="D963" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E963" t="s">
         <v>8150</v>
@@ -46722,7 +46722,7 @@
         <v>6150</v>
       </c>
       <c r="D964" t="s">
-        <v>7687</v>
+        <v>7686</v>
       </c>
       <c r="E964" t="s">
         <v>8150</v>
@@ -46762,7 +46762,7 @@
         <v>6150</v>
       </c>
       <c r="D966" t="s">
-        <v>7688</v>
+        <v>7687</v>
       </c>
       <c r="E966" t="s">
         <v>8150</v>
@@ -46782,7 +46782,7 @@
         <v>6599</v>
       </c>
       <c r="D967" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E967" t="s">
         <v>8150</v>
@@ -46805,7 +46805,7 @@
         <v>6588</v>
       </c>
       <c r="D968" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E968" t="s">
         <v>8150</v>
@@ -46868,7 +46868,7 @@
         <v>6611</v>
       </c>
       <c r="D971" t="s">
-        <v>7689</v>
+        <v>7688</v>
       </c>
       <c r="E971" t="s">
         <v>8150</v>
@@ -46891,7 +46891,7 @@
         <v>6612</v>
       </c>
       <c r="D972" t="s">
-        <v>7690</v>
+        <v>7689</v>
       </c>
       <c r="E972" t="s">
         <v>8150</v>
@@ -46957,7 +46957,7 @@
         <v>6150</v>
       </c>
       <c r="D975" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E975" t="s">
         <v>8150</v>
@@ -47000,7 +47000,7 @@
         <v>6601</v>
       </c>
       <c r="D977" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E977" t="s">
         <v>8150</v>
@@ -47063,7 +47063,7 @@
         <v>6150</v>
       </c>
       <c r="D980" t="s">
-        <v>7691</v>
+        <v>7690</v>
       </c>
       <c r="E980" t="s">
         <v>8150</v>
@@ -47083,7 +47083,7 @@
         <v>6587</v>
       </c>
       <c r="D981" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E981" t="s">
         <v>8150</v>
@@ -47183,7 +47183,7 @@
         <v>6615</v>
       </c>
       <c r="D986" t="s">
-        <v>7692</v>
+        <v>7691</v>
       </c>
       <c r="E986" t="s">
         <v>8150</v>
@@ -47206,7 +47206,7 @@
         <v>6150</v>
       </c>
       <c r="D987" t="s">
-        <v>7693</v>
+        <v>7692</v>
       </c>
       <c r="E987" t="s">
         <v>8150</v>
@@ -47226,7 +47226,7 @@
         <v>6150</v>
       </c>
       <c r="D988" t="s">
-        <v>7694</v>
+        <v>7693</v>
       </c>
       <c r="E988" t="s">
         <v>8150</v>
@@ -47266,7 +47266,7 @@
         <v>6150</v>
       </c>
       <c r="D990" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E990" t="s">
         <v>8150</v>
@@ -47289,7 +47289,7 @@
         <v>6617</v>
       </c>
       <c r="D991" t="s">
-        <v>7610</v>
+        <v>7609</v>
       </c>
       <c r="E991" t="s">
         <v>8150</v>
@@ -47309,7 +47309,7 @@
         <v>6618</v>
       </c>
       <c r="D992" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E992" t="s">
         <v>8150</v>
@@ -47332,7 +47332,7 @@
         <v>6619</v>
       </c>
       <c r="D993" t="s">
-        <v>7652</v>
+        <v>7651</v>
       </c>
       <c r="E993" t="s">
         <v>8150</v>
@@ -47372,7 +47372,7 @@
         <v>6150</v>
       </c>
       <c r="D995" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E995" t="s">
         <v>8150</v>
@@ -47461,7 +47461,7 @@
         <v>6585</v>
       </c>
       <c r="D999" t="s">
-        <v>7693</v>
+        <v>7692</v>
       </c>
       <c r="E999" t="s">
         <v>8150</v>
@@ -47481,7 +47481,7 @@
         <v>6150</v>
       </c>
       <c r="D1000" t="s">
-        <v>7622</v>
+        <v>7621</v>
       </c>
       <c r="E1000" t="s">
         <v>8150</v>
@@ -47501,7 +47501,7 @@
         <v>6594</v>
       </c>
       <c r="D1001" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E1001" t="s">
         <v>8150</v>
@@ -47541,7 +47541,7 @@
         <v>6603</v>
       </c>
       <c r="D1003" t="s">
-        <v>7692</v>
+        <v>7691</v>
       </c>
       <c r="E1003" t="s">
         <v>8150</v>
@@ -47561,7 +47561,7 @@
         <v>6587</v>
       </c>
       <c r="D1004" t="s">
-        <v>7660</v>
+        <v>7659</v>
       </c>
       <c r="E1004" t="s">
         <v>8150</v>
@@ -47624,7 +47624,7 @@
         <v>6278</v>
       </c>
       <c r="D1007" t="s">
-        <v>7695</v>
+        <v>7694</v>
       </c>
       <c r="E1007" t="s">
         <v>8150</v>
@@ -47667,7 +47667,7 @@
         <v>6623</v>
       </c>
       <c r="D1009" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1009" t="s">
         <v>8150</v>
@@ -47713,7 +47713,7 @@
         <v>6608</v>
       </c>
       <c r="D1011" t="s">
-        <v>7696</v>
+        <v>7695</v>
       </c>
       <c r="E1011" t="s">
         <v>8150</v>
@@ -47733,7 +47733,7 @@
         <v>6624</v>
       </c>
       <c r="D1012" t="s">
-        <v>7697</v>
+        <v>7696</v>
       </c>
       <c r="E1012" t="s">
         <v>8150</v>
@@ -47836,7 +47836,7 @@
         <v>6590</v>
       </c>
       <c r="D1017" t="s">
-        <v>7698</v>
+        <v>7697</v>
       </c>
       <c r="E1017" t="s">
         <v>8150</v>
@@ -47859,7 +47859,7 @@
         <v>6150</v>
       </c>
       <c r="D1018" t="s">
-        <v>7699</v>
+        <v>7698</v>
       </c>
       <c r="E1018" t="s">
         <v>8150</v>
@@ -47905,7 +47905,7 @@
         <v>6626</v>
       </c>
       <c r="D1020" t="s">
-        <v>7689</v>
+        <v>7688</v>
       </c>
       <c r="E1020" t="s">
         <v>8150</v>
@@ -47928,7 +47928,7 @@
         <v>6279</v>
       </c>
       <c r="D1021" t="s">
-        <v>7690</v>
+        <v>7689</v>
       </c>
       <c r="E1021" t="s">
         <v>8150</v>
@@ -47951,7 +47951,7 @@
         <v>6608</v>
       </c>
       <c r="D1022" t="s">
-        <v>7632</v>
+        <v>7631</v>
       </c>
       <c r="E1022" t="s">
         <v>8150</v>
@@ -47974,7 +47974,7 @@
         <v>6150</v>
       </c>
       <c r="D1023" t="s">
-        <v>7700</v>
+        <v>7699</v>
       </c>
       <c r="E1023" t="s">
         <v>8150</v>
@@ -47997,7 +47997,7 @@
         <v>6615</v>
       </c>
       <c r="D1024" t="s">
-        <v>7700</v>
+        <v>7699</v>
       </c>
       <c r="E1024" t="s">
         <v>8150</v>
@@ -48020,7 +48020,7 @@
         <v>6517</v>
       </c>
       <c r="D1025" t="s">
-        <v>7701</v>
+        <v>7700</v>
       </c>
       <c r="E1025" t="s">
         <v>8150</v>
@@ -48043,7 +48043,7 @@
         <v>6150</v>
       </c>
       <c r="D1026" t="s">
-        <v>7702</v>
+        <v>7701</v>
       </c>
       <c r="E1026" t="s">
         <v>8150</v>
@@ -48112,7 +48112,7 @@
         <v>6150</v>
       </c>
       <c r="D1029" t="s">
-        <v>7676</v>
+        <v>7675</v>
       </c>
       <c r="E1029" t="s">
         <v>8150</v>
@@ -48135,7 +48135,7 @@
         <v>6150</v>
       </c>
       <c r="D1030" t="s">
-        <v>7699</v>
+        <v>7698</v>
       </c>
       <c r="E1030" t="s">
         <v>8150</v>
@@ -48158,7 +48158,7 @@
         <v>6268</v>
       </c>
       <c r="D1031" t="s">
-        <v>7662</v>
+        <v>7661</v>
       </c>
       <c r="E1031" t="s">
         <v>8150</v>
@@ -48198,7 +48198,7 @@
         <v>6624</v>
       </c>
       <c r="D1033" t="s">
-        <v>7687</v>
+        <v>7686</v>
       </c>
       <c r="E1033" t="s">
         <v>8150</v>
@@ -48261,7 +48261,7 @@
         <v>6585</v>
       </c>
       <c r="D1036" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E1036" t="s">
         <v>8150</v>
@@ -48281,7 +48281,7 @@
         <v>6150</v>
       </c>
       <c r="D1037" t="s">
-        <v>7703</v>
+        <v>7702</v>
       </c>
       <c r="E1037" t="s">
         <v>8150</v>
@@ -48301,7 +48301,7 @@
         <v>6150</v>
       </c>
       <c r="D1038" t="s">
-        <v>7610</v>
+        <v>7609</v>
       </c>
       <c r="E1038" t="s">
         <v>8150</v>
@@ -48341,7 +48341,7 @@
         <v>6150</v>
       </c>
       <c r="D1040" t="s">
-        <v>7704</v>
+        <v>7703</v>
       </c>
       <c r="E1040" t="s">
         <v>8150</v>
@@ -48361,7 +48361,7 @@
         <v>6558</v>
       </c>
       <c r="D1041" t="s">
-        <v>7662</v>
+        <v>7661</v>
       </c>
       <c r="E1041" t="s">
         <v>8150</v>
@@ -48381,7 +48381,7 @@
         <v>6150</v>
       </c>
       <c r="D1042" t="s">
-        <v>7705</v>
+        <v>7704</v>
       </c>
       <c r="E1042" t="s">
         <v>8151</v>
@@ -48470,7 +48470,7 @@
         <v>6628</v>
       </c>
       <c r="D1046" t="s">
-        <v>7651</v>
+        <v>7650</v>
       </c>
       <c r="E1046" t="s">
         <v>8153</v>
@@ -48493,7 +48493,7 @@
         <v>6629</v>
       </c>
       <c r="D1047" t="s">
-        <v>7706</v>
+        <v>7705</v>
       </c>
       <c r="E1047" t="s">
         <v>8153</v>
@@ -48516,7 +48516,7 @@
         <v>6629</v>
       </c>
       <c r="D1048" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1048" t="s">
         <v>8153</v>
@@ -48539,7 +48539,7 @@
         <v>6320</v>
       </c>
       <c r="D1049" t="s">
-        <v>7707</v>
+        <v>7706</v>
       </c>
       <c r="E1049" t="s">
         <v>8153</v>
@@ -48582,7 +48582,7 @@
         <v>6630</v>
       </c>
       <c r="D1051" t="s">
-        <v>7708</v>
+        <v>7707</v>
       </c>
       <c r="E1051" t="s">
         <v>8153</v>
@@ -48648,7 +48648,7 @@
         <v>6632</v>
       </c>
       <c r="D1054" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1054" t="s">
         <v>8153</v>
@@ -48668,7 +48668,7 @@
         <v>6424</v>
       </c>
       <c r="D1055" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E1055" t="s">
         <v>8153</v>
@@ -48711,7 +48711,7 @@
         <v>6253</v>
       </c>
       <c r="D1057" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1057" t="s">
         <v>8153</v>
@@ -48734,7 +48734,7 @@
         <v>6634</v>
       </c>
       <c r="D1058" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1058" t="s">
         <v>8153</v>
@@ -48754,7 +48754,7 @@
         <v>6540</v>
       </c>
       <c r="D1059" t="s">
-        <v>7710</v>
+        <v>7709</v>
       </c>
       <c r="E1059" t="s">
         <v>8153</v>
@@ -48777,7 +48777,7 @@
         <v>6635</v>
       </c>
       <c r="D1060" t="s">
-        <v>7711</v>
+        <v>7710</v>
       </c>
       <c r="E1060" t="s">
         <v>8153</v>
@@ -48797,7 +48797,7 @@
         <v>6636</v>
       </c>
       <c r="D1061" t="s">
-        <v>7712</v>
+        <v>7711</v>
       </c>
       <c r="E1061" t="s">
         <v>8153</v>
@@ -48935,7 +48935,7 @@
         <v>6173</v>
       </c>
       <c r="D1067" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E1067" t="s">
         <v>8153</v>
@@ -48958,7 +48958,7 @@
         <v>6150</v>
       </c>
       <c r="D1068" t="s">
-        <v>7713</v>
+        <v>7712</v>
       </c>
       <c r="E1068" t="s">
         <v>8153</v>
@@ -49004,7 +49004,7 @@
         <v>6642</v>
       </c>
       <c r="D1070" t="s">
-        <v>7714</v>
+        <v>7713</v>
       </c>
       <c r="E1070" t="s">
         <v>8153</v>
@@ -49027,7 +49027,7 @@
         <v>6643</v>
       </c>
       <c r="D1071" t="s">
-        <v>7715</v>
+        <v>7714</v>
       </c>
       <c r="E1071" t="s">
         <v>8153</v>
@@ -49050,7 +49050,7 @@
         <v>6644</v>
       </c>
       <c r="D1072" t="s">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="E1072" t="s">
         <v>8153</v>
@@ -49096,7 +49096,7 @@
         <v>6558</v>
       </c>
       <c r="D1074" t="s">
-        <v>7717</v>
+        <v>7716</v>
       </c>
       <c r="E1074" t="s">
         <v>8153</v>
@@ -49116,7 +49116,7 @@
         <v>6488</v>
       </c>
       <c r="D1075" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1075" t="s">
         <v>8153</v>
@@ -49185,7 +49185,7 @@
         <v>6279</v>
       </c>
       <c r="D1078" t="s">
-        <v>7598</v>
+        <v>7597</v>
       </c>
       <c r="E1078" t="s">
         <v>8153</v>
@@ -49277,7 +49277,7 @@
         <v>6279</v>
       </c>
       <c r="D1082" t="s">
-        <v>7708</v>
+        <v>7707</v>
       </c>
       <c r="E1082" t="s">
         <v>8153</v>
@@ -49323,7 +49323,7 @@
         <v>6558</v>
       </c>
       <c r="D1084" t="s">
-        <v>7718</v>
+        <v>7717</v>
       </c>
       <c r="E1084" t="s">
         <v>8153</v>
@@ -49346,7 +49346,7 @@
         <v>6173</v>
       </c>
       <c r="D1085" t="s">
-        <v>7719</v>
+        <v>7718</v>
       </c>
       <c r="E1085" t="s">
         <v>8153</v>
@@ -49415,7 +49415,7 @@
         <v>6649</v>
       </c>
       <c r="D1088" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E1088" t="s">
         <v>8153</v>
@@ -49438,7 +49438,7 @@
         <v>6650</v>
       </c>
       <c r="D1089" t="s">
-        <v>7711</v>
+        <v>7710</v>
       </c>
       <c r="E1089" t="s">
         <v>8153</v>
@@ -49481,7 +49481,7 @@
         <v>6635</v>
       </c>
       <c r="D1091" t="s">
-        <v>7720</v>
+        <v>7719</v>
       </c>
       <c r="E1091" t="s">
         <v>8153</v>
@@ -49590,7 +49590,7 @@
         <v>6098</v>
       </c>
       <c r="D1096" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E1096" t="s">
         <v>8153</v>
@@ -49679,7 +49679,7 @@
         <v>6654</v>
       </c>
       <c r="D1100" t="s">
-        <v>7721</v>
+        <v>7720</v>
       </c>
       <c r="E1100" t="s">
         <v>8153</v>
@@ -49699,7 +49699,7 @@
         <v>6655</v>
       </c>
       <c r="D1101" t="s">
-        <v>7720</v>
+        <v>7719</v>
       </c>
       <c r="E1101" t="s">
         <v>8153</v>
@@ -49768,7 +49768,7 @@
         <v>6635</v>
       </c>
       <c r="D1104" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E1104" t="s">
         <v>8153</v>
@@ -49814,7 +49814,7 @@
         <v>6657</v>
       </c>
       <c r="D1106" t="s">
-        <v>7722</v>
+        <v>7721</v>
       </c>
       <c r="E1106" t="s">
         <v>8153</v>
@@ -49857,7 +49857,7 @@
         <v>6658</v>
       </c>
       <c r="D1108" t="s">
-        <v>7723</v>
+        <v>7722</v>
       </c>
       <c r="E1108" t="s">
         <v>8153</v>
@@ -49903,7 +49903,7 @@
         <v>6659</v>
       </c>
       <c r="D1110" t="s">
-        <v>7724</v>
+        <v>7723</v>
       </c>
       <c r="E1110" t="s">
         <v>8153</v>
@@ -49969,7 +49969,7 @@
         <v>6661</v>
       </c>
       <c r="D1113" t="s">
-        <v>7724</v>
+        <v>7723</v>
       </c>
       <c r="E1113" t="s">
         <v>8153</v>
@@ -50012,7 +50012,7 @@
         <v>6635</v>
       </c>
       <c r="D1115" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E1115" t="s">
         <v>8153</v>
@@ -50098,7 +50098,7 @@
         <v>6651</v>
       </c>
       <c r="D1119" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1119" t="s">
         <v>8153</v>
@@ -50144,7 +50144,7 @@
         <v>6320</v>
       </c>
       <c r="D1121" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E1121" t="s">
         <v>8153</v>
@@ -50351,7 +50351,7 @@
         <v>6419</v>
       </c>
       <c r="D1130" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1130" t="s">
         <v>8153</v>
@@ -50486,7 +50486,7 @@
         <v>6280</v>
       </c>
       <c r="D1136" t="s">
-        <v>7715</v>
+        <v>7714</v>
       </c>
       <c r="E1136" t="s">
         <v>8153</v>
@@ -50509,7 +50509,7 @@
         <v>6644</v>
       </c>
       <c r="D1137" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E1137" t="s">
         <v>8153</v>
@@ -50578,7 +50578,7 @@
         <v>6650</v>
       </c>
       <c r="D1140" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1140" t="s">
         <v>8153</v>
@@ -50647,7 +50647,7 @@
         <v>6650</v>
       </c>
       <c r="D1143" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E1143" t="s">
         <v>8153</v>
@@ -50739,7 +50739,7 @@
         <v>6673</v>
       </c>
       <c r="D1147" t="s">
-        <v>7567</v>
+        <v>7566</v>
       </c>
       <c r="E1147" t="s">
         <v>8153</v>
@@ -50831,7 +50831,7 @@
         <v>6675</v>
       </c>
       <c r="D1151" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1151" t="s">
         <v>8153</v>
@@ -50854,7 +50854,7 @@
         <v>6618</v>
       </c>
       <c r="D1152" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1152" t="s">
         <v>8153</v>
@@ -50877,7 +50877,7 @@
         <v>6651</v>
       </c>
       <c r="D1153" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1153" t="s">
         <v>8153</v>
@@ -50923,7 +50923,7 @@
         <v>6067</v>
       </c>
       <c r="D1155" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1155" t="s">
         <v>8154</v>
@@ -51199,7 +51199,7 @@
         <v>6094</v>
       </c>
       <c r="D1167" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E1167" t="s">
         <v>8156</v>
@@ -51498,7 +51498,7 @@
         <v>6320</v>
       </c>
       <c r="D1180" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E1180" t="s">
         <v>8156</v>
@@ -51636,7 +51636,7 @@
         <v>6680</v>
       </c>
       <c r="D1186" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E1186" t="s">
         <v>8156</v>
@@ -51705,7 +51705,7 @@
         <v>6320</v>
       </c>
       <c r="D1189" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1189" t="s">
         <v>8156</v>
@@ -52234,7 +52234,7 @@
         <v>6320</v>
       </c>
       <c r="D1212" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E1212" t="s">
         <v>8156</v>
@@ -52441,7 +52441,7 @@
         <v>6320</v>
       </c>
       <c r="D1221" t="s">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="E1221" t="s">
         <v>8156</v>
@@ -52901,7 +52901,7 @@
         <v>6094</v>
       </c>
       <c r="D1241" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E1241" t="s">
         <v>8156</v>
@@ -53108,7 +53108,7 @@
         <v>6094</v>
       </c>
       <c r="D1250" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E1250" t="s">
         <v>8156</v>
@@ -53154,7 +53154,7 @@
         <v>6320</v>
       </c>
       <c r="D1252" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1252" t="s">
         <v>8156</v>
@@ -53177,7 +53177,7 @@
         <v>6084</v>
       </c>
       <c r="D1253" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1253" t="s">
         <v>8156</v>
@@ -53223,7 +53223,7 @@
         <v>6320</v>
       </c>
       <c r="D1255" t="s">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="E1255" t="s">
         <v>8156</v>
@@ -53292,7 +53292,7 @@
         <v>6320</v>
       </c>
       <c r="D1258" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1258" t="s">
         <v>8156</v>
@@ -54143,7 +54143,7 @@
         <v>6320</v>
       </c>
       <c r="D1295" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1295" t="s">
         <v>8156</v>
@@ -54281,7 +54281,7 @@
         <v>6085</v>
       </c>
       <c r="D1301" t="s">
-        <v>7655</v>
+        <v>7654</v>
       </c>
       <c r="E1301" t="s">
         <v>8156</v>
@@ -54557,7 +54557,7 @@
         <v>6094</v>
       </c>
       <c r="D1313" t="s">
-        <v>7568</v>
+        <v>7567</v>
       </c>
       <c r="E1313" t="s">
         <v>8156</v>
@@ -54695,7 +54695,7 @@
         <v>6085</v>
       </c>
       <c r="D1319" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E1319" t="s">
         <v>8156</v>
@@ -54741,7 +54741,7 @@
         <v>6085</v>
       </c>
       <c r="D1321" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E1321" t="s">
         <v>8156</v>
@@ -54925,7 +54925,7 @@
         <v>6320</v>
       </c>
       <c r="D1329" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1329" t="s">
         <v>8156</v>
@@ -55339,7 +55339,7 @@
         <v>6320</v>
       </c>
       <c r="D1347" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1347" t="s">
         <v>8156</v>
@@ -55684,7 +55684,7 @@
         <v>6320</v>
       </c>
       <c r="D1362" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1362" t="s">
         <v>8156</v>
@@ -56098,7 +56098,7 @@
         <v>6320</v>
       </c>
       <c r="D1380" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E1380" t="s">
         <v>8156</v>
@@ -56213,7 +56213,7 @@
         <v>6421</v>
       </c>
       <c r="D1385" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E1385" t="s">
         <v>8156</v>
@@ -56351,7 +56351,7 @@
         <v>6320</v>
       </c>
       <c r="D1391" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E1391" t="s">
         <v>8156</v>
@@ -56512,7 +56512,7 @@
         <v>6320</v>
       </c>
       <c r="D1398" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1398" t="s">
         <v>8156</v>
@@ -56673,7 +56673,7 @@
         <v>6692</v>
       </c>
       <c r="D1405" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1405" t="s">
         <v>8156</v>
@@ -57225,7 +57225,7 @@
         <v>6085</v>
       </c>
       <c r="D1429" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1429" t="s">
         <v>8156</v>
@@ -57386,7 +57386,7 @@
         <v>6320</v>
       </c>
       <c r="D1436" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E1436" t="s">
         <v>8156</v>
@@ -57639,7 +57639,7 @@
         <v>6094</v>
       </c>
       <c r="D1447" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1447" t="s">
         <v>8156</v>
@@ -57731,7 +57731,7 @@
         <v>6320</v>
       </c>
       <c r="D1451" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E1451" t="s">
         <v>8156</v>
@@ -57754,7 +57754,7 @@
         <v>6320</v>
       </c>
       <c r="D1452" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1452" t="s">
         <v>8156</v>
@@ -58283,7 +58283,7 @@
         <v>6320</v>
       </c>
       <c r="D1475" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1475" t="s">
         <v>8156</v>
@@ -58743,7 +58743,7 @@
         <v>6320</v>
       </c>
       <c r="D1495" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E1495" t="s">
         <v>8156</v>
@@ -58996,7 +58996,7 @@
         <v>6320</v>
       </c>
       <c r="D1506" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1506" t="s">
         <v>8156</v>
@@ -59387,7 +59387,7 @@
         <v>6320</v>
       </c>
       <c r="D1523" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E1523" t="s">
         <v>8156</v>
@@ -59571,7 +59571,7 @@
         <v>6320</v>
       </c>
       <c r="D1531" t="s">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="E1531" t="s">
         <v>8156</v>
@@ -59939,7 +59939,7 @@
         <v>6085</v>
       </c>
       <c r="D1547" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E1547" t="s">
         <v>8156</v>
@@ -59962,7 +59962,7 @@
         <v>6085</v>
       </c>
       <c r="D1548" t="s">
-        <v>7655</v>
+        <v>7654</v>
       </c>
       <c r="E1548" t="s">
         <v>8156</v>
@@ -60123,7 +60123,7 @@
         <v>6150</v>
       </c>
       <c r="D1555" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1555" t="s">
         <v>8157</v>
@@ -60238,7 +60238,7 @@
         <v>6071</v>
       </c>
       <c r="D1560" t="s">
-        <v>7657</v>
+        <v>7656</v>
       </c>
       <c r="E1560" t="s">
         <v>8157</v>
@@ -60284,7 +60284,7 @@
         <v>6180</v>
       </c>
       <c r="D1562" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E1562" t="s">
         <v>8157</v>
@@ -60813,7 +60813,7 @@
         <v>6329</v>
       </c>
       <c r="D1585" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E1585" t="s">
         <v>8157</v>
@@ -61825,7 +61825,7 @@
         <v>6733</v>
       </c>
       <c r="D1629" t="s">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="E1629" t="s">
         <v>8157</v>
@@ -61894,7 +61894,7 @@
         <v>6736</v>
       </c>
       <c r="D1632" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E1632" t="s">
         <v>8157</v>
@@ -61963,7 +61963,7 @@
         <v>6739</v>
       </c>
       <c r="D1635" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1635" t="s">
         <v>8157</v>
@@ -62285,7 +62285,7 @@
         <v>6748</v>
       </c>
       <c r="D1649" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1649" t="s">
         <v>8157</v>
@@ -62331,7 +62331,7 @@
         <v>6713</v>
       </c>
       <c r="D1651" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E1651" t="s">
         <v>8157</v>
@@ -62354,7 +62354,7 @@
         <v>6749</v>
       </c>
       <c r="D1652" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E1652" t="s">
         <v>8157</v>
@@ -62377,7 +62377,7 @@
         <v>6750</v>
       </c>
       <c r="D1653" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E1653" t="s">
         <v>8157</v>
@@ -62653,7 +62653,7 @@
         <v>6712</v>
       </c>
       <c r="D1665" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E1665" t="s">
         <v>8157</v>
@@ -63021,7 +63021,7 @@
         <v>6764</v>
       </c>
       <c r="D1681" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1681" t="s">
         <v>8157</v>
@@ -63113,7 +63113,7 @@
         <v>6178</v>
       </c>
       <c r="D1685" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E1685" t="s">
         <v>8157</v>
@@ -63320,7 +63320,7 @@
         <v>6174</v>
       </c>
       <c r="D1694" t="s">
-        <v>7696</v>
+        <v>7695</v>
       </c>
       <c r="E1694" t="s">
         <v>8157</v>
@@ -63458,7 +63458,7 @@
         <v>6150</v>
       </c>
       <c r="D1700" t="s">
-        <v>7638</v>
+        <v>7637</v>
       </c>
       <c r="E1700" t="s">
         <v>8157</v>
@@ -63481,7 +63481,7 @@
         <v>6705</v>
       </c>
       <c r="D1701" t="s">
-        <v>7556</v>
+        <v>7559</v>
       </c>
       <c r="E1701" t="s">
         <v>8157</v>
@@ -63550,7 +63550,7 @@
         <v>6069</v>
       </c>
       <c r="D1704" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1704" t="s">
         <v>8157</v>
@@ -63665,7 +63665,7 @@
         <v>6771</v>
       </c>
       <c r="D1709" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1709" t="s">
         <v>8157</v>
@@ -63803,7 +63803,7 @@
         <v>6774</v>
       </c>
       <c r="D1715" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1715" t="s">
         <v>8157</v>
@@ -64102,7 +64102,7 @@
         <v>6457</v>
       </c>
       <c r="D1728" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1728" t="s">
         <v>8157</v>
@@ -64286,7 +64286,7 @@
         <v>6765</v>
       </c>
       <c r="D1736" t="s">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="E1736" t="s">
         <v>8157</v>
@@ -64355,7 +64355,7 @@
         <v>6785</v>
       </c>
       <c r="D1739" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E1739" t="s">
         <v>8157</v>
@@ -64401,7 +64401,7 @@
         <v>6320</v>
       </c>
       <c r="D1741" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1741" t="s">
         <v>8157</v>
@@ -64424,7 +64424,7 @@
         <v>6786</v>
       </c>
       <c r="D1742" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E1742" t="s">
         <v>8157</v>
@@ -65045,7 +65045,7 @@
         <v>6801</v>
       </c>
       <c r="D1769" t="s">
-        <v>7687</v>
+        <v>7686</v>
       </c>
       <c r="E1769" t="s">
         <v>8159</v>
@@ -65148,7 +65148,7 @@
         <v>6804</v>
       </c>
       <c r="D1774" t="s">
-        <v>7650</v>
+        <v>7649</v>
       </c>
       <c r="E1774" t="s">
         <v>8159</v>
@@ -65377,7 +65377,7 @@
         <v>6807</v>
       </c>
       <c r="D1785" t="s">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="E1785" t="s">
         <v>8159</v>
@@ -65520,7 +65520,7 @@
         <v>6550</v>
       </c>
       <c r="D1792" t="s">
-        <v>7635</v>
+        <v>7634</v>
       </c>
       <c r="E1792" t="s">
         <v>8159</v>
@@ -65563,7 +65563,7 @@
         <v>6550</v>
       </c>
       <c r="D1794" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E1794" t="s">
         <v>8159</v>
@@ -65609,7 +65609,7 @@
         <v>6801</v>
       </c>
       <c r="D1796" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E1796" t="s">
         <v>8159</v>
@@ -65669,7 +65669,7 @@
         <v>6550</v>
       </c>
       <c r="D1799" t="s">
-        <v>7702</v>
+        <v>7701</v>
       </c>
       <c r="E1799" t="s">
         <v>8159</v>
@@ -65689,7 +65689,7 @@
         <v>6526</v>
       </c>
       <c r="D1800" t="s">
-        <v>7671</v>
+        <v>7670</v>
       </c>
       <c r="E1800" t="s">
         <v>8159</v>
@@ -65709,7 +65709,7 @@
         <v>6808</v>
       </c>
       <c r="D1801" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E1801" t="s">
         <v>8159</v>
@@ -65795,7 +65795,7 @@
         <v>6814</v>
       </c>
       <c r="D1805" t="s">
-        <v>7704</v>
+        <v>7703</v>
       </c>
       <c r="E1805" t="s">
         <v>8159</v>
@@ -66116,7 +66116,7 @@
         <v>6497</v>
       </c>
       <c r="D1820" t="s">
-        <v>7699</v>
+        <v>7698</v>
       </c>
       <c r="E1820" t="s">
         <v>8159</v>
@@ -66374,7 +66374,7 @@
         <v>6811</v>
       </c>
       <c r="D1832" t="s">
-        <v>7620</v>
+        <v>7619</v>
       </c>
       <c r="E1832" t="s">
         <v>8159</v>
@@ -66454,7 +66454,7 @@
         <v>6803</v>
       </c>
       <c r="D1836" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E1836" t="s">
         <v>8159</v>
@@ -66474,7 +66474,7 @@
         <v>6821</v>
       </c>
       <c r="D1837" t="s">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="E1837" t="s">
         <v>8159</v>
@@ -66497,7 +66497,7 @@
         <v>6547</v>
       </c>
       <c r="D1838" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E1838" t="s">
         <v>8159</v>
@@ -66589,7 +66589,7 @@
         <v>6801</v>
       </c>
       <c r="D1842" t="s">
-        <v>7618</v>
+        <v>7617</v>
       </c>
       <c r="E1842" t="s">
         <v>8159</v>
@@ -66655,7 +66655,7 @@
         <v>6805</v>
       </c>
       <c r="D1845" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E1845" t="s">
         <v>8159</v>
@@ -66678,7 +66678,7 @@
         <v>6550</v>
       </c>
       <c r="D1846" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E1846" t="s">
         <v>8159</v>
@@ -66698,7 +66698,7 @@
         <v>6801</v>
       </c>
       <c r="D1847" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E1847" t="s">
         <v>8159</v>
@@ -66761,7 +66761,7 @@
         <v>6825</v>
       </c>
       <c r="D1850" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E1850" t="s">
         <v>8159</v>
@@ -66824,7 +66824,7 @@
         <v>6801</v>
       </c>
       <c r="D1853" t="s">
-        <v>7660</v>
+        <v>7659</v>
       </c>
       <c r="E1853" t="s">
         <v>8159</v>
@@ -66953,7 +66953,7 @@
         <v>6479</v>
       </c>
       <c r="D1859" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E1859" t="s">
         <v>8159</v>
@@ -67033,7 +67033,7 @@
         <v>6828</v>
       </c>
       <c r="D1863" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E1863" t="s">
         <v>8159</v>
@@ -67145,7 +67145,7 @@
         <v>6829</v>
       </c>
       <c r="D1868" t="s">
-        <v>7699</v>
+        <v>7698</v>
       </c>
       <c r="E1868" t="s">
         <v>8159</v>
@@ -67538,7 +67538,7 @@
         <v>6836</v>
       </c>
       <c r="D1886" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1886" t="s">
         <v>8164</v>
@@ -67621,7 +67621,7 @@
         <v>6070</v>
       </c>
       <c r="D1890" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1890" t="s">
         <v>8164</v>
@@ -67641,7 +67641,7 @@
         <v>6839</v>
       </c>
       <c r="D1891" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1891" t="s">
         <v>8164</v>
@@ -67744,7 +67744,7 @@
         <v>6844</v>
       </c>
       <c r="D1896" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1896" t="s">
         <v>8164</v>
@@ -67907,7 +67907,7 @@
         <v>6848</v>
       </c>
       <c r="D1904" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1904" t="s">
         <v>8164</v>
@@ -67927,7 +67927,7 @@
         <v>6321</v>
       </c>
       <c r="D1905" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1905" t="s">
         <v>8164</v>
@@ -68067,7 +68067,7 @@
         <v>6851</v>
       </c>
       <c r="D1912" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1912" t="s">
         <v>8164</v>
@@ -68107,7 +68107,7 @@
         <v>6692</v>
       </c>
       <c r="D1914" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1914" t="s">
         <v>8164</v>
@@ -68147,7 +68147,7 @@
         <v>6836</v>
       </c>
       <c r="D1916" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1916" t="s">
         <v>8164</v>
@@ -68167,7 +68167,7 @@
         <v>6150</v>
       </c>
       <c r="D1917" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1917" t="s">
         <v>8164</v>
@@ -68187,7 +68187,7 @@
         <v>6854</v>
       </c>
       <c r="D1918" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1918" t="s">
         <v>8164</v>
@@ -68250,7 +68250,7 @@
         <v>6856</v>
       </c>
       <c r="D1921" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1921" t="s">
         <v>8164</v>
@@ -68293,7 +68293,7 @@
         <v>6857</v>
       </c>
       <c r="D1923" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1923" t="s">
         <v>8164</v>
@@ -68313,7 +68313,7 @@
         <v>6839</v>
       </c>
       <c r="D1924" t="s">
-        <v>7721</v>
+        <v>7720</v>
       </c>
       <c r="E1924" t="s">
         <v>8164</v>
@@ -68353,7 +68353,7 @@
         <v>6075</v>
       </c>
       <c r="D1926" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E1926" t="s">
         <v>8164</v>
@@ -68456,7 +68456,7 @@
         <v>6858</v>
       </c>
       <c r="D1931" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1931" t="s">
         <v>8164</v>
@@ -68539,7 +68539,7 @@
         <v>6859</v>
       </c>
       <c r="D1935" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1935" t="s">
         <v>8164</v>
@@ -68559,7 +68559,7 @@
         <v>6839</v>
       </c>
       <c r="D1936" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1936" t="s">
         <v>8164</v>
@@ -68599,7 +68599,7 @@
         <v>6235</v>
       </c>
       <c r="D1938" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1938" t="s">
         <v>8164</v>
@@ -68702,7 +68702,7 @@
         <v>6862</v>
       </c>
       <c r="D1943" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1943" t="s">
         <v>8164</v>
@@ -68971,7 +68971,7 @@
         <v>6150</v>
       </c>
       <c r="D1956" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1956" t="s">
         <v>8164</v>
@@ -69011,7 +69011,7 @@
         <v>6082</v>
       </c>
       <c r="D1958" t="s">
-        <v>7652</v>
+        <v>7651</v>
       </c>
       <c r="E1958" t="s">
         <v>8164</v>
@@ -69031,7 +69031,7 @@
         <v>6868</v>
       </c>
       <c r="D1959" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E1959" t="s">
         <v>8164</v>
@@ -69074,7 +69074,7 @@
         <v>6870</v>
       </c>
       <c r="D1961" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1961" t="s">
         <v>8164</v>
@@ -69094,7 +69094,7 @@
         <v>6150</v>
       </c>
       <c r="D1962" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E1962" t="s">
         <v>8164</v>
@@ -69340,7 +69340,7 @@
         <v>6839</v>
       </c>
       <c r="D1974" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E1974" t="s">
         <v>8164</v>
@@ -69443,7 +69443,7 @@
         <v>6874</v>
       </c>
       <c r="D1979" t="s">
-        <v>7652</v>
+        <v>7651</v>
       </c>
       <c r="E1979" t="s">
         <v>8164</v>
@@ -69463,7 +69463,7 @@
         <v>6854</v>
       </c>
       <c r="D1980" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E1980" t="s">
         <v>8164</v>
@@ -69503,7 +69503,7 @@
         <v>6080</v>
       </c>
       <c r="D1982" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E1982" t="s">
         <v>8165</v>
@@ -69758,7 +69758,7 @@
         <v>6074</v>
       </c>
       <c r="D1994" t="s">
-        <v>7657</v>
+        <v>7656</v>
       </c>
       <c r="E1994" t="s">
         <v>8165</v>
@@ -69827,7 +69827,7 @@
         <v>6150</v>
       </c>
       <c r="D1997" t="s">
-        <v>7637</v>
+        <v>7636</v>
       </c>
       <c r="E1997" t="s">
         <v>8166</v>
@@ -69870,7 +69870,7 @@
         <v>6765</v>
       </c>
       <c r="D1999" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E1999" t="s">
         <v>8167</v>
@@ -70128,7 +70128,7 @@
         <v>6085</v>
       </c>
       <c r="D2011" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E2011" t="s">
         <v>8167</v>
@@ -70191,7 +70191,7 @@
         <v>6540</v>
       </c>
       <c r="D2014" t="s">
-        <v>7695</v>
+        <v>7694</v>
       </c>
       <c r="E2014" t="s">
         <v>8167</v>
@@ -70277,7 +70277,7 @@
         <v>6881</v>
       </c>
       <c r="D2018" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E2018" t="s">
         <v>8167</v>
@@ -70426,7 +70426,7 @@
         <v>6843</v>
       </c>
       <c r="D2025" t="s">
-        <v>7689</v>
+        <v>7688</v>
       </c>
       <c r="E2025" t="s">
         <v>8167</v>
@@ -70627,7 +70627,7 @@
         <v>6109</v>
       </c>
       <c r="D2034" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E2034" t="s">
         <v>8168</v>
@@ -70854,7 +70854,7 @@
         <v>6897</v>
       </c>
       <c r="D2044" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E2044" t="s">
         <v>8173</v>
@@ -71081,7 +71081,7 @@
         <v>6662</v>
       </c>
       <c r="D2054" t="s">
-        <v>7655</v>
+        <v>7654</v>
       </c>
       <c r="E2054" t="s">
         <v>8175</v>
@@ -71860,7 +71860,7 @@
         <v>6918</v>
       </c>
       <c r="D2091" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2091" t="s">
         <v>8175</v>
@@ -71929,7 +71929,7 @@
         <v>6270</v>
       </c>
       <c r="D2094" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E2094" t="s">
         <v>8175</v>
@@ -72230,7 +72230,7 @@
         <v>6926</v>
       </c>
       <c r="D2108" t="s">
-        <v>7574</v>
+        <v>7573</v>
       </c>
       <c r="E2108" t="s">
         <v>8175</v>
@@ -72522,7 +72522,7 @@
         <v>6934</v>
       </c>
       <c r="D2122" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E2122" t="s">
         <v>8176</v>
@@ -72682,7 +72682,7 @@
         <v>6940</v>
       </c>
       <c r="D2130" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E2130" t="s">
         <v>8177</v>
@@ -72857,7 +72857,7 @@
         <v>6175</v>
       </c>
       <c r="D2138" t="s">
-        <v>7650</v>
+        <v>7649</v>
       </c>
       <c r="E2138" t="s">
         <v>8180</v>
@@ -73049,7 +73049,7 @@
         <v>6954</v>
       </c>
       <c r="D2147" t="s">
-        <v>7570</v>
+        <v>7569</v>
       </c>
       <c r="E2147" t="s">
         <v>8181</v>
@@ -73109,7 +73109,7 @@
         <v>6150</v>
       </c>
       <c r="D2150" t="s">
-        <v>7655</v>
+        <v>7654</v>
       </c>
       <c r="E2150" t="s">
         <v>8181</v>
@@ -73269,7 +73269,7 @@
         <v>6959</v>
       </c>
       <c r="D2158" t="s">
-        <v>7567</v>
+        <v>7566</v>
       </c>
       <c r="E2158" t="s">
         <v>8181</v>
@@ -73335,7 +73335,7 @@
         <v>6960</v>
       </c>
       <c r="D2161" t="s">
-        <v>7583</v>
+        <v>7582</v>
       </c>
       <c r="E2161" t="s">
         <v>8183</v>
@@ -73475,7 +73475,7 @@
         <v>6180</v>
       </c>
       <c r="D2168" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E2168" t="s">
         <v>8184</v>
@@ -73498,7 +73498,7 @@
         <v>6966</v>
       </c>
       <c r="D2169" t="s">
-        <v>7574</v>
+        <v>7573</v>
       </c>
       <c r="E2169" t="s">
         <v>8185</v>
@@ -73761,7 +73761,7 @@
         <v>6346</v>
       </c>
       <c r="D2182" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E2182" t="s">
         <v>8185</v>
@@ -73781,7 +73781,7 @@
         <v>6978</v>
       </c>
       <c r="D2183" t="s">
-        <v>7582</v>
+        <v>7581</v>
       </c>
       <c r="E2183" t="s">
         <v>8185</v>
@@ -73924,7 +73924,7 @@
         <v>6150</v>
       </c>
       <c r="D2190" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2190" t="s">
         <v>8185</v>
@@ -74044,7 +74044,7 @@
         <v>6988</v>
       </c>
       <c r="D2196" t="s">
-        <v>7583</v>
+        <v>7582</v>
       </c>
       <c r="E2196" t="s">
         <v>8185</v>
@@ -74124,7 +74124,7 @@
         <v>6991</v>
       </c>
       <c r="D2200" t="s">
-        <v>7583</v>
+        <v>7582</v>
       </c>
       <c r="E2200" t="s">
         <v>8185</v>
@@ -74224,7 +74224,7 @@
         <v>6994</v>
       </c>
       <c r="D2205" t="s">
-        <v>7649</v>
+        <v>7648</v>
       </c>
       <c r="E2205" t="s">
         <v>8186</v>
@@ -74304,7 +74304,7 @@
         <v>6998</v>
       </c>
       <c r="D2209" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E2209" t="s">
         <v>8186</v>
@@ -74324,7 +74324,7 @@
         <v>6999</v>
       </c>
       <c r="D2210" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E2210" t="s">
         <v>8186</v>
@@ -74367,7 +74367,7 @@
         <v>6716</v>
       </c>
       <c r="D2212" t="s">
-        <v>7614</v>
+        <v>7613</v>
       </c>
       <c r="E2212" t="s">
         <v>8186</v>
@@ -74654,7 +74654,7 @@
         <v>6481</v>
       </c>
       <c r="D2225" t="s">
-        <v>7704</v>
+        <v>7703</v>
       </c>
       <c r="E2225" t="s">
         <v>8186</v>
@@ -74700,7 +74700,7 @@
         <v>7009</v>
       </c>
       <c r="D2227" t="s">
-        <v>7630</v>
+        <v>7629</v>
       </c>
       <c r="E2227" t="s">
         <v>8186</v>
@@ -74746,7 +74746,7 @@
         <v>6481</v>
       </c>
       <c r="D2229" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E2229" t="s">
         <v>8186</v>
@@ -74855,7 +74855,7 @@
         <v>6598</v>
       </c>
       <c r="D2234" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E2234" t="s">
         <v>8186</v>
@@ -74921,7 +74921,7 @@
         <v>7014</v>
       </c>
       <c r="D2237" t="s">
-        <v>7618</v>
+        <v>7617</v>
       </c>
       <c r="E2237" t="s">
         <v>8186</v>
@@ -74964,7 +74964,7 @@
         <v>7015</v>
       </c>
       <c r="D2239" t="s">
-        <v>7667</v>
+        <v>7666</v>
       </c>
       <c r="E2239" t="s">
         <v>8186</v>
@@ -75027,7 +75027,7 @@
         <v>7018</v>
       </c>
       <c r="D2242" t="s">
-        <v>7678</v>
+        <v>7677</v>
       </c>
       <c r="E2242" t="s">
         <v>8186</v>
@@ -75136,7 +75136,7 @@
         <v>7003</v>
       </c>
       <c r="D2247" t="s">
-        <v>7615</v>
+        <v>7614</v>
       </c>
       <c r="E2247" t="s">
         <v>8186</v>
@@ -75156,7 +75156,7 @@
         <v>7019</v>
       </c>
       <c r="D2248" t="s">
-        <v>7676</v>
+        <v>7675</v>
       </c>
       <c r="E2248" t="s">
         <v>8186</v>
@@ -75179,7 +75179,7 @@
         <v>6998</v>
       </c>
       <c r="D2249" t="s">
-        <v>7630</v>
+        <v>7629</v>
       </c>
       <c r="E2249" t="s">
         <v>8186</v>
@@ -75202,7 +75202,7 @@
         <v>7005</v>
       </c>
       <c r="D2250" t="s">
-        <v>7612</v>
+        <v>7611</v>
       </c>
       <c r="E2250" t="s">
         <v>8186</v>
@@ -75334,7 +75334,7 @@
         <v>7024</v>
       </c>
       <c r="D2256" t="s">
-        <v>7704</v>
+        <v>7703</v>
       </c>
       <c r="E2256" t="s">
         <v>8186</v>
@@ -75377,7 +75377,7 @@
         <v>6843</v>
       </c>
       <c r="D2258" t="s">
-        <v>7631</v>
+        <v>7630</v>
       </c>
       <c r="E2258" t="s">
         <v>8186</v>
@@ -75400,7 +75400,7 @@
         <v>6996</v>
       </c>
       <c r="D2259" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2259" t="s">
         <v>8186</v>
@@ -75523,7 +75523,7 @@
         <v>6149</v>
       </c>
       <c r="D2265" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2265" t="s">
         <v>8188</v>
@@ -75583,7 +75583,7 @@
         <v>7030</v>
       </c>
       <c r="D2268" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2268" t="s">
         <v>8188</v>
@@ -75606,7 +75606,7 @@
         <v>7031</v>
       </c>
       <c r="D2269" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2269" t="s">
         <v>8188</v>
@@ -75626,7 +75626,7 @@
         <v>7032</v>
       </c>
       <c r="D2270" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2270" t="s">
         <v>8188</v>
@@ -75649,7 +75649,7 @@
         <v>6705</v>
       </c>
       <c r="D2271" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2271" t="s">
         <v>8188</v>
@@ -75672,7 +75672,7 @@
         <v>6705</v>
       </c>
       <c r="D2272" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2272" t="s">
         <v>8188</v>
@@ -75695,7 +75695,7 @@
         <v>6973</v>
       </c>
       <c r="D2273" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2273" t="s">
         <v>8188</v>
@@ -75755,7 +75755,7 @@
         <v>7035</v>
       </c>
       <c r="D2276" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2276" t="s">
         <v>8188</v>
@@ -75835,7 +75835,7 @@
         <v>6203</v>
       </c>
       <c r="D2280" t="s">
-        <v>7577</v>
+        <v>7576</v>
       </c>
       <c r="E2280" t="s">
         <v>8188</v>
@@ -75858,7 +75858,7 @@
         <v>6319</v>
       </c>
       <c r="D2281" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2281" t="s">
         <v>8188</v>
@@ -75973,7 +75973,7 @@
         <v>6174</v>
       </c>
       <c r="D2286" t="s">
-        <v>7721</v>
+        <v>7720</v>
       </c>
       <c r="E2286" t="s">
         <v>8190</v>
@@ -75996,7 +75996,7 @@
         <v>6174</v>
       </c>
       <c r="D2287" t="s">
-        <v>7593</v>
+        <v>7592</v>
       </c>
       <c r="E2287" t="s">
         <v>8190</v>
@@ -76088,7 +76088,7 @@
         <v>7040</v>
       </c>
       <c r="D2291" t="s">
-        <v>7584</v>
+        <v>7583</v>
       </c>
       <c r="E2291" t="s">
         <v>8191</v>
@@ -76128,7 +76128,7 @@
         <v>7041</v>
       </c>
       <c r="D2293" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E2293" t="s">
         <v>8191</v>
@@ -77211,7 +77211,7 @@
         <v>6320</v>
       </c>
       <c r="D2341" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2341" t="s">
         <v>8193</v>
@@ -77363,7 +77363,7 @@
         <v>6085</v>
       </c>
       <c r="D2348" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E2348" t="s">
         <v>8193</v>
@@ -77449,7 +77449,7 @@
         <v>6275</v>
       </c>
       <c r="D2352" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E2352" t="s">
         <v>8193</v>
@@ -77472,7 +77472,7 @@
         <v>6082</v>
       </c>
       <c r="D2353" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E2353" t="s">
         <v>8193</v>
@@ -77624,7 +77624,7 @@
         <v>6320</v>
       </c>
       <c r="D2360" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2360" t="s">
         <v>8193</v>
@@ -77647,7 +77647,7 @@
         <v>6098</v>
       </c>
       <c r="D2361" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E2361" t="s">
         <v>8193</v>
@@ -77816,7 +77816,7 @@
         <v>6320</v>
       </c>
       <c r="D2369" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E2369" t="s">
         <v>8193</v>
@@ -77885,7 +77885,7 @@
         <v>6320</v>
       </c>
       <c r="D2372" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E2372" t="s">
         <v>8193</v>
@@ -77994,7 +77994,7 @@
         <v>6416</v>
       </c>
       <c r="D2377" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2377" t="s">
         <v>8193</v>
@@ -78083,7 +78083,7 @@
         <v>6320</v>
       </c>
       <c r="D2381" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E2381" t="s">
         <v>8193</v>
@@ -78221,7 +78221,7 @@
         <v>7069</v>
       </c>
       <c r="D2387" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E2387" t="s">
         <v>8193</v>
@@ -78261,7 +78261,7 @@
         <v>6658</v>
       </c>
       <c r="D2389" t="s">
-        <v>7724</v>
+        <v>7723</v>
       </c>
       <c r="E2389" t="s">
         <v>8193</v>
@@ -78413,7 +78413,7 @@
         <v>6662</v>
       </c>
       <c r="D2396" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2396" t="s">
         <v>8193</v>
@@ -78565,7 +78565,7 @@
         <v>6320</v>
       </c>
       <c r="D2403" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2403" t="s">
         <v>8193</v>
@@ -78680,7 +78680,7 @@
         <v>6662</v>
       </c>
       <c r="D2408" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E2408" t="s">
         <v>8193</v>
@@ -78964,7 +78964,7 @@
         <v>6544</v>
       </c>
       <c r="D2421" t="s">
-        <v>7652</v>
+        <v>7651</v>
       </c>
       <c r="E2421" t="s">
         <v>8193</v>
@@ -79030,7 +79030,7 @@
         <v>7077</v>
       </c>
       <c r="D2424" t="s">
-        <v>7652</v>
+        <v>7651</v>
       </c>
       <c r="E2424" t="s">
         <v>8193</v>
@@ -79446,7 +79446,7 @@
         <v>6177</v>
       </c>
       <c r="D2443" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E2443" t="s">
         <v>8193</v>
@@ -79535,7 +79535,7 @@
         <v>6177</v>
       </c>
       <c r="D2447" t="s">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="E2447" t="s">
         <v>8193</v>
@@ -79822,7 +79822,7 @@
         <v>6180</v>
       </c>
       <c r="D2460" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E2460" t="s">
         <v>8193</v>
@@ -79845,7 +79845,7 @@
         <v>7081</v>
       </c>
       <c r="D2461" t="s">
-        <v>7568</v>
+        <v>7567</v>
       </c>
       <c r="E2461" t="s">
         <v>8194</v>
@@ -79885,7 +79885,7 @@
         <v>7083</v>
       </c>
       <c r="D2463" t="s">
-        <v>7659</v>
+        <v>7658</v>
       </c>
       <c r="E2463" t="s">
         <v>8195</v>
@@ -80045,7 +80045,7 @@
         <v>7090</v>
       </c>
       <c r="D2471" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2471" t="s">
         <v>8195</v>
@@ -80231,7 +80231,7 @@
         <v>6431</v>
       </c>
       <c r="D2480" t="s">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="E2480" t="s">
         <v>8196</v>
@@ -80497,7 +80497,7 @@
         <v>6150</v>
       </c>
       <c r="D2493" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E2493" t="s">
         <v>8196</v>
@@ -80609,7 +80609,7 @@
         <v>7107</v>
       </c>
       <c r="D2498" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E2498" t="s">
         <v>8196</v>
@@ -80738,7 +80738,7 @@
         <v>6177</v>
       </c>
       <c r="D2504" t="s">
-        <v>7651</v>
+        <v>7650</v>
       </c>
       <c r="E2504" t="s">
         <v>8197</v>
@@ -80945,7 +80945,7 @@
         <v>6085</v>
       </c>
       <c r="D2513" t="s">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="E2513" t="s">
         <v>8199</v>
@@ -81034,7 +81034,7 @@
         <v>6285</v>
       </c>
       <c r="D2517" t="s">
-        <v>7623</v>
+        <v>7622</v>
       </c>
       <c r="E2517" t="s">
         <v>8199</v>
@@ -81470,7 +81470,7 @@
         <v>6150</v>
       </c>
       <c r="D2537" t="s">
-        <v>7650</v>
+        <v>7649</v>
       </c>
       <c r="E2537" t="s">
         <v>8199</v>
@@ -81765,7 +81765,7 @@
         <v>6271</v>
       </c>
       <c r="D2551" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E2551" t="s">
         <v>8199</v>
@@ -82083,7 +82083,7 @@
         <v>6068</v>
       </c>
       <c r="D2566" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E2566" t="s">
         <v>8199</v>
@@ -82229,7 +82229,7 @@
         <v>7115</v>
       </c>
       <c r="D2573" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E2573" t="s">
         <v>8201</v>
@@ -82249,7 +82249,7 @@
         <v>7119</v>
       </c>
       <c r="D2574" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2574" t="s">
         <v>8201</v>
@@ -82469,7 +82469,7 @@
         <v>7129</v>
       </c>
       <c r="D2585" t="s">
-        <v>7571</v>
+        <v>7570</v>
       </c>
       <c r="E2585" t="s">
         <v>8201</v>
@@ -82569,7 +82569,7 @@
         <v>7131</v>
       </c>
       <c r="D2590" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2590" t="s">
         <v>8201</v>
@@ -82649,7 +82649,7 @@
         <v>7133</v>
       </c>
       <c r="D2594" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E2594" t="s">
         <v>8202</v>
@@ -82769,7 +82769,7 @@
         <v>6150</v>
       </c>
       <c r="D2600" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E2600" t="s">
         <v>8203</v>
@@ -82869,7 +82869,7 @@
         <v>6150</v>
       </c>
       <c r="D2605" t="s">
-        <v>7580</v>
+        <v>7579</v>
       </c>
       <c r="E2605" t="s">
         <v>8203</v>
@@ -82889,7 +82889,7 @@
         <v>7138</v>
       </c>
       <c r="D2606" t="s">
-        <v>7580</v>
+        <v>7579</v>
       </c>
       <c r="E2606" t="s">
         <v>8203</v>
@@ -83244,7 +83244,7 @@
         <v>7145</v>
       </c>
       <c r="D2623" t="s">
-        <v>7581</v>
+        <v>7580</v>
       </c>
       <c r="E2623" t="s">
         <v>8204</v>
@@ -83511,7 +83511,7 @@
         <v>7148</v>
       </c>
       <c r="D2635" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E2635" t="s">
         <v>8206</v>
@@ -83631,7 +83631,7 @@
         <v>7120</v>
       </c>
       <c r="D2641" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E2641" t="s">
         <v>8206</v>
@@ -83697,7 +83697,7 @@
         <v>6150</v>
       </c>
       <c r="D2644" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E2644" t="s">
         <v>8207</v>
@@ -84351,7 +84351,7 @@
         <v>6719</v>
       </c>
       <c r="D2674" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E2674" t="s">
         <v>8208</v>
@@ -84397,7 +84397,7 @@
         <v>7158</v>
       </c>
       <c r="D2676" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E2676" t="s">
         <v>8208</v>
@@ -84420,7 +84420,7 @@
         <v>7160</v>
       </c>
       <c r="D2677" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E2677" t="s">
         <v>8208</v>
@@ -84443,7 +84443,7 @@
         <v>7161</v>
       </c>
       <c r="D2678" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E2678" t="s">
         <v>8208</v>
@@ -85000,7 +85000,7 @@
         <v>6658</v>
       </c>
       <c r="D2703" t="s">
-        <v>7650</v>
+        <v>7649</v>
       </c>
       <c r="E2703" t="s">
         <v>8208</v>
@@ -85109,7 +85109,7 @@
         <v>6109</v>
       </c>
       <c r="D2708" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E2708" t="s">
         <v>8208</v>
@@ -85221,7 +85221,7 @@
         <v>7169</v>
       </c>
       <c r="D2713" t="s">
-        <v>7708</v>
+        <v>7707</v>
       </c>
       <c r="E2713" t="s">
         <v>8208</v>
@@ -85356,7 +85356,7 @@
         <v>7172</v>
       </c>
       <c r="D2719" t="s">
-        <v>7613</v>
+        <v>7612</v>
       </c>
       <c r="E2719" t="s">
         <v>8208</v>
@@ -85468,7 +85468,7 @@
         <v>6150</v>
       </c>
       <c r="D2724" t="s">
-        <v>7597</v>
+        <v>7596</v>
       </c>
       <c r="E2724" t="s">
         <v>8208</v>
@@ -85577,7 +85577,7 @@
         <v>7174</v>
       </c>
       <c r="D2729" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E2729" t="s">
         <v>8208</v>
@@ -85692,7 +85692,7 @@
         <v>7146</v>
       </c>
       <c r="D2734" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E2734" t="s">
         <v>8208</v>
@@ -85715,7 +85715,7 @@
         <v>7164</v>
       </c>
       <c r="D2735" t="s">
-        <v>7715</v>
+        <v>7714</v>
       </c>
       <c r="E2735" t="s">
         <v>8208</v>
@@ -86008,7 +86008,7 @@
         <v>6109</v>
       </c>
       <c r="D2748" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E2748" t="s">
         <v>8208</v>
@@ -86077,7 +86077,7 @@
         <v>7178</v>
       </c>
       <c r="D2751" t="s">
-        <v>7600</v>
+        <v>7599</v>
       </c>
       <c r="E2751" t="s">
         <v>8208</v>
@@ -86295,7 +86295,7 @@
         <v>6831</v>
       </c>
       <c r="D2761" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E2761" t="s">
         <v>8210</v>
@@ -86421,7 +86421,7 @@
         <v>6831</v>
       </c>
       <c r="D2767" t="s">
-        <v>7584</v>
+        <v>7583</v>
       </c>
       <c r="E2767" t="s">
         <v>8210</v>
@@ -86481,7 +86481,7 @@
         <v>6150</v>
       </c>
       <c r="D2770" t="s">
-        <v>7702</v>
+        <v>7701</v>
       </c>
       <c r="E2770" t="s">
         <v>8210</v>
@@ -86741,7 +86741,7 @@
         <v>6150</v>
       </c>
       <c r="D2783" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E2783" t="s">
         <v>8210</v>
@@ -86761,7 +86761,7 @@
         <v>7190</v>
       </c>
       <c r="D2784" t="s">
-        <v>7626</v>
+        <v>7625</v>
       </c>
       <c r="E2784" t="s">
         <v>8210</v>
@@ -86887,7 +86887,7 @@
         <v>6150</v>
       </c>
       <c r="D2790" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E2790" t="s">
         <v>8210</v>
@@ -86930,7 +86930,7 @@
         <v>7183</v>
       </c>
       <c r="D2792" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E2792" t="s">
         <v>8210</v>
@@ -87036,7 +87036,7 @@
         <v>7181</v>
       </c>
       <c r="D2797" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E2797" t="s">
         <v>8210</v>
@@ -87059,7 +87059,7 @@
         <v>7194</v>
       </c>
       <c r="D2798" t="s">
-        <v>7702</v>
+        <v>7701</v>
       </c>
       <c r="E2798" t="s">
         <v>8210</v>
@@ -87208,7 +87208,7 @@
         <v>6996</v>
       </c>
       <c r="D2805" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E2805" t="s">
         <v>8210</v>
@@ -87317,7 +87317,7 @@
         <v>7201</v>
       </c>
       <c r="D2810" t="s">
-        <v>7643</v>
+        <v>7642</v>
       </c>
       <c r="E2810" t="s">
         <v>8211</v>
@@ -87643,7 +87643,7 @@
         <v>7214</v>
       </c>
       <c r="D2826" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E2826" t="s">
         <v>8212</v>
@@ -87663,7 +87663,7 @@
         <v>7215</v>
       </c>
       <c r="D2827" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E2827" t="s">
         <v>8212</v>
@@ -87932,7 +87932,7 @@
         <v>6831</v>
       </c>
       <c r="D2840" t="s">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="E2840" t="s">
         <v>8213</v>
@@ -87972,7 +87972,7 @@
         <v>7226</v>
       </c>
       <c r="D2842" t="s">
-        <v>7702</v>
+        <v>7701</v>
       </c>
       <c r="E2842" t="s">
         <v>8213</v>
@@ -88035,7 +88035,7 @@
         <v>7224</v>
       </c>
       <c r="D2845" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E2845" t="s">
         <v>8213</v>
@@ -88075,7 +88075,7 @@
         <v>7227</v>
       </c>
       <c r="D2847" t="s">
-        <v>7649</v>
+        <v>7648</v>
       </c>
       <c r="E2847" t="s">
         <v>8213</v>
@@ -88161,7 +88161,7 @@
         <v>7229</v>
       </c>
       <c r="D2851" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E2851" t="s">
         <v>8213</v>
@@ -88304,7 +88304,7 @@
         <v>6150</v>
       </c>
       <c r="D2858" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E2858" t="s">
         <v>8213</v>
@@ -88327,7 +88327,7 @@
         <v>7230</v>
       </c>
       <c r="D2859" t="s">
-        <v>7630</v>
+        <v>7629</v>
       </c>
       <c r="E2859" t="s">
         <v>8213</v>
@@ -88347,7 +88347,7 @@
         <v>7230</v>
       </c>
       <c r="D2860" t="s">
-        <v>7702</v>
+        <v>7701</v>
       </c>
       <c r="E2860" t="s">
         <v>8213</v>
@@ -88393,7 +88393,7 @@
         <v>7231</v>
       </c>
       <c r="D2862" t="s">
-        <v>7585</v>
+        <v>7584</v>
       </c>
       <c r="E2862" t="s">
         <v>8213</v>
@@ -88436,7 +88436,7 @@
         <v>7220</v>
       </c>
       <c r="D2864" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E2864" t="s">
         <v>8213</v>
@@ -88456,7 +88456,7 @@
         <v>7233</v>
       </c>
       <c r="D2865" t="s">
-        <v>7564</v>
+        <v>7563</v>
       </c>
       <c r="E2865" t="s">
         <v>8213</v>
@@ -88614,7 +88614,7 @@
         <v>6086</v>
       </c>
       <c r="D2872" t="s">
-        <v>7695</v>
+        <v>7694</v>
       </c>
       <c r="E2872" t="s">
         <v>8213</v>
@@ -88800,7 +88800,7 @@
         <v>6150</v>
       </c>
       <c r="D2881" t="s">
-        <v>7656</v>
+        <v>7655</v>
       </c>
       <c r="E2881" t="s">
         <v>8214</v>
@@ -89020,7 +89020,7 @@
         <v>7249</v>
       </c>
       <c r="D2892" t="s">
-        <v>7573</v>
+        <v>7572</v>
       </c>
       <c r="E2892" t="s">
         <v>8214</v>
@@ -89060,7 +89060,7 @@
         <v>7246</v>
       </c>
       <c r="D2894" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2894" t="s">
         <v>8214</v>
@@ -89080,7 +89080,7 @@
         <v>7251</v>
       </c>
       <c r="D2895" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2895" t="s">
         <v>8214</v>
@@ -89120,7 +89120,7 @@
         <v>7253</v>
       </c>
       <c r="D2897" t="s">
-        <v>7569</v>
+        <v>7568</v>
       </c>
       <c r="E2897" t="s">
         <v>8215</v>
@@ -89183,7 +89183,7 @@
         <v>7256</v>
       </c>
       <c r="D2900" t="s">
-        <v>7656</v>
+        <v>7655</v>
       </c>
       <c r="E2900" t="s">
         <v>8215</v>
@@ -89243,7 +89243,7 @@
         <v>7259</v>
       </c>
       <c r="D2903" t="s">
-        <v>7705</v>
+        <v>7704</v>
       </c>
       <c r="E2903" t="s">
         <v>8215</v>
@@ -89323,7 +89323,7 @@
         <v>7263</v>
       </c>
       <c r="D2907" t="s">
-        <v>7656</v>
+        <v>7655</v>
       </c>
       <c r="E2907" t="s">
         <v>8215</v>
@@ -89363,7 +89363,7 @@
         <v>6705</v>
       </c>
       <c r="D2909" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E2909" t="s">
         <v>8215</v>
@@ -89643,7 +89643,7 @@
         <v>7274</v>
       </c>
       <c r="D2923" t="s">
-        <v>7583</v>
+        <v>7582</v>
       </c>
       <c r="E2923" t="s">
         <v>8216</v>
@@ -89663,7 +89663,7 @@
         <v>7034</v>
       </c>
       <c r="D2924" t="s">
-        <v>7571</v>
+        <v>7570</v>
       </c>
       <c r="E2924" t="s">
         <v>8216</v>
@@ -89723,7 +89723,7 @@
         <v>7276</v>
       </c>
       <c r="D2927" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E2927" t="s">
         <v>8216</v>
@@ -89923,7 +89923,7 @@
         <v>6954</v>
       </c>
       <c r="D2937" t="s">
-        <v>7567</v>
+        <v>7566</v>
       </c>
       <c r="E2937" t="s">
         <v>8216</v>
@@ -90192,7 +90192,7 @@
         <v>7289</v>
       </c>
       <c r="D2950" t="s">
-        <v>7575</v>
+        <v>7574</v>
       </c>
       <c r="E2950" t="s">
         <v>8217</v>
@@ -90298,7 +90298,7 @@
         <v>7196</v>
       </c>
       <c r="D2955" t="s">
-        <v>7687</v>
+        <v>7686</v>
       </c>
       <c r="E2955" t="s">
         <v>8217</v>
@@ -90533,7 +90533,7 @@
         <v>6136</v>
       </c>
       <c r="D2966" t="s">
-        <v>7708</v>
+        <v>7707</v>
       </c>
       <c r="E2966" t="s">
         <v>8218</v>
@@ -90806,7 +90806,7 @@
         <v>7300</v>
       </c>
       <c r="D2978" t="s">
-        <v>7583</v>
+        <v>7582</v>
       </c>
       <c r="E2978" t="s">
         <v>8219</v>
@@ -91069,7 +91069,7 @@
         <v>7110</v>
       </c>
       <c r="D2991" t="s">
-        <v>7566</v>
+        <v>7565</v>
       </c>
       <c r="E2991" t="s">
         <v>8219</v>
@@ -91149,7 +91149,7 @@
         <v>6257</v>
       </c>
       <c r="D2995" t="s">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="E2995" t="s">
         <v>8219</v>
@@ -91413,7 +91413,7 @@
         <v>6150</v>
       </c>
       <c r="D3007" t="s">
-        <v>7647</v>
+        <v>7646</v>
       </c>
       <c r="E3007" t="s">
         <v>8223</v>
@@ -91539,7 +91539,7 @@
         <v>6166</v>
       </c>
       <c r="D3013" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E3013" t="s">
         <v>8223</v>
@@ -91708,7 +91708,7 @@
         <v>7321</v>
       </c>
       <c r="D3021" t="s">
-        <v>7675</v>
+        <v>7674</v>
       </c>
       <c r="E3021" t="s">
         <v>8223</v>
@@ -91751,7 +91751,7 @@
         <v>7318</v>
       </c>
       <c r="D3023" t="s">
-        <v>7675</v>
+        <v>7674</v>
       </c>
       <c r="E3023" t="s">
         <v>8223</v>
@@ -91794,7 +91794,7 @@
         <v>6525</v>
       </c>
       <c r="D3025" t="s">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="E3025" t="s">
         <v>8223</v>
@@ -91863,7 +91863,7 @@
         <v>6166</v>
       </c>
       <c r="D3028" t="s">
-        <v>7642</v>
+        <v>7641</v>
       </c>
       <c r="E3028" t="s">
         <v>8223</v>
@@ -91923,7 +91923,7 @@
         <v>7324</v>
       </c>
       <c r="D3031" t="s">
-        <v>7595</v>
+        <v>7594</v>
       </c>
       <c r="E3031" t="s">
         <v>8223</v>
@@ -91983,7 +91983,7 @@
         <v>6490</v>
       </c>
       <c r="D3034" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E3034" t="s">
         <v>8223</v>
@@ -92364,7 +92364,7 @@
         <v>7328</v>
       </c>
       <c r="D3052" t="s">
-        <v>7685</v>
+        <v>7684</v>
       </c>
       <c r="E3052" t="s">
         <v>8223</v>
@@ -92407,7 +92407,7 @@
         <v>6464</v>
       </c>
       <c r="D3054" t="s">
-        <v>7671</v>
+        <v>7670</v>
       </c>
       <c r="E3054" t="s">
         <v>8223</v>
@@ -92450,7 +92450,7 @@
         <v>6525</v>
       </c>
       <c r="D3056" t="s">
-        <v>7692</v>
+        <v>7691</v>
       </c>
       <c r="E3056" t="s">
         <v>8223</v>
@@ -92473,7 +92473,7 @@
         <v>7329</v>
       </c>
       <c r="D3057" t="s">
-        <v>7559</v>
+        <v>7724</v>
       </c>
       <c r="E3057" t="s">
         <v>8223</v>
@@ -92513,7 +92513,7 @@
         <v>6525</v>
       </c>
       <c r="D3059" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E3059" t="s">
         <v>8223</v>
@@ -92536,7 +92536,7 @@
         <v>7330</v>
       </c>
       <c r="D3060" t="s">
-        <v>7651</v>
+        <v>7650</v>
       </c>
       <c r="E3060" t="s">
         <v>8223</v>
@@ -92619,7 +92619,7 @@
         <v>6166</v>
       </c>
       <c r="D3064" t="s">
-        <v>7616</v>
+        <v>7615</v>
       </c>
       <c r="E3064" t="s">
         <v>8223</v>
@@ -92639,7 +92639,7 @@
         <v>6166</v>
       </c>
       <c r="D3065" t="s">
-        <v>7641</v>
+        <v>7640</v>
       </c>
       <c r="E3065" t="s">
         <v>8223</v>
@@ -92963,7 +92963,7 @@
         <v>6491</v>
       </c>
       <c r="D3080" t="s">
-        <v>7723</v>
+        <v>7722</v>
       </c>
       <c r="E3080" t="s">
         <v>8223</v>
@@ -93491,7 +93491,7 @@
         <v>6525</v>
       </c>
       <c r="D3104" t="s">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="E3104" t="s">
         <v>8223</v>
@@ -93514,7 +93514,7 @@
         <v>6525</v>
       </c>
       <c r="D3105" t="s">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="E3105" t="s">
         <v>8223</v>
@@ -93600,7 +93600,7 @@
         <v>6525</v>
       </c>
       <c r="D3109" t="s">
-        <v>7613</v>
+        <v>7612</v>
       </c>
       <c r="E3109" t="s">
         <v>8223</v>
@@ -93660,7 +93660,7 @@
         <v>6460</v>
       </c>
       <c r="D3112" t="s">
-        <v>7690</v>
+        <v>7689</v>
       </c>
       <c r="E3112" t="s">
         <v>8223</v>
@@ -93680,7 +93680,7 @@
         <v>7319</v>
       </c>
       <c r="D3113" t="s">
-        <v>7663</v>
+        <v>7662</v>
       </c>
       <c r="E3113" t="s">
         <v>8223</v>
@@ -93700,7 +93700,7 @@
         <v>7337</v>
       </c>
       <c r="D3114" t="s">
-        <v>7618</v>
+        <v>7617</v>
       </c>
       <c r="E3114" t="s">
         <v>8223</v>
@@ -93869,7 +93869,7 @@
         <v>7332</v>
       </c>
       <c r="D3122" t="s">
-        <v>7617</v>
+        <v>7616</v>
       </c>
       <c r="E3122" t="s">
         <v>8223</v>
@@ -93978,7 +93978,7 @@
         <v>7334</v>
       </c>
       <c r="D3127" t="s">
-        <v>7689</v>
+        <v>7688</v>
       </c>
       <c r="E3127" t="s">
         <v>8223</v>
@@ -94047,7 +94047,7 @@
         <v>7344</v>
       </c>
       <c r="D3130" t="s">
-        <v>7709</v>
+        <v>7708</v>
       </c>
       <c r="E3130" t="s">
         <v>8225</v>
@@ -94139,7 +94139,7 @@
         <v>6083</v>
       </c>
       <c r="D3134" t="s">
-        <v>7726</v>
+        <v>7869</v>
       </c>
       <c r="E3134" t="s">
         <v>8226</v>
@@ -94159,7 +94159,7 @@
         <v>6253</v>
       </c>
       <c r="D3135" t="s">
-        <v>7558</v>
+        <v>7557</v>
       </c>
       <c r="E3135" t="s">
         <v>8226</v>
@@ -94228,7 +94228,7 @@
         <v>6319</v>
       </c>
       <c r="D3138" t="s">
-        <v>7637</v>
+        <v>7636</v>
       </c>
       <c r="E3138" t="s">
         <v>8226</v>
@@ -94820,7 +94820,7 @@
         <v>7359</v>
       </c>
       <c r="D3164" t="s">
-        <v>7565</v>
+        <v>7564</v>
       </c>
       <c r="E3164" t="s">
         <v>8228</v>
@@ -95023,7 +95023,7 @@
         <v>7365</v>
       </c>
       <c r="D3174" t="s">
-        <v>7593</v>
+        <v>7592</v>
       </c>
       <c r="E3174" t="s">
         <v>8230</v>
@@ -95537,7 +95537,7 @@
         <v>7368</v>
       </c>
       <c r="D3197" t="s">
-        <v>7683</v>
+        <v>7682</v>
       </c>
       <c r="E3197" t="s">
         <v>8230</v>
